--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -512,7 +512,7 @@
         <v>1189.99</v>
       </c>
       <c r="G3" t="n">
-        <v>1192.5</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="4">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="F4" t="n">
-        <v>1189.99</v>
+        <v>1189.49</v>
       </c>
       <c r="G4" t="n">
         <v>1194</v>
@@ -571,7 +571,7 @@
         <v>1199</v>
       </c>
       <c r="F5" t="n">
-        <v>1189.49</v>
+        <v>1187.49</v>
       </c>
       <c r="G5" t="n">
         <v>1194</v>
@@ -602,7 +602,7 @@
         <v>1199</v>
       </c>
       <c r="F6" t="n">
-        <v>1191.49</v>
+        <v>1189.99</v>
       </c>
       <c r="G6" t="n">
         <v>1196</v>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="F7" t="n">
-        <v>1187.49</v>
+        <v>1189.99</v>
       </c>
       <c r="G7" t="n">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="8">
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="F8" t="n">
-        <v>1189.99</v>
+        <v>1187.49</v>
       </c>
       <c r="G8" t="n">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="9">
@@ -695,10 +695,10 @@
         <v>1199</v>
       </c>
       <c r="F9" t="n">
-        <v>1189.49</v>
+        <v>1189.99</v>
       </c>
       <c r="G9" t="n">
-        <v>1192.5</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="10">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="F10" t="n">
-        <v>1189.99</v>
+        <v>1191.49</v>
       </c>
       <c r="G10" t="n">
         <v>1194</v>
@@ -754,13 +754,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="F11" t="n">
-        <v>1189.49</v>
+        <v>1189.99</v>
       </c>
       <c r="G11" t="n">
-        <v>1194</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="12">
@@ -785,13 +785,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="F12" t="n">
-        <v>1189.99</v>
+        <v>1187.49</v>
       </c>
       <c r="G12" t="n">
-        <v>1192.5</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="13">
@@ -819,10 +819,10 @@
         <v>1199</v>
       </c>
       <c r="F13" t="n">
-        <v>1189.99</v>
+        <v>1191.49</v>
       </c>
       <c r="G13" t="n">
-        <v>1194</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="14">
@@ -850,10 +850,10 @@
         <v>1199</v>
       </c>
       <c r="F14" t="n">
-        <v>1187.49</v>
+        <v>1189.99</v>
       </c>
       <c r="G14" t="n">
-        <v>1194</v>
+        <v>1192.5</v>
       </c>
     </row>
     <row r="15">
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="F15" t="n">
-        <v>1187.49</v>
+        <v>1189.99</v>
       </c>
       <c r="G15" t="n">
-        <v>1194</v>
+        <v>1192.5</v>
       </c>
     </row>
     <row r="16">
@@ -915,7 +915,7 @@
         <v>1191.49</v>
       </c>
       <c r="G16" t="n">
-        <v>1196</v>
+        <v>1192.5</v>
       </c>
     </row>
     <row r="17">
@@ -940,13 +940,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="F17" t="n">
-        <v>1191.49</v>
+        <v>1189.99</v>
       </c>
       <c r="G17" t="n">
-        <v>1192.5</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="18">
@@ -974,10 +974,10 @@
         <v>1199</v>
       </c>
       <c r="F18" t="n">
-        <v>1187.49</v>
+        <v>1191.49</v>
       </c>
       <c r="G18" t="n">
-        <v>1194</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="19">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="F19" t="n">
         <v>1191.49</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="F20" t="n">
-        <v>1187.49</v>
+        <v>1191.49</v>
       </c>
       <c r="G20" t="n">
         <v>1196</v>
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="F21" t="n">
-        <v>1189.99</v>
+        <v>1191.49</v>
       </c>
       <c r="G21" t="n">
-        <v>1194</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="22">
@@ -1098,7 +1098,7 @@
         <v>1199</v>
       </c>
       <c r="F22" t="n">
-        <v>1189.49</v>
+        <v>1189.99</v>
       </c>
       <c r="G22" t="n">
         <v>1192.5</v>
@@ -1132,7 +1132,7 @@
         <v>1189.99</v>
       </c>
       <c r="G23" t="n">
-        <v>1194</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="24">
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="F24" t="n">
         <v>1189.99</v>
       </c>
       <c r="G24" t="n">
-        <v>1194</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="25">
@@ -1188,13 +1188,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="F25" t="n">
-        <v>1189.99</v>
+        <v>1191.49</v>
       </c>
       <c r="G25" t="n">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="26">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="F26" t="n">
         <v>1189.99</v>
@@ -1253,7 +1253,7 @@
         <v>1199</v>
       </c>
       <c r="F27" t="n">
-        <v>1189.99</v>
+        <v>1189.49</v>
       </c>
       <c r="G27" t="n">
         <v>1196</v>
@@ -1281,13 +1281,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="F28" t="n">
-        <v>1191.49</v>
+        <v>1187.49</v>
       </c>
       <c r="G28" t="n">
-        <v>1194</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="29">
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="F29" t="n">
         <v>1189.99</v>
       </c>
       <c r="G29" t="n">
-        <v>1194</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="30">
@@ -1346,7 +1346,7 @@
         <v>1199</v>
       </c>
       <c r="F30" t="n">
-        <v>1189.99</v>
+        <v>1187.49</v>
       </c>
       <c r="G30" t="n">
         <v>1194</v>
@@ -1377,7 +1377,7 @@
         <v>1199</v>
       </c>
       <c r="F31" t="n">
-        <v>1189.49</v>
+        <v>1189.99</v>
       </c>
       <c r="G31" t="n">
         <v>1194</v>
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>870.99</v>
+        <v>869.99</v>
       </c>
       <c r="F32" t="n">
         <v>827.49</v>
       </c>
       <c r="G32" t="n">
-        <v>848.49</v>
+        <v>849.99</v>
       </c>
     </row>
     <row r="33">
@@ -1439,7 +1439,7 @@
         <v>869.99</v>
       </c>
       <c r="F33" t="n">
-        <v>831.49</v>
+        <v>827.49</v>
       </c>
       <c r="G33" t="n">
         <v>848.49</v>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>869.99</v>
+        <v>868.99</v>
       </c>
       <c r="F34" t="n">
-        <v>829.49</v>
+        <v>829.99</v>
       </c>
       <c r="G34" t="n">
         <v>849.99</v>
@@ -1498,13 +1498,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>868.99</v>
+        <v>869.99</v>
       </c>
       <c r="F35" t="n">
-        <v>829.99</v>
+        <v>831.49</v>
       </c>
       <c r="G35" t="n">
-        <v>849.99</v>
+        <v>851.99</v>
       </c>
     </row>
     <row r="36">
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>869.99</v>
+        <v>870.99</v>
       </c>
       <c r="F36" t="n">
-        <v>829.49</v>
+        <v>831.49</v>
       </c>
       <c r="G36" t="n">
-        <v>851.99</v>
+        <v>849.99</v>
       </c>
     </row>
     <row r="37">
@@ -1563,7 +1563,7 @@
         <v>868.99</v>
       </c>
       <c r="F37" t="n">
-        <v>829.49</v>
+        <v>829.99</v>
       </c>
       <c r="G37" t="n">
         <v>848.49</v>
@@ -1594,7 +1594,7 @@
         <v>869.99</v>
       </c>
       <c r="F38" t="n">
-        <v>829.99</v>
+        <v>831.49</v>
       </c>
       <c r="G38" t="n">
         <v>851.99</v>
@@ -1622,13 +1622,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>870.99</v>
+        <v>869.99</v>
       </c>
       <c r="F39" t="n">
         <v>829.99</v>
       </c>
       <c r="G39" t="n">
-        <v>848.49</v>
+        <v>849.99</v>
       </c>
     </row>
     <row r="40">
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>869.99</v>
+        <v>868.99</v>
       </c>
       <c r="F40" t="n">
-        <v>829.49</v>
+        <v>829.99</v>
       </c>
       <c r="G40" t="n">
         <v>851.99</v>
@@ -1684,13 +1684,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>869.99</v>
+        <v>870.99</v>
       </c>
       <c r="F41" t="n">
-        <v>829.99</v>
+        <v>829.49</v>
       </c>
       <c r="G41" t="n">
-        <v>851.99</v>
+        <v>849.99</v>
       </c>
     </row>
     <row r="42">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>868.99</v>
+        <v>869.99</v>
       </c>
       <c r="F42" t="n">
         <v>829.99</v>
       </c>
       <c r="G42" t="n">
-        <v>851.99</v>
+        <v>849.99</v>
       </c>
     </row>
     <row r="43">
@@ -1752,7 +1752,7 @@
         <v>827.49</v>
       </c>
       <c r="G43" t="n">
-        <v>849.99</v>
+        <v>851.99</v>
       </c>
     </row>
     <row r="44">
@@ -1783,7 +1783,7 @@
         <v>827.49</v>
       </c>
       <c r="G44" t="n">
-        <v>851.99</v>
+        <v>849.99</v>
       </c>
     </row>
     <row r="45">
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>869.99</v>
+        <v>870.99</v>
       </c>
       <c r="F45" t="n">
         <v>831.49</v>
@@ -1842,10 +1842,10 @@
         <v>869.99</v>
       </c>
       <c r="F46" t="n">
-        <v>829.99</v>
+        <v>831.49</v>
       </c>
       <c r="G46" t="n">
-        <v>851.99</v>
+        <v>848.49</v>
       </c>
     </row>
     <row r="47">
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>870.99</v>
+        <v>869.99</v>
       </c>
       <c r="F47" t="n">
-        <v>829.49</v>
+        <v>829.99</v>
       </c>
       <c r="G47" t="n">
         <v>849.99</v>
@@ -1907,7 +1907,7 @@
         <v>829.49</v>
       </c>
       <c r="G48" t="n">
-        <v>848.49</v>
+        <v>849.99</v>
       </c>
     </row>
     <row r="49">
@@ -1932,13 +1932,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>868.99</v>
+        <v>869.99</v>
       </c>
       <c r="F49" t="n">
-        <v>827.49</v>
+        <v>829.99</v>
       </c>
       <c r="G49" t="n">
-        <v>848.49</v>
+        <v>849.99</v>
       </c>
     </row>
     <row r="50">
@@ -1963,13 +1963,13 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>869.99</v>
+        <v>868.99</v>
       </c>
       <c r="F50" t="n">
-        <v>827.49</v>
+        <v>829.99</v>
       </c>
       <c r="G50" t="n">
-        <v>848.49</v>
+        <v>849.99</v>
       </c>
     </row>
     <row r="51">
@@ -2028,10 +2028,10 @@
         <v>869.99</v>
       </c>
       <c r="F52" t="n">
-        <v>827.49</v>
+        <v>829.99</v>
       </c>
       <c r="G52" t="n">
-        <v>848.49</v>
+        <v>849.99</v>
       </c>
     </row>
     <row r="53">
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>869.99</v>
+        <v>870.99</v>
       </c>
       <c r="F53" t="n">
         <v>829.99</v>
       </c>
       <c r="G53" t="n">
-        <v>851.99</v>
+        <v>849.99</v>
       </c>
     </row>
     <row r="54">
@@ -2093,7 +2093,7 @@
         <v>829.99</v>
       </c>
       <c r="G54" t="n">
-        <v>849.99</v>
+        <v>848.49</v>
       </c>
     </row>
     <row r="55">
@@ -2121,10 +2121,10 @@
         <v>869.99</v>
       </c>
       <c r="F55" t="n">
-        <v>829.49</v>
+        <v>831.49</v>
       </c>
       <c r="G55" t="n">
-        <v>849.99</v>
+        <v>848.49</v>
       </c>
     </row>
     <row r="56">
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>869.99</v>
+        <v>870.99</v>
       </c>
       <c r="F56" t="n">
-        <v>829.99</v>
+        <v>831.49</v>
       </c>
       <c r="G56" t="n">
-        <v>848.49</v>
+        <v>851.99</v>
       </c>
     </row>
     <row r="57">
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>868.99</v>
+        <v>869.99</v>
       </c>
       <c r="F57" t="n">
         <v>827.49</v>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>870.99</v>
+        <v>869.99</v>
       </c>
       <c r="F58" t="n">
-        <v>827.49</v>
+        <v>831.49</v>
       </c>
       <c r="G58" t="n">
         <v>849.99</v>
@@ -2245,10 +2245,10 @@
         <v>869.99</v>
       </c>
       <c r="F59" t="n">
-        <v>829.99</v>
+        <v>827.49</v>
       </c>
       <c r="G59" t="n">
-        <v>851.99</v>
+        <v>849.99</v>
       </c>
     </row>
     <row r="60">
@@ -2276,7 +2276,7 @@
         <v>869.99</v>
       </c>
       <c r="F60" t="n">
-        <v>829.99</v>
+        <v>827.49</v>
       </c>
       <c r="G60" t="n">
         <v>848.49</v>
@@ -2307,10 +2307,10 @@
         <v>869.99</v>
       </c>
       <c r="F61" t="n">
-        <v>829.49</v>
+        <v>827.49</v>
       </c>
       <c r="G61" t="n">
-        <v>851.99</v>
+        <v>849.99</v>
       </c>
     </row>
     <row r="62">
@@ -2335,13 +2335,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="F62" t="n">
-        <v>1298.5</v>
+        <v>1300.5</v>
       </c>
       <c r="G62" t="n">
-        <v>1349</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="63">
@@ -2400,7 +2400,7 @@
         <v>1399</v>
       </c>
       <c r="F64" t="n">
-        <v>1300.5</v>
+        <v>1296.5</v>
       </c>
       <c r="G64" t="n">
         <v>1349</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="F65" t="n">
         <v>1299</v>
@@ -2459,13 +2459,13 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="F66" t="n">
         <v>1299</v>
       </c>
       <c r="G66" t="n">
-        <v>1349</v>
+        <v>1347.5</v>
       </c>
     </row>
     <row r="67">
@@ -2493,10 +2493,10 @@
         <v>1398</v>
       </c>
       <c r="F67" t="n">
-        <v>1298.5</v>
+        <v>1300.5</v>
       </c>
       <c r="G67" t="n">
-        <v>1349</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="68">
@@ -2524,7 +2524,7 @@
         <v>1399</v>
       </c>
       <c r="F68" t="n">
-        <v>1296.5</v>
+        <v>1299</v>
       </c>
       <c r="G68" t="n">
         <v>1349</v>
@@ -2552,13 +2552,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="F69" t="n">
         <v>1299</v>
       </c>
       <c r="G69" t="n">
-        <v>1349</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="70">
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="F70" t="n">
-        <v>1299</v>
+        <v>1300.5</v>
       </c>
       <c r="G70" t="n">
         <v>1349</v>
@@ -2614,13 +2614,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="F71" t="n">
-        <v>1299</v>
+        <v>1298.5</v>
       </c>
       <c r="G71" t="n">
-        <v>1349</v>
+        <v>1347.5</v>
       </c>
     </row>
     <row r="72">
@@ -2651,7 +2651,7 @@
         <v>1299</v>
       </c>
       <c r="G72" t="n">
-        <v>1347.5</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="73">
@@ -2679,10 +2679,10 @@
         <v>1399</v>
       </c>
       <c r="F73" t="n">
-        <v>1300.5</v>
+        <v>1299</v>
       </c>
       <c r="G73" t="n">
-        <v>1351</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="74">
@@ -2707,13 +2707,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="F74" t="n">
         <v>1299</v>
       </c>
       <c r="G74" t="n">
-        <v>1347.5</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="75">
@@ -2744,7 +2744,7 @@
         <v>1299</v>
       </c>
       <c r="G75" t="n">
-        <v>1349</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="76">
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="F76" t="n">
-        <v>1298.5</v>
+        <v>1296.5</v>
       </c>
       <c r="G76" t="n">
         <v>1349</v>
@@ -2800,13 +2800,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="F77" t="n">
         <v>1299</v>
       </c>
       <c r="G77" t="n">
-        <v>1347.5</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="78">
@@ -2834,10 +2834,10 @@
         <v>1399</v>
       </c>
       <c r="F78" t="n">
-        <v>1300.5</v>
+        <v>1296.5</v>
       </c>
       <c r="G78" t="n">
-        <v>1349</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="79">
@@ -2868,7 +2868,7 @@
         <v>1296.5</v>
       </c>
       <c r="G79" t="n">
-        <v>1347.5</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="80">
@@ -2896,10 +2896,10 @@
         <v>1399</v>
       </c>
       <c r="F80" t="n">
-        <v>1296.5</v>
+        <v>1298.5</v>
       </c>
       <c r="G80" t="n">
-        <v>1349</v>
+        <v>1347.5</v>
       </c>
     </row>
     <row r="81">
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="F81" t="n">
-        <v>1299</v>
+        <v>1296.5</v>
       </c>
       <c r="G81" t="n">
         <v>1349</v>
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="F82" t="n">
         <v>1300.5</v>
       </c>
       <c r="G82" t="n">
-        <v>1349</v>
+        <v>1347.5</v>
       </c>
     </row>
     <row r="83">
@@ -2989,7 +2989,7 @@
         <v>1399</v>
       </c>
       <c r="F83" t="n">
-        <v>1299</v>
+        <v>1296.5</v>
       </c>
       <c r="G83" t="n">
         <v>1347.5</v>
@@ -3017,13 +3017,13 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="F84" t="n">
         <v>1299</v>
       </c>
       <c r="G84" t="n">
-        <v>1351</v>
+        <v>1347.5</v>
       </c>
     </row>
     <row r="85">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="F86" t="n">
-        <v>1296.5</v>
+        <v>1299</v>
       </c>
       <c r="G86" t="n">
         <v>1349</v>
@@ -3116,7 +3116,7 @@
         <v>1299</v>
       </c>
       <c r="G87" t="n">
-        <v>1347.5</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="88">
@@ -3141,13 +3141,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="F88" t="n">
-        <v>1300.5</v>
+        <v>1299</v>
       </c>
       <c r="G88" t="n">
-        <v>1349</v>
+        <v>1347.5</v>
       </c>
     </row>
     <row r="89">
@@ -3172,13 +3172,13 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="F89" t="n">
         <v>1300.5</v>
       </c>
       <c r="G89" t="n">
-        <v>1349</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="90">
@@ -3206,10 +3206,10 @@
         <v>1399</v>
       </c>
       <c r="F90" t="n">
-        <v>1296.5</v>
+        <v>1300.5</v>
       </c>
       <c r="G90" t="n">
-        <v>1351</v>
+        <v>1347.5</v>
       </c>
     </row>
     <row r="91">
@@ -3234,7 +3234,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="F91" t="n">
         <v>1299</v>
@@ -3265,13 +3265,13 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F92" t="n">
         <v>499</v>
       </c>
       <c r="G92" t="n">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="93">
@@ -3299,10 +3299,10 @@
         <v>549</v>
       </c>
       <c r="F93" t="n">
-        <v>499</v>
+        <v>498.5</v>
       </c>
       <c r="G93" t="n">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="94">
@@ -3327,13 +3327,13 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F94" t="n">
-        <v>500.5</v>
+        <v>496.5</v>
       </c>
       <c r="G94" t="n">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="95">
@@ -3361,7 +3361,7 @@
         <v>549</v>
       </c>
       <c r="F95" t="n">
-        <v>499</v>
+        <v>500.5</v>
       </c>
       <c r="G95" t="n">
         <v>527.5</v>
@@ -3392,7 +3392,7 @@
         <v>549</v>
       </c>
       <c r="F96" t="n">
-        <v>500.5</v>
+        <v>499</v>
       </c>
       <c r="G96" t="n">
         <v>531</v>
@@ -3420,13 +3420,13 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F97" t="n">
-        <v>500.5</v>
+        <v>499</v>
       </c>
       <c r="G97" t="n">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="98">
@@ -3451,13 +3451,13 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F98" t="n">
-        <v>496.5</v>
+        <v>499</v>
       </c>
       <c r="G98" t="n">
-        <v>531</v>
+        <v>527.5</v>
       </c>
     </row>
     <row r="99">
@@ -3485,10 +3485,10 @@
         <v>549</v>
       </c>
       <c r="F99" t="n">
-        <v>500.5</v>
+        <v>499</v>
       </c>
       <c r="G99" t="n">
-        <v>529</v>
+        <v>527.5</v>
       </c>
     </row>
     <row r="100">
@@ -3516,10 +3516,10 @@
         <v>549</v>
       </c>
       <c r="F100" t="n">
-        <v>499</v>
+        <v>498.5</v>
       </c>
       <c r="G100" t="n">
-        <v>529</v>
+        <v>527.5</v>
       </c>
     </row>
     <row r="101">
@@ -3544,13 +3544,13 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F101" t="n">
         <v>498.5</v>
       </c>
       <c r="G101" t="n">
-        <v>527.5</v>
+        <v>529</v>
       </c>
     </row>
     <row r="102">
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F102" t="n">
-        <v>499</v>
+        <v>496.5</v>
       </c>
       <c r="G102" t="n">
         <v>527.5</v>
@@ -3609,10 +3609,10 @@
         <v>549</v>
       </c>
       <c r="F103" t="n">
-        <v>496.5</v>
+        <v>500.5</v>
       </c>
       <c r="G103" t="n">
-        <v>527.5</v>
+        <v>531</v>
       </c>
     </row>
     <row r="104">
@@ -3637,13 +3637,13 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F104" t="n">
-        <v>499</v>
+        <v>500.5</v>
       </c>
       <c r="G104" t="n">
-        <v>529</v>
+        <v>527.5</v>
       </c>
     </row>
     <row r="105">
@@ -3671,10 +3671,10 @@
         <v>549</v>
       </c>
       <c r="F105" t="n">
-        <v>496.5</v>
+        <v>500.5</v>
       </c>
       <c r="G105" t="n">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="106">
@@ -3699,10 +3699,10 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F106" t="n">
-        <v>500.5</v>
+        <v>499</v>
       </c>
       <c r="G106" t="n">
         <v>527.5</v>
@@ -3730,10 +3730,10 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="F107" t="n">
-        <v>498.5</v>
+        <v>500.5</v>
       </c>
       <c r="G107" t="n">
         <v>529</v>
@@ -3761,13 +3761,13 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F108" t="n">
         <v>499</v>
       </c>
       <c r="G108" t="n">
-        <v>531</v>
+        <v>527.5</v>
       </c>
     </row>
     <row r="109">
@@ -3795,10 +3795,10 @@
         <v>549</v>
       </c>
       <c r="F109" t="n">
-        <v>499</v>
+        <v>496.5</v>
       </c>
       <c r="G109" t="n">
-        <v>527.5</v>
+        <v>529</v>
       </c>
     </row>
     <row r="110">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F110" t="n">
         <v>498.5</v>
@@ -3854,13 +3854,13 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F111" t="n">
-        <v>500.5</v>
+        <v>498.5</v>
       </c>
       <c r="G111" t="n">
-        <v>529</v>
+        <v>527.5</v>
       </c>
     </row>
     <row r="112">
@@ -3888,10 +3888,10 @@
         <v>549</v>
       </c>
       <c r="F112" t="n">
-        <v>496.5</v>
+        <v>500.5</v>
       </c>
       <c r="G112" t="n">
-        <v>527.5</v>
+        <v>531</v>
       </c>
     </row>
     <row r="113">
@@ -3916,13 +3916,13 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F113" t="n">
-        <v>500.5</v>
+        <v>496.5</v>
       </c>
       <c r="G113" t="n">
-        <v>531</v>
+        <v>527.5</v>
       </c>
     </row>
     <row r="114">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F114" t="n">
-        <v>500.5</v>
+        <v>496.5</v>
       </c>
       <c r="G114" t="n">
         <v>529</v>
@@ -3978,13 +3978,13 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F115" t="n">
         <v>500.5</v>
       </c>
       <c r="G115" t="n">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="116">
@@ -4009,13 +4009,13 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F116" t="n">
-        <v>499</v>
+        <v>500.5</v>
       </c>
       <c r="G116" t="n">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="117">
@@ -4046,7 +4046,7 @@
         <v>499</v>
       </c>
       <c r="G117" t="n">
-        <v>527.5</v>
+        <v>529</v>
       </c>
     </row>
     <row r="118">
@@ -4071,13 +4071,13 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F118" t="n">
-        <v>496.5</v>
+        <v>499</v>
       </c>
       <c r="G118" t="n">
-        <v>527.5</v>
+        <v>529</v>
       </c>
     </row>
     <row r="119">
@@ -4105,7 +4105,7 @@
         <v>548</v>
       </c>
       <c r="F119" t="n">
-        <v>500.5</v>
+        <v>496.5</v>
       </c>
       <c r="G119" t="n">
         <v>527.5</v>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F120" t="n">
         <v>496.5</v>
@@ -4170,7 +4170,7 @@
         <v>499</v>
       </c>
       <c r="G121" t="n">
-        <v>529</v>
+        <v>527.5</v>
       </c>
     </row>
     <row r="122">
@@ -4198,10 +4198,10 @@
         <v>1299</v>
       </c>
       <c r="F122" t="n">
-        <v>1200.5</v>
+        <v>1199</v>
       </c>
       <c r="G122" t="n">
-        <v>1249</v>
+        <v>1247.5</v>
       </c>
     </row>
     <row r="123">
@@ -4229,10 +4229,10 @@
         <v>1299</v>
       </c>
       <c r="F123" t="n">
-        <v>1199</v>
+        <v>1198.5</v>
       </c>
       <c r="G123" t="n">
-        <v>1251</v>
+        <v>1247.5</v>
       </c>
     </row>
     <row r="124">
@@ -4260,10 +4260,10 @@
         <v>1299</v>
       </c>
       <c r="F124" t="n">
-        <v>1198.5</v>
+        <v>1200.5</v>
       </c>
       <c r="G124" t="n">
-        <v>1249</v>
+        <v>1247.5</v>
       </c>
     </row>
     <row r="125">
@@ -4291,7 +4291,7 @@
         <v>1299</v>
       </c>
       <c r="F125" t="n">
-        <v>1198.5</v>
+        <v>1196.5</v>
       </c>
       <c r="G125" t="n">
         <v>1249</v>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F126" t="n">
-        <v>1196.5</v>
+        <v>1198.5</v>
       </c>
       <c r="G126" t="n">
         <v>1247.5</v>
@@ -4353,10 +4353,10 @@
         <v>1299</v>
       </c>
       <c r="F127" t="n">
-        <v>1200.5</v>
+        <v>1199</v>
       </c>
       <c r="G127" t="n">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="128">
@@ -4381,10 +4381,10 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="F128" t="n">
-        <v>1199</v>
+        <v>1200.5</v>
       </c>
       <c r="G128" t="n">
         <v>1249</v>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F129" t="n">
-        <v>1199</v>
+        <v>1200.5</v>
       </c>
       <c r="G129" t="n">
-        <v>1247.5</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="130">
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="F130" t="n">
-        <v>1199</v>
+        <v>1198.5</v>
       </c>
       <c r="G130" t="n">
         <v>1247.5</v>
@@ -4474,13 +4474,13 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F131" t="n">
         <v>1198.5</v>
       </c>
       <c r="G131" t="n">
-        <v>1249</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="132">
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="F132" t="n">
         <v>1196.5</v>
       </c>
       <c r="G132" t="n">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="133">
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="F133" t="n">
-        <v>1198.5</v>
+        <v>1199</v>
       </c>
       <c r="G133" t="n">
-        <v>1249</v>
+        <v>1247.5</v>
       </c>
     </row>
     <row r="134">
@@ -4598,10 +4598,10 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="F135" t="n">
-        <v>1196.5</v>
+        <v>1198.5</v>
       </c>
       <c r="G135" t="n">
         <v>1249</v>
@@ -4632,10 +4632,10 @@
         <v>1299</v>
       </c>
       <c r="F136" t="n">
-        <v>1200.5</v>
+        <v>1199</v>
       </c>
       <c r="G136" t="n">
-        <v>1247.5</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="137">
@@ -4663,10 +4663,10 @@
         <v>1299</v>
       </c>
       <c r="F137" t="n">
-        <v>1200.5</v>
+        <v>1199</v>
       </c>
       <c r="G137" t="n">
-        <v>1249</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="138">
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="F138" t="n">
         <v>1199</v>
@@ -4722,13 +4722,13 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F139" t="n">
         <v>1199</v>
       </c>
       <c r="G139" t="n">
-        <v>1249</v>
+        <v>1247.5</v>
       </c>
     </row>
     <row r="140">
@@ -4756,7 +4756,7 @@
         <v>1299</v>
       </c>
       <c r="F140" t="n">
-        <v>1200.5</v>
+        <v>1198.5</v>
       </c>
       <c r="G140" t="n">
         <v>1249</v>
@@ -4784,10 +4784,10 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="F141" t="n">
-        <v>1199</v>
+        <v>1196.5</v>
       </c>
       <c r="G141" t="n">
         <v>1249</v>
@@ -4815,13 +4815,13 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="F142" t="n">
-        <v>1199</v>
+        <v>1198.5</v>
       </c>
       <c r="G142" t="n">
-        <v>1247.5</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="143">
@@ -4846,13 +4846,13 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="F143" t="n">
         <v>1199</v>
       </c>
       <c r="G143" t="n">
-        <v>1249</v>
+        <v>1247.5</v>
       </c>
     </row>
     <row r="144">
@@ -4883,7 +4883,7 @@
         <v>1199</v>
       </c>
       <c r="G144" t="n">
-        <v>1249</v>
+        <v>1247.5</v>
       </c>
     </row>
     <row r="145">
@@ -4914,7 +4914,7 @@
         <v>1199</v>
       </c>
       <c r="G145" t="n">
-        <v>1251</v>
+        <v>1247.5</v>
       </c>
     </row>
     <row r="146">
@@ -4945,7 +4945,7 @@
         <v>1199</v>
       </c>
       <c r="G146" t="n">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="147">
@@ -4973,7 +4973,7 @@
         <v>1299</v>
       </c>
       <c r="F147" t="n">
-        <v>1198.5</v>
+        <v>1200.5</v>
       </c>
       <c r="G147" t="n">
         <v>1249</v>
@@ -5001,13 +5001,13 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="F148" t="n">
-        <v>1198.5</v>
+        <v>1196.5</v>
       </c>
       <c r="G148" t="n">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="149">
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="F149" t="n">
-        <v>1199</v>
+        <v>1198.5</v>
       </c>
       <c r="G149" t="n">
-        <v>1249</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="150">
@@ -5066,10 +5066,10 @@
         <v>1299</v>
       </c>
       <c r="F150" t="n">
-        <v>1196.5</v>
+        <v>1199</v>
       </c>
       <c r="G150" t="n">
-        <v>1247.5</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="151">
@@ -5094,13 +5094,13 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F151" t="n">
-        <v>1198.5</v>
+        <v>1199</v>
       </c>
       <c r="G151" t="n">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="152">
@@ -5128,10 +5128,10 @@
         <v>1219.99</v>
       </c>
       <c r="F152" t="n">
-        <v>1151.49</v>
+        <v>1149.99</v>
       </c>
       <c r="G152" t="n">
-        <v>1179.99</v>
+        <v>1181.99</v>
       </c>
     </row>
     <row r="153">
@@ -5190,10 +5190,10 @@
         <v>1219.99</v>
       </c>
       <c r="F154" t="n">
-        <v>1149.49</v>
+        <v>1147.49</v>
       </c>
       <c r="G154" t="n">
-        <v>1181.99</v>
+        <v>1178.49</v>
       </c>
     </row>
     <row r="155">
@@ -5224,7 +5224,7 @@
         <v>1149.99</v>
       </c>
       <c r="G155" t="n">
-        <v>1181.99</v>
+        <v>1178.49</v>
       </c>
     </row>
     <row r="156">
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1220.99</v>
+        <v>1219.99</v>
       </c>
       <c r="F156" t="n">
         <v>1149.49</v>
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1219.99</v>
+        <v>1218.99</v>
       </c>
       <c r="F157" t="n">
-        <v>1149.49</v>
+        <v>1149.99</v>
       </c>
       <c r="G157" t="n">
         <v>1181.99</v>
@@ -5314,10 +5314,10 @@
         <v>1219.99</v>
       </c>
       <c r="F158" t="n">
-        <v>1151.49</v>
+        <v>1149.99</v>
       </c>
       <c r="G158" t="n">
-        <v>1181.99</v>
+        <v>1178.49</v>
       </c>
     </row>
     <row r="159">
@@ -5342,10 +5342,10 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1218.99</v>
+        <v>1219.99</v>
       </c>
       <c r="F159" t="n">
-        <v>1149.99</v>
+        <v>1151.49</v>
       </c>
       <c r="G159" t="n">
         <v>1178.49</v>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1218.99</v>
+        <v>1219.99</v>
       </c>
       <c r="F160" t="n">
-        <v>1147.49</v>
+        <v>1149.99</v>
       </c>
       <c r="G160" t="n">
         <v>1179.99</v>
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1220.99</v>
+        <v>1219.99</v>
       </c>
       <c r="F161" t="n">
-        <v>1147.49</v>
+        <v>1149.99</v>
       </c>
       <c r="G161" t="n">
         <v>1179.99</v>
@@ -5435,10 +5435,10 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1219.99</v>
+        <v>1220.99</v>
       </c>
       <c r="F162" t="n">
-        <v>1149.99</v>
+        <v>1151.49</v>
       </c>
       <c r="G162" t="n">
         <v>1178.49</v>
@@ -5469,7 +5469,7 @@
         <v>1219.99</v>
       </c>
       <c r="F163" t="n">
-        <v>1149.99</v>
+        <v>1151.49</v>
       </c>
       <c r="G163" t="n">
         <v>1179.99</v>
@@ -5497,13 +5497,13 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1220.99</v>
+        <v>1219.99</v>
       </c>
       <c r="F164" t="n">
         <v>1151.49</v>
       </c>
       <c r="G164" t="n">
-        <v>1178.49</v>
+        <v>1179.99</v>
       </c>
     </row>
     <row r="165">
@@ -5534,7 +5534,7 @@
         <v>1149.99</v>
       </c>
       <c r="G165" t="n">
-        <v>1179.99</v>
+        <v>1181.99</v>
       </c>
     </row>
     <row r="166">
@@ -5559,13 +5559,13 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1219.99</v>
+        <v>1218.99</v>
       </c>
       <c r="F166" t="n">
-        <v>1149.99</v>
+        <v>1151.49</v>
       </c>
       <c r="G166" t="n">
-        <v>1178.49</v>
+        <v>1181.99</v>
       </c>
     </row>
     <row r="167">
@@ -5596,7 +5596,7 @@
         <v>1151.49</v>
       </c>
       <c r="G167" t="n">
-        <v>1181.99</v>
+        <v>1178.49</v>
       </c>
     </row>
     <row r="168">
@@ -5624,7 +5624,7 @@
         <v>1219.99</v>
       </c>
       <c r="F168" t="n">
-        <v>1149.49</v>
+        <v>1149.99</v>
       </c>
       <c r="G168" t="n">
         <v>1181.99</v>
@@ -5655,7 +5655,7 @@
         <v>1219.99</v>
       </c>
       <c r="F169" t="n">
-        <v>1149.49</v>
+        <v>1147.49</v>
       </c>
       <c r="G169" t="n">
         <v>1179.99</v>
@@ -5683,13 +5683,13 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1218.99</v>
+        <v>1219.99</v>
       </c>
       <c r="F170" t="n">
-        <v>1149.99</v>
+        <v>1151.49</v>
       </c>
       <c r="G170" t="n">
-        <v>1181.99</v>
+        <v>1178.49</v>
       </c>
     </row>
     <row r="171">
@@ -5714,13 +5714,13 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1219.99</v>
+        <v>1218.99</v>
       </c>
       <c r="F171" t="n">
-        <v>1151.49</v>
+        <v>1149.99</v>
       </c>
       <c r="G171" t="n">
-        <v>1181.99</v>
+        <v>1179.99</v>
       </c>
     </row>
     <row r="172">
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1219.99</v>
+        <v>1220.99</v>
       </c>
       <c r="F172" t="n">
         <v>1149.99</v>
@@ -5810,7 +5810,7 @@
         <v>1219.99</v>
       </c>
       <c r="F174" t="n">
-        <v>1147.49</v>
+        <v>1151.49</v>
       </c>
       <c r="G174" t="n">
         <v>1179.99</v>
@@ -5838,13 +5838,13 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1220.99</v>
+        <v>1218.99</v>
       </c>
       <c r="F175" t="n">
-        <v>1149.49</v>
+        <v>1149.99</v>
       </c>
       <c r="G175" t="n">
-        <v>1178.49</v>
+        <v>1181.99</v>
       </c>
     </row>
     <row r="176">
@@ -5869,13 +5869,13 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1219.99</v>
+        <v>1220.99</v>
       </c>
       <c r="F176" t="n">
-        <v>1149.49</v>
+        <v>1149.99</v>
       </c>
       <c r="G176" t="n">
-        <v>1179.99</v>
+        <v>1181.99</v>
       </c>
     </row>
     <row r="177">
@@ -5903,10 +5903,10 @@
         <v>1220.99</v>
       </c>
       <c r="F177" t="n">
-        <v>1147.49</v>
+        <v>1151.49</v>
       </c>
       <c r="G177" t="n">
-        <v>1179.99</v>
+        <v>1181.99</v>
       </c>
     </row>
     <row r="178">
@@ -5934,10 +5934,10 @@
         <v>1220.99</v>
       </c>
       <c r="F178" t="n">
-        <v>1149.99</v>
+        <v>1151.49</v>
       </c>
       <c r="G178" t="n">
-        <v>1178.49</v>
+        <v>1181.99</v>
       </c>
     </row>
     <row r="179">
@@ -5962,13 +5962,13 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1219.99</v>
+        <v>1220.99</v>
       </c>
       <c r="F179" t="n">
         <v>1149.99</v>
       </c>
       <c r="G179" t="n">
-        <v>1179.99</v>
+        <v>1178.49</v>
       </c>
     </row>
     <row r="180">
@@ -6024,13 +6024,13 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1219.99</v>
+        <v>1220.99</v>
       </c>
       <c r="F181" t="n">
-        <v>1149.99</v>
+        <v>1151.49</v>
       </c>
       <c r="G181" t="n">
-        <v>1181.99</v>
+        <v>1179.99</v>
       </c>
     </row>
     <row r="182">
@@ -6055,13 +6055,13 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1698.99</v>
+        <v>1799.99</v>
       </c>
       <c r="F182" t="n">
-        <v>1599.99</v>
+        <v>1730.5</v>
       </c>
       <c r="G182" t="n">
-        <v>1649.99</v>
+        <v>1751.99</v>
       </c>
     </row>
     <row r="183">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1699.99</v>
+        <v>1799.99</v>
       </c>
       <c r="F183" t="n">
-        <v>1599.99</v>
+        <v>1729</v>
       </c>
       <c r="G183" t="n">
-        <v>1648.49</v>
+        <v>1749.99</v>
       </c>
     </row>
     <row r="184">
@@ -6117,13 +6117,13 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1699.99</v>
+        <v>1799.99</v>
       </c>
       <c r="F184" t="n">
-        <v>1599.99</v>
+        <v>1726.5</v>
       </c>
       <c r="G184" t="n">
-        <v>1651.99</v>
+        <v>1751.99</v>
       </c>
     </row>
     <row r="185">
@@ -6148,13 +6148,13 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1698.99</v>
+        <v>1799.99</v>
       </c>
       <c r="F185" t="n">
-        <v>1597.49</v>
+        <v>1729</v>
       </c>
       <c r="G185" t="n">
-        <v>1648.49</v>
+        <v>1749.99</v>
       </c>
     </row>
     <row r="186">
@@ -6179,13 +6179,13 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1698.99</v>
+        <v>1800.99</v>
       </c>
       <c r="F186" t="n">
-        <v>1597.49</v>
+        <v>1730.5</v>
       </c>
       <c r="G186" t="n">
-        <v>1648.49</v>
+        <v>1751.99</v>
       </c>
     </row>
     <row r="187">
@@ -6210,13 +6210,13 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1698.99</v>
+        <v>1799.99</v>
       </c>
       <c r="F187" t="n">
-        <v>1599.49</v>
+        <v>1728.5</v>
       </c>
       <c r="G187" t="n">
-        <v>1651.99</v>
+        <v>1749.99</v>
       </c>
     </row>
     <row r="188">
@@ -6241,13 +6241,13 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1699.99</v>
+        <v>1799.99</v>
       </c>
       <c r="F188" t="n">
-        <v>1599.99</v>
+        <v>1730.5</v>
       </c>
       <c r="G188" t="n">
-        <v>1648.49</v>
+        <v>1749.99</v>
       </c>
     </row>
     <row r="189">
@@ -6272,13 +6272,13 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1698.99</v>
+        <v>1798.99</v>
       </c>
       <c r="F189" t="n">
-        <v>1599.49</v>
+        <v>1729</v>
       </c>
       <c r="G189" t="n">
-        <v>1649.99</v>
+        <v>1749.99</v>
       </c>
     </row>
     <row r="190">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1699.99</v>
+        <v>1800.99</v>
       </c>
       <c r="F190" t="n">
-        <v>1601.49</v>
+        <v>1729</v>
       </c>
       <c r="G190" t="n">
-        <v>1651.99</v>
+        <v>1751.99</v>
       </c>
     </row>
     <row r="191">
@@ -6334,13 +6334,13 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1699.99</v>
+        <v>1798.99</v>
       </c>
       <c r="F191" t="n">
-        <v>1599.99</v>
+        <v>1730.5</v>
       </c>
       <c r="G191" t="n">
-        <v>1649.99</v>
+        <v>1749.99</v>
       </c>
     </row>
     <row r="192">
@@ -6365,13 +6365,13 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1699.99</v>
+        <v>1799.99</v>
       </c>
       <c r="F192" t="n">
-        <v>1601.49</v>
+        <v>1730.5</v>
       </c>
       <c r="G192" t="n">
-        <v>1648.49</v>
+        <v>1748.49</v>
       </c>
     </row>
     <row r="193">
@@ -6396,13 +6396,13 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1698.99</v>
+        <v>1799.99</v>
       </c>
       <c r="F193" t="n">
-        <v>1599.49</v>
+        <v>1730.5</v>
       </c>
       <c r="G193" t="n">
-        <v>1648.49</v>
+        <v>1749.99</v>
       </c>
     </row>
     <row r="194">
@@ -6427,13 +6427,13 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1698.99</v>
+        <v>1798.99</v>
       </c>
       <c r="F194" t="n">
-        <v>1601.49</v>
+        <v>1728.5</v>
       </c>
       <c r="G194" t="n">
-        <v>1649.99</v>
+        <v>1749.99</v>
       </c>
     </row>
     <row r="195">
@@ -6458,13 +6458,13 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1699.99</v>
+        <v>1799.99</v>
       </c>
       <c r="F195" t="n">
-        <v>1599.49</v>
+        <v>1728.5</v>
       </c>
       <c r="G195" t="n">
-        <v>1648.49</v>
+        <v>1749.99</v>
       </c>
     </row>
     <row r="196">
@@ -6489,13 +6489,13 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1698.99</v>
+        <v>1800.99</v>
       </c>
       <c r="F196" t="n">
-        <v>1599.99</v>
+        <v>1726.5</v>
       </c>
       <c r="G196" t="n">
-        <v>1649.99</v>
+        <v>1748.49</v>
       </c>
     </row>
     <row r="197">
@@ -6520,13 +6520,13 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1700.99</v>
+        <v>1800.99</v>
       </c>
       <c r="F197" t="n">
-        <v>1599.99</v>
+        <v>1726.5</v>
       </c>
       <c r="G197" t="n">
-        <v>1651.99</v>
+        <v>1748.49</v>
       </c>
     </row>
     <row r="198">
@@ -6551,13 +6551,13 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1699.99</v>
+        <v>1799.99</v>
       </c>
       <c r="F198" t="n">
-        <v>1599.99</v>
+        <v>1726.5</v>
       </c>
       <c r="G198" t="n">
-        <v>1648.49</v>
+        <v>1748.49</v>
       </c>
     </row>
     <row r="199">
@@ -6582,13 +6582,13 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1700.99</v>
+        <v>1799.99</v>
       </c>
       <c r="F199" t="n">
-        <v>1599.99</v>
+        <v>1730.5</v>
       </c>
       <c r="G199" t="n">
-        <v>1651.99</v>
+        <v>1749.99</v>
       </c>
     </row>
     <row r="200">
@@ -6613,13 +6613,13 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1699.99</v>
+        <v>1800.99</v>
       </c>
       <c r="F200" t="n">
-        <v>1601.49</v>
+        <v>1728.5</v>
       </c>
       <c r="G200" t="n">
-        <v>1651.99</v>
+        <v>1751.99</v>
       </c>
     </row>
     <row r="201">
@@ -6644,13 +6644,13 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>1700.99</v>
+        <v>1799.99</v>
       </c>
       <c r="F201" t="n">
-        <v>1597.49</v>
+        <v>1730.5</v>
       </c>
       <c r="G201" t="n">
-        <v>1651.99</v>
+        <v>1749.99</v>
       </c>
     </row>
     <row r="202">
@@ -6675,13 +6675,13 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1700.99</v>
+        <v>1800.99</v>
       </c>
       <c r="F202" t="n">
-        <v>1599.99</v>
+        <v>1729</v>
       </c>
       <c r="G202" t="n">
-        <v>1651.99</v>
+        <v>1749.99</v>
       </c>
     </row>
     <row r="203">
@@ -6706,13 +6706,13 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>1698.99</v>
+        <v>1798.99</v>
       </c>
       <c r="F203" t="n">
-        <v>1599.99</v>
+        <v>1729</v>
       </c>
       <c r="G203" t="n">
-        <v>1651.99</v>
+        <v>1748.49</v>
       </c>
     </row>
     <row r="204">
@@ -6737,13 +6737,13 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1699.99</v>
+        <v>1799.99</v>
       </c>
       <c r="F204" t="n">
-        <v>1599.99</v>
+        <v>1730.5</v>
       </c>
       <c r="G204" t="n">
-        <v>1648.49</v>
+        <v>1749.99</v>
       </c>
     </row>
     <row r="205">
@@ -6768,13 +6768,13 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1699.99</v>
+        <v>1798.99</v>
       </c>
       <c r="F205" t="n">
-        <v>1599.99</v>
+        <v>1729</v>
       </c>
       <c r="G205" t="n">
-        <v>1649.99</v>
+        <v>1751.99</v>
       </c>
     </row>
     <row r="206">
@@ -6799,13 +6799,13 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1698.99</v>
+        <v>1798.99</v>
       </c>
       <c r="F206" t="n">
-        <v>1597.49</v>
+        <v>1729</v>
       </c>
       <c r="G206" t="n">
-        <v>1649.99</v>
+        <v>1751.99</v>
       </c>
     </row>
     <row r="207">
@@ -6830,13 +6830,13 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>1699.99</v>
+        <v>1798.99</v>
       </c>
       <c r="F207" t="n">
-        <v>1599.99</v>
+        <v>1728.5</v>
       </c>
       <c r="G207" t="n">
-        <v>1651.99</v>
+        <v>1749.99</v>
       </c>
     </row>
     <row r="208">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1698.99</v>
+        <v>1799.99</v>
       </c>
       <c r="F208" t="n">
-        <v>1599.99</v>
+        <v>1730.5</v>
       </c>
       <c r="G208" t="n">
-        <v>1648.49</v>
+        <v>1749.99</v>
       </c>
     </row>
     <row r="209">
@@ -6892,13 +6892,13 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>1698.99</v>
+        <v>1799.99</v>
       </c>
       <c r="F209" t="n">
-        <v>1599.49</v>
+        <v>1729</v>
       </c>
       <c r="G209" t="n">
-        <v>1648.49</v>
+        <v>1751.99</v>
       </c>
     </row>
     <row r="210">
@@ -6923,13 +6923,13 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1698.99</v>
+        <v>1800.99</v>
       </c>
       <c r="F210" t="n">
-        <v>1597.49</v>
+        <v>1730.5</v>
       </c>
       <c r="G210" t="n">
-        <v>1649.99</v>
+        <v>1751.99</v>
       </c>
     </row>
     <row r="211">
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>1699.99</v>
+        <v>1798.99</v>
       </c>
       <c r="F211" t="n">
-        <v>1599.99</v>
+        <v>1728.5</v>
       </c>
       <c r="G211" t="n">
-        <v>1649.99</v>
+        <v>1749.99</v>
       </c>
     </row>
     <row r="212">
@@ -6988,10 +6988,10 @@
         <v>649.99</v>
       </c>
       <c r="F212" t="n">
-        <v>549.99</v>
+        <v>547.49</v>
       </c>
       <c r="G212" t="n">
-        <v>598.49</v>
+        <v>601.99</v>
       </c>
     </row>
     <row r="213">
@@ -7016,13 +7016,13 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>648.99</v>
+        <v>650.99</v>
       </c>
       <c r="F213" t="n">
-        <v>549.49</v>
+        <v>547.49</v>
       </c>
       <c r="G213" t="n">
-        <v>598.49</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="214">
@@ -7047,13 +7047,13 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>650.99</v>
+        <v>649.99</v>
       </c>
       <c r="F214" t="n">
-        <v>549.49</v>
+        <v>549.99</v>
       </c>
       <c r="G214" t="n">
-        <v>598.49</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="215">
@@ -7078,13 +7078,13 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>650.99</v>
+        <v>648.99</v>
       </c>
       <c r="F215" t="n">
         <v>547.49</v>
       </c>
       <c r="G215" t="n">
-        <v>601.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="216">
@@ -7109,10 +7109,10 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>649.99</v>
+        <v>648.99</v>
       </c>
       <c r="F216" t="n">
-        <v>551.49</v>
+        <v>547.49</v>
       </c>
       <c r="G216" t="n">
         <v>601.99</v>
@@ -7146,7 +7146,7 @@
         <v>549.99</v>
       </c>
       <c r="G217" t="n">
-        <v>599.99</v>
+        <v>601.99</v>
       </c>
     </row>
     <row r="218">
@@ -7171,13 +7171,13 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>648.99</v>
+        <v>649.99</v>
       </c>
       <c r="F218" t="n">
         <v>549.99</v>
       </c>
       <c r="G218" t="n">
-        <v>598.49</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="219">
@@ -7202,10 +7202,10 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>650.99</v>
+        <v>649.99</v>
       </c>
       <c r="F219" t="n">
-        <v>551.49</v>
+        <v>549.49</v>
       </c>
       <c r="G219" t="n">
         <v>599.99</v>
@@ -7233,13 +7233,13 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>649.99</v>
+        <v>648.99</v>
       </c>
       <c r="F220" t="n">
-        <v>547.49</v>
+        <v>549.99</v>
       </c>
       <c r="G220" t="n">
-        <v>598.49</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="221">
@@ -7264,7 +7264,7 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>650.99</v>
+        <v>649.99</v>
       </c>
       <c r="F221" t="n">
         <v>547.49</v>
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>648.99</v>
+        <v>650.99</v>
       </c>
       <c r="F222" t="n">
-        <v>549.99</v>
+        <v>549.49</v>
       </c>
       <c r="G222" t="n">
         <v>599.99</v>
@@ -7326,13 +7326,13 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>649.99</v>
+        <v>650.99</v>
       </c>
       <c r="F223" t="n">
         <v>549.99</v>
       </c>
       <c r="G223" t="n">
-        <v>598.49</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="224">
@@ -7391,7 +7391,7 @@
         <v>648.99</v>
       </c>
       <c r="F225" t="n">
-        <v>547.49</v>
+        <v>549.99</v>
       </c>
       <c r="G225" t="n">
         <v>599.99</v>
@@ -7419,13 +7419,13 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>648.99</v>
+        <v>649.99</v>
       </c>
       <c r="F226" t="n">
-        <v>547.49</v>
+        <v>551.49</v>
       </c>
       <c r="G226" t="n">
-        <v>601.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="227">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>650.99</v>
+        <v>648.99</v>
       </c>
       <c r="F228" t="n">
-        <v>547.49</v>
+        <v>549.99</v>
       </c>
       <c r="G228" t="n">
-        <v>601.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="229">
@@ -7512,13 +7512,13 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>650.99</v>
+        <v>649.99</v>
       </c>
       <c r="F229" t="n">
         <v>551.49</v>
       </c>
       <c r="G229" t="n">
-        <v>601.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="230">
@@ -7574,7 +7574,7 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>649.99</v>
+        <v>650.99</v>
       </c>
       <c r="F231" t="n">
         <v>551.49</v>
@@ -7605,13 +7605,13 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>650.99</v>
+        <v>649.99</v>
       </c>
       <c r="F232" t="n">
         <v>549.99</v>
       </c>
       <c r="G232" t="n">
-        <v>599.99</v>
+        <v>601.99</v>
       </c>
     </row>
     <row r="233">
@@ -7642,7 +7642,7 @@
         <v>549.99</v>
       </c>
       <c r="G233" t="n">
-        <v>599.99</v>
+        <v>598.49</v>
       </c>
     </row>
     <row r="234">
@@ -7670,10 +7670,10 @@
         <v>649.99</v>
       </c>
       <c r="F234" t="n">
-        <v>551.49</v>
+        <v>549.49</v>
       </c>
       <c r="G234" t="n">
-        <v>598.49</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="235">
@@ -7701,7 +7701,7 @@
         <v>648.99</v>
       </c>
       <c r="F235" t="n">
-        <v>549.99</v>
+        <v>549.49</v>
       </c>
       <c r="G235" t="n">
         <v>599.99</v>
@@ -7732,7 +7732,7 @@
         <v>649.99</v>
       </c>
       <c r="F236" t="n">
-        <v>549.99</v>
+        <v>551.49</v>
       </c>
       <c r="G236" t="n">
         <v>599.99</v>
@@ -7791,13 +7791,13 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>649.99</v>
+        <v>650.99</v>
       </c>
       <c r="F238" t="n">
-        <v>549.49</v>
+        <v>549.99</v>
       </c>
       <c r="G238" t="n">
-        <v>599.99</v>
+        <v>598.49</v>
       </c>
     </row>
     <row r="239">
@@ -7822,10 +7822,10 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>649.99</v>
+        <v>648.99</v>
       </c>
       <c r="F239" t="n">
-        <v>549.49</v>
+        <v>549.99</v>
       </c>
       <c r="G239" t="n">
         <v>601.99</v>
@@ -7853,13 +7853,13 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>649.99</v>
+        <v>650.99</v>
       </c>
       <c r="F240" t="n">
-        <v>549.99</v>
+        <v>549.49</v>
       </c>
       <c r="G240" t="n">
-        <v>599.99</v>
+        <v>598.49</v>
       </c>
     </row>
     <row r="241">
@@ -7884,13 +7884,13 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>650.99</v>
+        <v>649.99</v>
       </c>
       <c r="F241" t="n">
-        <v>551.49</v>
+        <v>547.49</v>
       </c>
       <c r="G241" t="n">
-        <v>598.49</v>
+        <v>601.99</v>
       </c>
     </row>
     <row r="242">
@@ -7915,13 +7915,13 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>378.99</v>
+        <v>379.99</v>
       </c>
       <c r="F242" t="n">
-        <v>327.5</v>
+        <v>329.5</v>
       </c>
       <c r="G242" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="243">
@@ -7946,10 +7946,10 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>380.99</v>
+        <v>379.99</v>
       </c>
       <c r="F243" t="n">
-        <v>328</v>
+        <v>325.5</v>
       </c>
       <c r="G243" t="n">
         <v>346.5</v>
@@ -7977,10 +7977,10 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>378.99</v>
+        <v>380.99</v>
       </c>
       <c r="F244" t="n">
-        <v>327.5</v>
+        <v>328</v>
       </c>
       <c r="G244" t="n">
         <v>348</v>
@@ -8008,13 +8008,13 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>379.99</v>
+        <v>378.99</v>
       </c>
       <c r="F245" t="n">
-        <v>329.5</v>
+        <v>328</v>
       </c>
       <c r="G245" t="n">
-        <v>350</v>
+        <v>346.5</v>
       </c>
     </row>
     <row r="246">
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>380.99</v>
+        <v>379.99</v>
       </c>
       <c r="F246" t="n">
-        <v>328</v>
+        <v>329.5</v>
       </c>
       <c r="G246" t="n">
         <v>348</v>
@@ -8070,10 +8070,10 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>380.99</v>
+        <v>378.99</v>
       </c>
       <c r="F247" t="n">
-        <v>328</v>
+        <v>327.5</v>
       </c>
       <c r="G247" t="n">
         <v>348</v>
@@ -8101,13 +8101,13 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>378.99</v>
+        <v>379.99</v>
       </c>
       <c r="F248" t="n">
-        <v>325.5</v>
+        <v>328</v>
       </c>
       <c r="G248" t="n">
-        <v>346.5</v>
+        <v>348</v>
       </c>
     </row>
     <row r="249">
@@ -8132,7 +8132,7 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>380.99</v>
+        <v>379.99</v>
       </c>
       <c r="F249" t="n">
         <v>325.5</v>
@@ -8166,7 +8166,7 @@
         <v>379.99</v>
       </c>
       <c r="F250" t="n">
-        <v>327.5</v>
+        <v>328</v>
       </c>
       <c r="G250" t="n">
         <v>346.5</v>
@@ -8194,10 +8194,10 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>379.99</v>
+        <v>378.99</v>
       </c>
       <c r="F251" t="n">
-        <v>325.5</v>
+        <v>327.5</v>
       </c>
       <c r="G251" t="n">
         <v>348</v>
@@ -8225,13 +8225,13 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>379.99</v>
+        <v>378.99</v>
       </c>
       <c r="F252" t="n">
-        <v>329.5</v>
+        <v>327.5</v>
       </c>
       <c r="G252" t="n">
-        <v>346.5</v>
+        <v>350</v>
       </c>
     </row>
     <row r="253">
@@ -8259,7 +8259,7 @@
         <v>379.99</v>
       </c>
       <c r="F253" t="n">
-        <v>328</v>
+        <v>327.5</v>
       </c>
       <c r="G253" t="n">
         <v>348</v>
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>380.99</v>
+        <v>379.99</v>
       </c>
       <c r="F254" t="n">
-        <v>327.5</v>
+        <v>325.5</v>
       </c>
       <c r="G254" t="n">
-        <v>346.5</v>
+        <v>348</v>
       </c>
     </row>
     <row r="255">
@@ -8318,13 +8318,13 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>378.99</v>
+        <v>379.99</v>
       </c>
       <c r="F255" t="n">
-        <v>328</v>
+        <v>327.5</v>
       </c>
       <c r="G255" t="n">
-        <v>346.5</v>
+        <v>350</v>
       </c>
     </row>
     <row r="256">
@@ -8349,10 +8349,10 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>379.99</v>
+        <v>380.99</v>
       </c>
       <c r="F256" t="n">
-        <v>327.5</v>
+        <v>329.5</v>
       </c>
       <c r="G256" t="n">
         <v>348</v>
@@ -8380,10 +8380,10 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>379.99</v>
+        <v>380.99</v>
       </c>
       <c r="F257" t="n">
-        <v>328</v>
+        <v>329.5</v>
       </c>
       <c r="G257" t="n">
         <v>348</v>
@@ -8414,7 +8414,7 @@
         <v>379.99</v>
       </c>
       <c r="F258" t="n">
-        <v>328</v>
+        <v>327.5</v>
       </c>
       <c r="G258" t="n">
         <v>348</v>
@@ -8445,7 +8445,7 @@
         <v>378.99</v>
       </c>
       <c r="F259" t="n">
-        <v>325.5</v>
+        <v>327.5</v>
       </c>
       <c r="G259" t="n">
         <v>350</v>
@@ -8473,13 +8473,13 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>378.99</v>
+        <v>379.99</v>
       </c>
       <c r="F260" t="n">
-        <v>325.5</v>
+        <v>329.5</v>
       </c>
       <c r="G260" t="n">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="261">
@@ -8510,7 +8510,7 @@
         <v>328</v>
       </c>
       <c r="G261" t="n">
-        <v>346.5</v>
+        <v>350</v>
       </c>
     </row>
     <row r="262">
@@ -8538,10 +8538,10 @@
         <v>379.99</v>
       </c>
       <c r="F262" t="n">
-        <v>329.5</v>
+        <v>328</v>
       </c>
       <c r="G262" t="n">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="263">
@@ -8566,13 +8566,13 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>380.99</v>
+        <v>379.99</v>
       </c>
       <c r="F263" t="n">
-        <v>328</v>
+        <v>327.5</v>
       </c>
       <c r="G263" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="264">
@@ -8600,10 +8600,10 @@
         <v>379.99</v>
       </c>
       <c r="F264" t="n">
-        <v>327.5</v>
+        <v>328</v>
       </c>
       <c r="G264" t="n">
-        <v>348</v>
+        <v>346.5</v>
       </c>
     </row>
     <row r="265">
@@ -8628,10 +8628,10 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>378.99</v>
+        <v>380.99</v>
       </c>
       <c r="F265" t="n">
-        <v>325.5</v>
+        <v>328</v>
       </c>
       <c r="G265" t="n">
         <v>348</v>
@@ -8659,13 +8659,13 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>378.99</v>
+        <v>379.99</v>
       </c>
       <c r="F266" t="n">
-        <v>329.5</v>
+        <v>325.5</v>
       </c>
       <c r="G266" t="n">
-        <v>346.5</v>
+        <v>350</v>
       </c>
     </row>
     <row r="267">
@@ -8690,13 +8690,13 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>379.99</v>
+        <v>380.99</v>
       </c>
       <c r="F267" t="n">
-        <v>325.5</v>
+        <v>328</v>
       </c>
       <c r="G267" t="n">
-        <v>348</v>
+        <v>346.5</v>
       </c>
     </row>
     <row r="268">
@@ -8721,13 +8721,13 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>380.99</v>
+        <v>379.99</v>
       </c>
       <c r="F268" t="n">
-        <v>329.5</v>
+        <v>325.5</v>
       </c>
       <c r="G268" t="n">
-        <v>346.5</v>
+        <v>350</v>
       </c>
     </row>
     <row r="269">
@@ -8755,10 +8755,10 @@
         <v>379.99</v>
       </c>
       <c r="F269" t="n">
-        <v>329.5</v>
+        <v>328</v>
       </c>
       <c r="G269" t="n">
-        <v>346.5</v>
+        <v>348</v>
       </c>
     </row>
     <row r="270">
@@ -8783,10 +8783,10 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>380.99</v>
+        <v>378.99</v>
       </c>
       <c r="F270" t="n">
-        <v>327.5</v>
+        <v>328</v>
       </c>
       <c r="G270" t="n">
         <v>348</v>
@@ -8814,7 +8814,7 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>379.99</v>
+        <v>378.99</v>
       </c>
       <c r="F271" t="n">
         <v>328</v>
@@ -8848,10 +8848,10 @@
         <v>699.99</v>
       </c>
       <c r="F272" t="n">
+        <v>701.49</v>
+      </c>
+      <c r="G272" t="n">
         <v>699.99</v>
-      </c>
-      <c r="G272" t="n">
-        <v>701.99</v>
       </c>
     </row>
     <row r="273">
@@ -8879,10 +8879,10 @@
         <v>699.99</v>
       </c>
       <c r="F273" t="n">
-        <v>699.99</v>
+        <v>697.49</v>
       </c>
       <c r="G273" t="n">
-        <v>701.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="274">
@@ -8907,10 +8907,10 @@
         </is>
       </c>
       <c r="E274" t="n">
+        <v>700.99</v>
+      </c>
+      <c r="F274" t="n">
         <v>699.99</v>
-      </c>
-      <c r="F274" t="n">
-        <v>697.49</v>
       </c>
       <c r="G274" t="n">
         <v>698.49</v>
@@ -8938,13 +8938,13 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>698.99</v>
+        <v>699.99</v>
       </c>
       <c r="F275" t="n">
         <v>699.49</v>
       </c>
       <c r="G275" t="n">
-        <v>699.99</v>
+        <v>701.99</v>
       </c>
     </row>
     <row r="276">
@@ -8969,13 +8969,13 @@
         </is>
       </c>
       <c r="E276" t="n">
+        <v>698.99</v>
+      </c>
+      <c r="F276" t="n">
         <v>699.99</v>
       </c>
-      <c r="F276" t="n">
-        <v>697.49</v>
-      </c>
       <c r="G276" t="n">
-        <v>701.99</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="277">
@@ -9000,13 +9000,13 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>699.99</v>
+        <v>700.99</v>
       </c>
       <c r="F277" t="n">
         <v>697.49</v>
       </c>
       <c r="G277" t="n">
-        <v>701.99</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="278">
@@ -9034,7 +9034,7 @@
         <v>699.99</v>
       </c>
       <c r="F278" t="n">
-        <v>699.49</v>
+        <v>697.49</v>
       </c>
       <c r="G278" t="n">
         <v>699.99</v>
@@ -9062,10 +9062,10 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>699.99</v>
+        <v>700.99</v>
       </c>
       <c r="F279" t="n">
-        <v>699.99</v>
+        <v>699.49</v>
       </c>
       <c r="G279" t="n">
         <v>699.99</v>
@@ -9093,10 +9093,10 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>700.99</v>
+        <v>699.99</v>
       </c>
       <c r="F280" t="n">
-        <v>701.49</v>
+        <v>699.49</v>
       </c>
       <c r="G280" t="n">
         <v>699.99</v>
@@ -9127,10 +9127,10 @@
         <v>700.99</v>
       </c>
       <c r="F281" t="n">
+        <v>699.49</v>
+      </c>
+      <c r="G281" t="n">
         <v>699.99</v>
-      </c>
-      <c r="G281" t="n">
-        <v>698.49</v>
       </c>
     </row>
     <row r="282">
@@ -9158,7 +9158,7 @@
         <v>698.99</v>
       </c>
       <c r="F282" t="n">
-        <v>699.49</v>
+        <v>699.99</v>
       </c>
       <c r="G282" t="n">
         <v>701.99</v>
@@ -9217,13 +9217,13 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>700.99</v>
+        <v>699.99</v>
       </c>
       <c r="F284" t="n">
-        <v>699.99</v>
+        <v>697.49</v>
       </c>
       <c r="G284" t="n">
-        <v>699.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="285">
@@ -9254,7 +9254,7 @@
         <v>699.99</v>
       </c>
       <c r="G285" t="n">
-        <v>699.99</v>
+        <v>701.99</v>
       </c>
     </row>
     <row r="286">
@@ -9279,13 +9279,13 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>699.99</v>
+        <v>700.99</v>
       </c>
       <c r="F286" t="n">
-        <v>701.49</v>
+        <v>697.49</v>
       </c>
       <c r="G286" t="n">
-        <v>699.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="287">
@@ -9310,13 +9310,13 @@
         </is>
       </c>
       <c r="E287" t="n">
+        <v>698.99</v>
+      </c>
+      <c r="F287" t="n">
         <v>699.99</v>
       </c>
-      <c r="F287" t="n">
-        <v>697.49</v>
-      </c>
       <c r="G287" t="n">
-        <v>698.49</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="288">
@@ -9341,13 +9341,13 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>698.99</v>
+        <v>699.99</v>
       </c>
       <c r="F288" t="n">
-        <v>699.49</v>
+        <v>697.49</v>
       </c>
       <c r="G288" t="n">
-        <v>701.99</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="289">
@@ -9372,10 +9372,10 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>699.99</v>
+        <v>698.99</v>
       </c>
       <c r="F289" t="n">
-        <v>699.99</v>
+        <v>697.49</v>
       </c>
       <c r="G289" t="n">
         <v>701.99</v>
@@ -9409,7 +9409,7 @@
         <v>699.99</v>
       </c>
       <c r="G290" t="n">
-        <v>699.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="291">
@@ -9434,7 +9434,7 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>700.99</v>
+        <v>699.99</v>
       </c>
       <c r="F291" t="n">
         <v>697.49</v>
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>698.99</v>
+        <v>699.99</v>
       </c>
       <c r="F292" t="n">
+        <v>701.49</v>
+      </c>
+      <c r="G292" t="n">
         <v>699.99</v>
-      </c>
-      <c r="G292" t="n">
-        <v>698.49</v>
       </c>
     </row>
     <row r="293">
@@ -9496,7 +9496,7 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>698.99</v>
+        <v>699.99</v>
       </c>
       <c r="F293" t="n">
         <v>697.49</v>
@@ -9530,7 +9530,7 @@
         <v>700.99</v>
       </c>
       <c r="F294" t="n">
-        <v>699.99</v>
+        <v>701.49</v>
       </c>
       <c r="G294" t="n">
         <v>698.49</v>
@@ -9558,13 +9558,13 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>698.99</v>
+        <v>699.99</v>
       </c>
       <c r="F295" t="n">
+        <v>701.49</v>
+      </c>
+      <c r="G295" t="n">
         <v>699.99</v>
-      </c>
-      <c r="G295" t="n">
-        <v>701.99</v>
       </c>
     </row>
     <row r="296">
@@ -9595,7 +9595,7 @@
         <v>699.99</v>
       </c>
       <c r="G296" t="n">
-        <v>701.99</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="297">
@@ -9623,10 +9623,10 @@
         <v>699.99</v>
       </c>
       <c r="F297" t="n">
-        <v>697.49</v>
+        <v>699.99</v>
       </c>
       <c r="G297" t="n">
-        <v>701.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="298">
@@ -9651,13 +9651,13 @@
         </is>
       </c>
       <c r="E298" t="n">
+        <v>698.99</v>
+      </c>
+      <c r="F298" t="n">
+        <v>697.49</v>
+      </c>
+      <c r="G298" t="n">
         <v>699.99</v>
-      </c>
-      <c r="F298" t="n">
-        <v>699.99</v>
-      </c>
-      <c r="G298" t="n">
-        <v>701.99</v>
       </c>
     </row>
     <row r="299">
@@ -9682,10 +9682,10 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>700.99</v>
+        <v>699.99</v>
       </c>
       <c r="F299" t="n">
-        <v>699.99</v>
+        <v>699.49</v>
       </c>
       <c r="G299" t="n">
         <v>699.99</v>
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>700.99</v>
+        <v>699.99</v>
       </c>
       <c r="F300" t="n">
-        <v>701.49</v>
+        <v>699.49</v>
       </c>
       <c r="G300" t="n">
-        <v>701.99</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="301">
@@ -9744,13 +9744,13 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>698.99</v>
+        <v>699.99</v>
       </c>
       <c r="F301" t="n">
-        <v>699.49</v>
+        <v>697.49</v>
       </c>
       <c r="G301" t="n">
-        <v>698.49</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="302">
@@ -9775,7 +9775,7 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>599.99</v>
+        <v>600.99</v>
       </c>
       <c r="F302" t="n">
         <v>579.99</v>
@@ -9806,13 +9806,13 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>598.99</v>
+        <v>599.99</v>
       </c>
       <c r="F303" t="n">
-        <v>579.49</v>
+        <v>579.99</v>
       </c>
       <c r="G303" t="n">
-        <v>588.49</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="304">
@@ -9837,13 +9837,13 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>599.99</v>
+        <v>600.99</v>
       </c>
       <c r="F304" t="n">
-        <v>579.49</v>
+        <v>579.99</v>
       </c>
       <c r="G304" t="n">
-        <v>591.99</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="305">
@@ -9868,13 +9868,13 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>599.99</v>
+        <v>600.99</v>
       </c>
       <c r="F305" t="n">
-        <v>579.99</v>
+        <v>579.49</v>
       </c>
       <c r="G305" t="n">
-        <v>589.99</v>
+        <v>591.99</v>
       </c>
     </row>
     <row r="306">
@@ -9899,10 +9899,10 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>599.99</v>
+        <v>600.99</v>
       </c>
       <c r="F306" t="n">
-        <v>579.99</v>
+        <v>581.49</v>
       </c>
       <c r="G306" t="n">
         <v>589.99</v>
@@ -9936,7 +9936,7 @@
         <v>577.49</v>
       </c>
       <c r="G307" t="n">
-        <v>589.99</v>
+        <v>588.49</v>
       </c>
     </row>
     <row r="308">
@@ -9964,10 +9964,10 @@
         <v>599.99</v>
       </c>
       <c r="F308" t="n">
-        <v>581.49</v>
+        <v>579.99</v>
       </c>
       <c r="G308" t="n">
-        <v>589.99</v>
+        <v>588.49</v>
       </c>
     </row>
     <row r="309">
@@ -9992,13 +9992,13 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>598.99</v>
+        <v>599.99</v>
       </c>
       <c r="F309" t="n">
-        <v>579.99</v>
+        <v>579.49</v>
       </c>
       <c r="G309" t="n">
-        <v>591.99</v>
+        <v>588.49</v>
       </c>
     </row>
     <row r="310">
@@ -10026,10 +10026,10 @@
         <v>599.99</v>
       </c>
       <c r="F310" t="n">
-        <v>577.49</v>
+        <v>579.99</v>
       </c>
       <c r="G310" t="n">
-        <v>589.99</v>
+        <v>591.99</v>
       </c>
     </row>
     <row r="311">
@@ -10057,10 +10057,10 @@
         <v>599.99</v>
       </c>
       <c r="F311" t="n">
-        <v>579.49</v>
+        <v>581.49</v>
       </c>
       <c r="G311" t="n">
-        <v>588.49</v>
+        <v>591.99</v>
       </c>
     </row>
     <row r="312">
@@ -10085,13 +10085,13 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>598.99</v>
+        <v>599.99</v>
       </c>
       <c r="F312" t="n">
         <v>581.49</v>
       </c>
       <c r="G312" t="n">
-        <v>588.49</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="313">
@@ -10116,10 +10116,10 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>599.99</v>
+        <v>600.99</v>
       </c>
       <c r="F313" t="n">
-        <v>579.99</v>
+        <v>577.49</v>
       </c>
       <c r="G313" t="n">
         <v>591.99</v>
@@ -10147,7 +10147,7 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>598.99</v>
+        <v>599.99</v>
       </c>
       <c r="F314" t="n">
         <v>579.99</v>
@@ -10181,7 +10181,7 @@
         <v>599.99</v>
       </c>
       <c r="F315" t="n">
-        <v>579.99</v>
+        <v>581.49</v>
       </c>
       <c r="G315" t="n">
         <v>589.99</v>
@@ -10212,7 +10212,7 @@
         <v>599.99</v>
       </c>
       <c r="F316" t="n">
-        <v>581.49</v>
+        <v>579.99</v>
       </c>
       <c r="G316" t="n">
         <v>589.99</v>
@@ -10240,13 +10240,13 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>599.99</v>
+        <v>600.99</v>
       </c>
       <c r="F317" t="n">
-        <v>579.99</v>
+        <v>579.49</v>
       </c>
       <c r="G317" t="n">
-        <v>591.99</v>
+        <v>588.49</v>
       </c>
     </row>
     <row r="318">
@@ -10274,7 +10274,7 @@
         <v>600.99</v>
       </c>
       <c r="F318" t="n">
-        <v>579.49</v>
+        <v>579.99</v>
       </c>
       <c r="G318" t="n">
         <v>591.99</v>
@@ -10305,10 +10305,10 @@
         <v>599.99</v>
       </c>
       <c r="F319" t="n">
-        <v>579.99</v>
+        <v>581.49</v>
       </c>
       <c r="G319" t="n">
-        <v>589.99</v>
+        <v>588.49</v>
       </c>
     </row>
     <row r="320">
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>599.99</v>
+        <v>598.99</v>
       </c>
       <c r="F320" t="n">
         <v>581.49</v>
@@ -10364,10 +10364,10 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>598.99</v>
+        <v>600.99</v>
       </c>
       <c r="F321" t="n">
-        <v>579.99</v>
+        <v>579.49</v>
       </c>
       <c r="G321" t="n">
         <v>589.99</v>
@@ -10395,13 +10395,13 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>599.99</v>
+        <v>598.99</v>
       </c>
       <c r="F322" t="n">
-        <v>579.49</v>
+        <v>579.99</v>
       </c>
       <c r="G322" t="n">
-        <v>588.49</v>
+        <v>591.99</v>
       </c>
     </row>
     <row r="323">
@@ -10426,13 +10426,13 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>600.99</v>
+        <v>598.99</v>
       </c>
       <c r="F323" t="n">
-        <v>581.49</v>
+        <v>579.49</v>
       </c>
       <c r="G323" t="n">
-        <v>591.99</v>
+        <v>588.49</v>
       </c>
     </row>
     <row r="324">
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>598.99</v>
+        <v>599.99</v>
       </c>
       <c r="F324" t="n">
-        <v>579.99</v>
+        <v>577.49</v>
       </c>
       <c r="G324" t="n">
         <v>589.99</v>
@@ -10488,10 +10488,10 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>598.99</v>
+        <v>599.99</v>
       </c>
       <c r="F325" t="n">
-        <v>579.99</v>
+        <v>579.49</v>
       </c>
       <c r="G325" t="n">
         <v>589.99</v>
@@ -10519,13 +10519,13 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>600.99</v>
+        <v>599.99</v>
       </c>
       <c r="F326" t="n">
-        <v>581.49</v>
+        <v>579.99</v>
       </c>
       <c r="G326" t="n">
-        <v>589.99</v>
+        <v>591.99</v>
       </c>
     </row>
     <row r="327">
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>599.99</v>
+        <v>598.99</v>
       </c>
       <c r="F327" t="n">
         <v>579.99</v>
       </c>
       <c r="G327" t="n">
-        <v>588.49</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="328">
@@ -10581,13 +10581,13 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>600.99</v>
+        <v>599.99</v>
       </c>
       <c r="F328" t="n">
-        <v>581.49</v>
+        <v>579.99</v>
       </c>
       <c r="G328" t="n">
-        <v>589.99</v>
+        <v>588.49</v>
       </c>
     </row>
     <row r="329">
@@ -10615,7 +10615,7 @@
         <v>599.99</v>
       </c>
       <c r="F329" t="n">
-        <v>579.99</v>
+        <v>577.49</v>
       </c>
       <c r="G329" t="n">
         <v>589.99</v>
@@ -10643,13 +10643,13 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>599.99</v>
+        <v>598.99</v>
       </c>
       <c r="F330" t="n">
         <v>579.49</v>
       </c>
       <c r="G330" t="n">
-        <v>591.99</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="331">
@@ -10677,10 +10677,10 @@
         <v>599.99</v>
       </c>
       <c r="F331" t="n">
-        <v>579.99</v>
+        <v>581.49</v>
       </c>
       <c r="G331" t="n">
-        <v>589.99</v>
+        <v>588.49</v>
       </c>
     </row>
     <row r="332">
@@ -10705,13 +10705,13 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>748.99</v>
+        <v>750.99</v>
       </c>
       <c r="F332" t="n">
-        <v>651.49</v>
+        <v>649.49</v>
       </c>
       <c r="G332" t="n">
-        <v>701.99</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="333">
@@ -10736,13 +10736,13 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>750.99</v>
+        <v>749.99</v>
       </c>
       <c r="F333" t="n">
         <v>649.99</v>
       </c>
       <c r="G333" t="n">
-        <v>698.49</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="334">
@@ -10767,13 +10767,13 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>750.99</v>
+        <v>748.99</v>
       </c>
       <c r="F334" t="n">
-        <v>647.49</v>
+        <v>649.49</v>
       </c>
       <c r="G334" t="n">
-        <v>701.99</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="335">
@@ -10798,10 +10798,10 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>748.99</v>
+        <v>749.99</v>
       </c>
       <c r="F335" t="n">
-        <v>649.99</v>
+        <v>649.49</v>
       </c>
       <c r="G335" t="n">
         <v>699.99</v>
@@ -10829,13 +10829,13 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>749.99</v>
+        <v>748.99</v>
       </c>
       <c r="F336" t="n">
-        <v>647.49</v>
+        <v>649.99</v>
       </c>
       <c r="G336" t="n">
-        <v>699.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="337">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>750.99</v>
+        <v>748.99</v>
       </c>
       <c r="F337" t="n">
-        <v>647.49</v>
+        <v>649.49</v>
       </c>
       <c r="G337" t="n">
-        <v>701.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="338">
@@ -10894,7 +10894,7 @@
         <v>749.99</v>
       </c>
       <c r="F338" t="n">
-        <v>651.49</v>
+        <v>647.49</v>
       </c>
       <c r="G338" t="n">
         <v>701.99</v>
@@ -10922,13 +10922,13 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>750.99</v>
+        <v>749.99</v>
       </c>
       <c r="F339" t="n">
-        <v>651.49</v>
+        <v>647.49</v>
       </c>
       <c r="G339" t="n">
-        <v>699.99</v>
+        <v>701.99</v>
       </c>
     </row>
     <row r="340">
@@ -10953,7 +10953,7 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>748.99</v>
+        <v>749.99</v>
       </c>
       <c r="F340" t="n">
         <v>647.49</v>
@@ -10984,10 +10984,10 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>750.99</v>
+        <v>749.99</v>
       </c>
       <c r="F341" t="n">
-        <v>649.99</v>
+        <v>647.49</v>
       </c>
       <c r="G341" t="n">
         <v>699.99</v>
@@ -11018,10 +11018,10 @@
         <v>749.99</v>
       </c>
       <c r="F342" t="n">
-        <v>649.99</v>
+        <v>649.49</v>
       </c>
       <c r="G342" t="n">
-        <v>699.99</v>
+        <v>701.99</v>
       </c>
     </row>
     <row r="343">
@@ -11046,10 +11046,10 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>748.99</v>
+        <v>749.99</v>
       </c>
       <c r="F343" t="n">
-        <v>649.99</v>
+        <v>647.49</v>
       </c>
       <c r="G343" t="n">
         <v>699.99</v>
@@ -11080,10 +11080,10 @@
         <v>750.99</v>
       </c>
       <c r="F344" t="n">
-        <v>647.49</v>
+        <v>649.49</v>
       </c>
       <c r="G344" t="n">
-        <v>699.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="345">
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>749.99</v>
+        <v>750.99</v>
       </c>
       <c r="F345" t="n">
-        <v>649.49</v>
+        <v>651.49</v>
       </c>
       <c r="G345" t="n">
         <v>699.99</v>
@@ -11139,10 +11139,10 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>749.99</v>
+        <v>750.99</v>
       </c>
       <c r="F346" t="n">
-        <v>649.99</v>
+        <v>647.49</v>
       </c>
       <c r="G346" t="n">
         <v>701.99</v>
@@ -11173,7 +11173,7 @@
         <v>748.99</v>
       </c>
       <c r="F347" t="n">
-        <v>649.99</v>
+        <v>647.49</v>
       </c>
       <c r="G347" t="n">
         <v>699.99</v>
@@ -11201,10 +11201,10 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>749.99</v>
+        <v>748.99</v>
       </c>
       <c r="F348" t="n">
-        <v>649.99</v>
+        <v>651.49</v>
       </c>
       <c r="G348" t="n">
         <v>701.99</v>
@@ -11235,10 +11235,10 @@
         <v>749.99</v>
       </c>
       <c r="F349" t="n">
-        <v>647.49</v>
+        <v>651.49</v>
       </c>
       <c r="G349" t="n">
-        <v>701.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="350">
@@ -11266,7 +11266,7 @@
         <v>749.99</v>
       </c>
       <c r="F350" t="n">
-        <v>647.49</v>
+        <v>651.49</v>
       </c>
       <c r="G350" t="n">
         <v>698.49</v>
@@ -11331,7 +11331,7 @@
         <v>649.49</v>
       </c>
       <c r="G352" t="n">
-        <v>698.49</v>
+        <v>701.99</v>
       </c>
     </row>
     <row r="353">
@@ -11393,7 +11393,7 @@
         <v>649.49</v>
       </c>
       <c r="G354" t="n">
-        <v>701.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="355">
@@ -11418,13 +11418,13 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>749.99</v>
+        <v>748.99</v>
       </c>
       <c r="F355" t="n">
-        <v>649.99</v>
+        <v>651.49</v>
       </c>
       <c r="G355" t="n">
-        <v>701.99</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="356">
@@ -11449,10 +11449,10 @@
         </is>
       </c>
       <c r="E356" t="n">
-        <v>748.99</v>
+        <v>749.99</v>
       </c>
       <c r="F356" t="n">
-        <v>651.49</v>
+        <v>649.99</v>
       </c>
       <c r="G356" t="n">
         <v>698.49</v>
@@ -11483,7 +11483,7 @@
         <v>748.99</v>
       </c>
       <c r="F357" t="n">
-        <v>647.49</v>
+        <v>649.99</v>
       </c>
       <c r="G357" t="n">
         <v>699.99</v>
@@ -11511,13 +11511,13 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>750.99</v>
+        <v>748.99</v>
       </c>
       <c r="F358" t="n">
-        <v>649.99</v>
+        <v>651.49</v>
       </c>
       <c r="G358" t="n">
-        <v>698.49</v>
+        <v>701.99</v>
       </c>
     </row>
     <row r="359">
@@ -11542,13 +11542,13 @@
         </is>
       </c>
       <c r="E359" t="n">
-        <v>749.99</v>
+        <v>750.99</v>
       </c>
       <c r="F359" t="n">
-        <v>649.49</v>
+        <v>651.49</v>
       </c>
       <c r="G359" t="n">
-        <v>701.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="360">
@@ -11576,7 +11576,7 @@
         <v>749.99</v>
       </c>
       <c r="F360" t="n">
-        <v>649.99</v>
+        <v>647.49</v>
       </c>
       <c r="G360" t="n">
         <v>699.99</v>
@@ -11604,7 +11604,7 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>749.99</v>
+        <v>748.99</v>
       </c>
       <c r="F361" t="n">
         <v>649.99</v>
@@ -11635,13 +11635,13 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="F362" t="n">
-        <v>379</v>
+        <v>376.5</v>
       </c>
       <c r="G362" t="n">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="363">
@@ -11669,10 +11669,10 @@
         <v>430</v>
       </c>
       <c r="F363" t="n">
-        <v>380.5</v>
+        <v>379</v>
       </c>
       <c r="G363" t="n">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="364">
@@ -11703,7 +11703,7 @@
         <v>379</v>
       </c>
       <c r="G364" t="n">
-        <v>399</v>
+        <v>397.5</v>
       </c>
     </row>
     <row r="365">
@@ -11731,10 +11731,10 @@
         <v>429</v>
       </c>
       <c r="F365" t="n">
-        <v>380.5</v>
+        <v>378.5</v>
       </c>
       <c r="G365" t="n">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="366">
@@ -11759,13 +11759,13 @@
         </is>
       </c>
       <c r="E366" t="n">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F366" t="n">
-        <v>380.5</v>
+        <v>378.5</v>
       </c>
       <c r="G366" t="n">
-        <v>401</v>
+        <v>397.5</v>
       </c>
     </row>
     <row r="367">
@@ -11790,13 +11790,13 @@
         </is>
       </c>
       <c r="E367" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F367" t="n">
-        <v>376.5</v>
+        <v>379</v>
       </c>
       <c r="G367" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="368">
@@ -11821,13 +11821,13 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F368" t="n">
-        <v>380.5</v>
+        <v>379</v>
       </c>
       <c r="G368" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="369">
@@ -11855,10 +11855,10 @@
         <v>429</v>
       </c>
       <c r="F369" t="n">
-        <v>380.5</v>
+        <v>379</v>
       </c>
       <c r="G369" t="n">
-        <v>401</v>
+        <v>397.5</v>
       </c>
     </row>
     <row r="370">
@@ -11886,10 +11886,10 @@
         <v>429</v>
       </c>
       <c r="F370" t="n">
-        <v>380.5</v>
+        <v>378.5</v>
       </c>
       <c r="G370" t="n">
-        <v>401</v>
+        <v>397.5</v>
       </c>
     </row>
     <row r="371">
@@ -11914,10 +11914,10 @@
         </is>
       </c>
       <c r="E371" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F371" t="n">
-        <v>378.5</v>
+        <v>379</v>
       </c>
       <c r="G371" t="n">
         <v>399</v>
@@ -11945,13 +11945,13 @@
         </is>
       </c>
       <c r="E372" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F372" t="n">
         <v>379</v>
       </c>
       <c r="G372" t="n">
-        <v>397.5</v>
+        <v>401</v>
       </c>
     </row>
     <row r="373">
@@ -11982,7 +11982,7 @@
         <v>376.5</v>
       </c>
       <c r="G373" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="374">
@@ -12010,7 +12010,7 @@
         <v>428</v>
       </c>
       <c r="F374" t="n">
-        <v>379</v>
+        <v>378.5</v>
       </c>
       <c r="G374" t="n">
         <v>399</v>
@@ -12038,13 +12038,13 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F375" t="n">
-        <v>376.5</v>
+        <v>378.5</v>
       </c>
       <c r="G375" t="n">
-        <v>399</v>
+        <v>397.5</v>
       </c>
     </row>
     <row r="376">
@@ -12072,10 +12072,10 @@
         <v>429</v>
       </c>
       <c r="F376" t="n">
-        <v>376.5</v>
+        <v>380.5</v>
       </c>
       <c r="G376" t="n">
-        <v>399</v>
+        <v>397.5</v>
       </c>
     </row>
     <row r="377">
@@ -12100,13 +12100,13 @@
         </is>
       </c>
       <c r="E377" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F377" t="n">
         <v>379</v>
       </c>
       <c r="G377" t="n">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="378">
@@ -12134,10 +12134,10 @@
         <v>429</v>
       </c>
       <c r="F378" t="n">
-        <v>379</v>
+        <v>378.5</v>
       </c>
       <c r="G378" t="n">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="379">
@@ -12196,10 +12196,10 @@
         <v>429</v>
       </c>
       <c r="F380" t="n">
-        <v>378.5</v>
+        <v>379</v>
       </c>
       <c r="G380" t="n">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="381">
@@ -12227,7 +12227,7 @@
         <v>429</v>
       </c>
       <c r="F381" t="n">
-        <v>380.5</v>
+        <v>376.5</v>
       </c>
       <c r="G381" t="n">
         <v>397.5</v>
@@ -12258,10 +12258,10 @@
         <v>429</v>
       </c>
       <c r="F382" t="n">
-        <v>380.5</v>
+        <v>378.5</v>
       </c>
       <c r="G382" t="n">
-        <v>401</v>
+        <v>397.5</v>
       </c>
     </row>
     <row r="383">
@@ -12286,13 +12286,13 @@
         </is>
       </c>
       <c r="E383" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F383" t="n">
-        <v>376.5</v>
+        <v>379</v>
       </c>
       <c r="G383" t="n">
-        <v>401</v>
+        <v>397.5</v>
       </c>
     </row>
     <row r="384">
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="E384" t="n">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F384" t="n">
         <v>378.5</v>
@@ -12348,7 +12348,7 @@
         </is>
       </c>
       <c r="E385" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F385" t="n">
         <v>379</v>
@@ -12379,13 +12379,13 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F386" t="n">
-        <v>376.5</v>
+        <v>379</v>
       </c>
       <c r="G386" t="n">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="387">
@@ -12410,7 +12410,7 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="F387" t="n">
         <v>379</v>
@@ -12441,13 +12441,13 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F388" t="n">
-        <v>380.5</v>
+        <v>378.5</v>
       </c>
       <c r="G388" t="n">
-        <v>399</v>
+        <v>397.5</v>
       </c>
     </row>
     <row r="389">
@@ -12472,10 +12472,10 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F389" t="n">
-        <v>376.5</v>
+        <v>378.5</v>
       </c>
       <c r="G389" t="n">
         <v>397.5</v>
@@ -12503,13 +12503,13 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F390" t="n">
         <v>376.5</v>
       </c>
       <c r="G390" t="n">
-        <v>399</v>
+        <v>397.5</v>
       </c>
     </row>
     <row r="391">
@@ -12537,10 +12537,10 @@
         <v>429</v>
       </c>
       <c r="F391" t="n">
-        <v>378.5</v>
+        <v>376.5</v>
       </c>
       <c r="G391" t="n">
-        <v>397.5</v>
+        <v>399</v>
       </c>
     </row>
     <row r="392">
@@ -12596,13 +12596,13 @@
         </is>
       </c>
       <c r="E393" t="n">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="F393" t="n">
-        <v>1049</v>
+        <v>1050.5</v>
       </c>
       <c r="G393" t="n">
-        <v>1067.5</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="394">
@@ -12627,10 +12627,10 @@
         </is>
       </c>
       <c r="E394" t="n">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="F394" t="n">
-        <v>1046.5</v>
+        <v>1049</v>
       </c>
       <c r="G394" t="n">
         <v>1069</v>
@@ -12661,10 +12661,10 @@
         <v>1149</v>
       </c>
       <c r="F395" t="n">
-        <v>1048.5</v>
+        <v>1049</v>
       </c>
       <c r="G395" t="n">
-        <v>1067.5</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="396">
@@ -12692,10 +12692,10 @@
         <v>1149</v>
       </c>
       <c r="F396" t="n">
-        <v>1049</v>
+        <v>1046.5</v>
       </c>
       <c r="G396" t="n">
-        <v>1067.5</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="397">
@@ -12723,10 +12723,10 @@
         <v>1149</v>
       </c>
       <c r="F397" t="n">
-        <v>1046.5</v>
+        <v>1049</v>
       </c>
       <c r="G397" t="n">
-        <v>1069</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="398">
@@ -12751,13 +12751,13 @@
         </is>
       </c>
       <c r="E398" t="n">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="F398" t="n">
-        <v>1050.5</v>
+        <v>1049</v>
       </c>
       <c r="G398" t="n">
-        <v>1067.5</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="399">
@@ -12788,7 +12788,7 @@
         <v>1046.5</v>
       </c>
       <c r="G399" t="n">
-        <v>1069</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="400">
@@ -12813,13 +12813,13 @@
         </is>
       </c>
       <c r="E400" t="n">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="F400" t="n">
         <v>1049</v>
       </c>
       <c r="G400" t="n">
-        <v>1071</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="401">
@@ -12844,10 +12844,10 @@
         </is>
       </c>
       <c r="E401" t="n">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="F401" t="n">
-        <v>1049</v>
+        <v>1050.5</v>
       </c>
       <c r="G401" t="n">
         <v>1071</v>
@@ -12875,13 +12875,13 @@
         </is>
       </c>
       <c r="E402" t="n">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F402" t="n">
-        <v>1049</v>
+        <v>1046.5</v>
       </c>
       <c r="G402" t="n">
-        <v>1069</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="403">
@@ -12909,10 +12909,10 @@
         <v>1149</v>
       </c>
       <c r="F403" t="n">
-        <v>1050.5</v>
+        <v>1048.5</v>
       </c>
       <c r="G403" t="n">
-        <v>1071</v>
+        <v>1067.5</v>
       </c>
     </row>
     <row r="404">
@@ -12937,13 +12937,13 @@
         </is>
       </c>
       <c r="E404" t="n">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="F404" t="n">
-        <v>1046.5</v>
+        <v>1050.5</v>
       </c>
       <c r="G404" t="n">
-        <v>1067.5</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="405">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="E405" t="n">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="F405" t="n">
         <v>1046.5</v>
       </c>
       <c r="G405" t="n">
-        <v>1069</v>
+        <v>1067.5</v>
       </c>
     </row>
     <row r="406">
@@ -13002,10 +13002,10 @@
         <v>1149</v>
       </c>
       <c r="F406" t="n">
-        <v>1046.5</v>
+        <v>1048.5</v>
       </c>
       <c r="G406" t="n">
-        <v>1069</v>
+        <v>1067.5</v>
       </c>
     </row>
     <row r="407">
@@ -13030,13 +13030,13 @@
         </is>
       </c>
       <c r="E407" t="n">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="F407" t="n">
-        <v>1049</v>
+        <v>1046.5</v>
       </c>
       <c r="G407" t="n">
-        <v>1067.5</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="408">
@@ -13061,10 +13061,10 @@
         </is>
       </c>
       <c r="E408" t="n">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="F408" t="n">
-        <v>1050.5</v>
+        <v>1046.5</v>
       </c>
       <c r="G408" t="n">
         <v>1067.5</v>
@@ -13092,13 +13092,13 @@
         </is>
       </c>
       <c r="E409" t="n">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="F409" t="n">
-        <v>1050.5</v>
+        <v>1046.5</v>
       </c>
       <c r="G409" t="n">
-        <v>1069</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="410">
@@ -13123,13 +13123,13 @@
         </is>
       </c>
       <c r="E410" t="n">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="F410" t="n">
-        <v>1050.5</v>
+        <v>1049</v>
       </c>
       <c r="G410" t="n">
-        <v>1071</v>
+        <v>1067.5</v>
       </c>
     </row>
     <row r="411">
@@ -13157,7 +13157,7 @@
         <v>1149</v>
       </c>
       <c r="F411" t="n">
-        <v>1048.5</v>
+        <v>1049</v>
       </c>
       <c r="G411" t="n">
         <v>1071</v>
@@ -13185,13 +13185,13 @@
         </is>
       </c>
       <c r="E412" t="n">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="F412" t="n">
-        <v>1049</v>
+        <v>1046.5</v>
       </c>
       <c r="G412" t="n">
-        <v>1069</v>
+        <v>1067.5</v>
       </c>
     </row>
     <row r="413">
@@ -13250,10 +13250,10 @@
         <v>1149</v>
       </c>
       <c r="F414" t="n">
-        <v>1046.5</v>
+        <v>1049</v>
       </c>
       <c r="G414" t="n">
-        <v>1067.5</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="415">
@@ -13284,7 +13284,7 @@
         <v>1050.5</v>
       </c>
       <c r="G415" t="n">
-        <v>1067.5</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="416">
@@ -13312,10 +13312,10 @@
         <v>1149</v>
       </c>
       <c r="F416" t="n">
-        <v>1050.5</v>
+        <v>1049</v>
       </c>
       <c r="G416" t="n">
-        <v>1067.5</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="417">
@@ -13340,13 +13340,13 @@
         </is>
       </c>
       <c r="E417" t="n">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="F417" t="n">
-        <v>1050.5</v>
+        <v>1048.5</v>
       </c>
       <c r="G417" t="n">
-        <v>1071</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="418">
@@ -13374,10 +13374,10 @@
         <v>1149</v>
       </c>
       <c r="F418" t="n">
-        <v>1048.5</v>
+        <v>1050.5</v>
       </c>
       <c r="G418" t="n">
-        <v>1071</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="419">
@@ -13405,10 +13405,10 @@
         <v>1149</v>
       </c>
       <c r="F419" t="n">
-        <v>1048.5</v>
+        <v>1049</v>
       </c>
       <c r="G419" t="n">
-        <v>1071</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="420">
@@ -13436,7 +13436,7 @@
         <v>1149</v>
       </c>
       <c r="F420" t="n">
-        <v>1046.5</v>
+        <v>1049</v>
       </c>
       <c r="G420" t="n">
         <v>1069</v>
@@ -13464,10 +13464,10 @@
         </is>
       </c>
       <c r="E421" t="n">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F421" t="n">
-        <v>1050.5</v>
+        <v>1048.5</v>
       </c>
       <c r="G421" t="n">
         <v>1067.5</v>
@@ -13498,10 +13498,10 @@
         <v>1099</v>
       </c>
       <c r="F422" t="n">
-        <v>1049</v>
+        <v>1048.5</v>
       </c>
       <c r="G422" t="n">
-        <v>1079</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="423">
@@ -13526,13 +13526,13 @@
         </is>
       </c>
       <c r="E423" t="n">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="F423" t="n">
-        <v>1049</v>
+        <v>1050.5</v>
       </c>
       <c r="G423" t="n">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="424">
@@ -13560,7 +13560,7 @@
         <v>1099</v>
       </c>
       <c r="F424" t="n">
-        <v>1049</v>
+        <v>1050.5</v>
       </c>
       <c r="G424" t="n">
         <v>1081</v>
@@ -13588,13 +13588,13 @@
         </is>
       </c>
       <c r="E425" t="n">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="F425" t="n">
-        <v>1049</v>
+        <v>1046.5</v>
       </c>
       <c r="G425" t="n">
-        <v>1077.5</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="426">
@@ -13619,10 +13619,10 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="F426" t="n">
-        <v>1046.5</v>
+        <v>1049</v>
       </c>
       <c r="G426" t="n">
         <v>1079</v>
@@ -13650,13 +13650,13 @@
         </is>
       </c>
       <c r="E427" t="n">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="F427" t="n">
-        <v>1048.5</v>
+        <v>1049</v>
       </c>
       <c r="G427" t="n">
-        <v>1077.5</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="428">
@@ -13681,7 +13681,7 @@
         </is>
       </c>
       <c r="E428" t="n">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="F428" t="n">
         <v>1049</v>
@@ -13712,10 +13712,10 @@
         </is>
       </c>
       <c r="E429" t="n">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="F429" t="n">
-        <v>1048.5</v>
+        <v>1049</v>
       </c>
       <c r="G429" t="n">
         <v>1081</v>
@@ -13746,7 +13746,7 @@
         <v>1099</v>
       </c>
       <c r="F430" t="n">
-        <v>1049</v>
+        <v>1046.5</v>
       </c>
       <c r="G430" t="n">
         <v>1081</v>
@@ -13777,10 +13777,10 @@
         <v>1099</v>
       </c>
       <c r="F431" t="n">
-        <v>1049</v>
+        <v>1050.5</v>
       </c>
       <c r="G431" t="n">
-        <v>1079</v>
+        <v>1077.5</v>
       </c>
     </row>
     <row r="432">
@@ -13808,10 +13808,10 @@
         <v>1099</v>
       </c>
       <c r="F432" t="n">
-        <v>1046.5</v>
+        <v>1050.5</v>
       </c>
       <c r="G432" t="n">
-        <v>1077.5</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="433">
@@ -13836,13 +13836,13 @@
         </is>
       </c>
       <c r="E433" t="n">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="F433" t="n">
-        <v>1049</v>
+        <v>1048.5</v>
       </c>
       <c r="G433" t="n">
-        <v>1079</v>
+        <v>1077.5</v>
       </c>
     </row>
     <row r="434">
@@ -13867,13 +13867,13 @@
         </is>
       </c>
       <c r="E434" t="n">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="F434" t="n">
         <v>1050.5</v>
       </c>
       <c r="G434" t="n">
-        <v>1081</v>
+        <v>1077.5</v>
       </c>
     </row>
     <row r="435">
@@ -13898,13 +13898,13 @@
         </is>
       </c>
       <c r="E435" t="n">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="F435" t="n">
-        <v>1050.5</v>
+        <v>1046.5</v>
       </c>
       <c r="G435" t="n">
-        <v>1079</v>
+        <v>1077.5</v>
       </c>
     </row>
     <row r="436">
@@ -13932,10 +13932,10 @@
         <v>1099</v>
       </c>
       <c r="F436" t="n">
-        <v>1046.5</v>
+        <v>1048.5</v>
       </c>
       <c r="G436" t="n">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="437">
@@ -13960,7 +13960,7 @@
         </is>
       </c>
       <c r="E437" t="n">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="F437" t="n">
         <v>1049</v>
@@ -13991,10 +13991,10 @@
         </is>
       </c>
       <c r="E438" t="n">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="F438" t="n">
-        <v>1049</v>
+        <v>1048.5</v>
       </c>
       <c r="G438" t="n">
         <v>1077.5</v>
@@ -14022,13 +14022,13 @@
         </is>
       </c>
       <c r="E439" t="n">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="F439" t="n">
-        <v>1046.5</v>
+        <v>1050.5</v>
       </c>
       <c r="G439" t="n">
-        <v>1079</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="440">
@@ -14053,10 +14053,10 @@
         </is>
       </c>
       <c r="E440" t="n">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="F440" t="n">
-        <v>1050.5</v>
+        <v>1049</v>
       </c>
       <c r="G440" t="n">
         <v>1079</v>
@@ -14115,13 +14115,13 @@
         </is>
       </c>
       <c r="E442" t="n">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="F442" t="n">
         <v>1046.5</v>
       </c>
       <c r="G442" t="n">
-        <v>1079</v>
+        <v>1077.5</v>
       </c>
     </row>
     <row r="443">
@@ -14146,10 +14146,10 @@
         </is>
       </c>
       <c r="E443" t="n">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="F443" t="n">
-        <v>1049</v>
+        <v>1048.5</v>
       </c>
       <c r="G443" t="n">
         <v>1077.5</v>
@@ -14177,10 +14177,10 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="F444" t="n">
-        <v>1050.5</v>
+        <v>1046.5</v>
       </c>
       <c r="G444" t="n">
         <v>1079</v>
@@ -14211,10 +14211,10 @@
         <v>1099</v>
       </c>
       <c r="F445" t="n">
-        <v>1046.5</v>
+        <v>1049</v>
       </c>
       <c r="G445" t="n">
-        <v>1079</v>
+        <v>1077.5</v>
       </c>
     </row>
     <row r="446">
@@ -14245,7 +14245,7 @@
         <v>1049</v>
       </c>
       <c r="G446" t="n">
-        <v>1077.5</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="447">
@@ -14270,13 +14270,13 @@
         </is>
       </c>
       <c r="E447" t="n">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="F447" t="n">
-        <v>1049</v>
+        <v>1050.5</v>
       </c>
       <c r="G447" t="n">
-        <v>1077.5</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="448">
@@ -14301,10 +14301,10 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="F448" t="n">
-        <v>1050.5</v>
+        <v>1046.5</v>
       </c>
       <c r="G448" t="n">
         <v>1077.5</v>
@@ -14332,13 +14332,13 @@
         </is>
       </c>
       <c r="E449" t="n">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="F449" t="n">
         <v>1048.5</v>
       </c>
       <c r="G449" t="n">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="450">
@@ -14363,13 +14363,13 @@
         </is>
       </c>
       <c r="E450" t="n">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="F450" t="n">
         <v>1049</v>
       </c>
       <c r="G450" t="n">
-        <v>1079</v>
+        <v>1077.5</v>
       </c>
     </row>
     <row r="451">
@@ -14400,7 +14400,7 @@
         <v>1049</v>
       </c>
       <c r="G451" t="n">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="452">
@@ -14425,13 +14425,13 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>498.99</v>
+        <v>499.99</v>
       </c>
       <c r="F452" t="n">
-        <v>489.99</v>
+        <v>487.49</v>
       </c>
       <c r="G452" t="n">
-        <v>501.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="453">
@@ -14459,10 +14459,10 @@
         <v>499.99</v>
       </c>
       <c r="F453" t="n">
-        <v>489.49</v>
+        <v>489.99</v>
       </c>
       <c r="G453" t="n">
-        <v>501.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="454">
@@ -14487,13 +14487,13 @@
         </is>
       </c>
       <c r="E454" t="n">
-        <v>499.99</v>
+        <v>500.99</v>
       </c>
       <c r="F454" t="n">
-        <v>489.99</v>
+        <v>491.49</v>
       </c>
       <c r="G454" t="n">
-        <v>499.99</v>
+        <v>501.99</v>
       </c>
     </row>
     <row r="455">
@@ -14518,13 +14518,13 @@
         </is>
       </c>
       <c r="E455" t="n">
+        <v>498.99</v>
+      </c>
+      <c r="F455" t="n">
+        <v>489.49</v>
+      </c>
+      <c r="G455" t="n">
         <v>499.99</v>
-      </c>
-      <c r="F455" t="n">
-        <v>489.99</v>
-      </c>
-      <c r="G455" t="n">
-        <v>501.99</v>
       </c>
     </row>
     <row r="456">
@@ -14549,10 +14549,10 @@
         </is>
       </c>
       <c r="E456" t="n">
-        <v>500.99</v>
+        <v>498.99</v>
       </c>
       <c r="F456" t="n">
-        <v>489.99</v>
+        <v>491.49</v>
       </c>
       <c r="G456" t="n">
         <v>499.99</v>
@@ -14611,13 +14611,13 @@
         </is>
       </c>
       <c r="E458" t="n">
+        <v>500.99</v>
+      </c>
+      <c r="F458" t="n">
+        <v>489.99</v>
+      </c>
+      <c r="G458" t="n">
         <v>499.99</v>
-      </c>
-      <c r="F458" t="n">
-        <v>487.49</v>
-      </c>
-      <c r="G458" t="n">
-        <v>498.49</v>
       </c>
     </row>
     <row r="459">
@@ -14673,13 +14673,13 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>498.99</v>
+        <v>500.99</v>
       </c>
       <c r="F460" t="n">
-        <v>491.49</v>
+        <v>489.99</v>
       </c>
       <c r="G460" t="n">
-        <v>498.49</v>
+        <v>501.99</v>
       </c>
     </row>
     <row r="461">
@@ -14704,10 +14704,10 @@
         </is>
       </c>
       <c r="E461" t="n">
-        <v>500.99</v>
+        <v>499.99</v>
       </c>
       <c r="F461" t="n">
-        <v>489.49</v>
+        <v>489.99</v>
       </c>
       <c r="G461" t="n">
         <v>499.99</v>
@@ -14735,13 +14735,13 @@
         </is>
       </c>
       <c r="E462" t="n">
-        <v>499.99</v>
+        <v>500.99</v>
       </c>
       <c r="F462" t="n">
-        <v>489.99</v>
+        <v>491.49</v>
       </c>
       <c r="G462" t="n">
-        <v>499.99</v>
+        <v>501.99</v>
       </c>
     </row>
     <row r="463">
@@ -14769,10 +14769,10 @@
         <v>499.99</v>
       </c>
       <c r="F463" t="n">
-        <v>489.99</v>
+        <v>487.49</v>
       </c>
       <c r="G463" t="n">
-        <v>498.49</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="464">
@@ -14797,13 +14797,13 @@
         </is>
       </c>
       <c r="E464" t="n">
-        <v>498.99</v>
+        <v>500.99</v>
       </c>
       <c r="F464" t="n">
         <v>487.49</v>
       </c>
       <c r="G464" t="n">
-        <v>499.99</v>
+        <v>501.99</v>
       </c>
     </row>
     <row r="465">
@@ -14831,10 +14831,10 @@
         <v>499.99</v>
       </c>
       <c r="F465" t="n">
-        <v>489.49</v>
+        <v>487.49</v>
       </c>
       <c r="G465" t="n">
-        <v>501.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="466">
@@ -14862,7 +14862,7 @@
         <v>500.99</v>
       </c>
       <c r="F466" t="n">
-        <v>489.49</v>
+        <v>491.49</v>
       </c>
       <c r="G466" t="n">
         <v>499.99</v>
@@ -14893,7 +14893,7 @@
         <v>499.99</v>
       </c>
       <c r="F467" t="n">
-        <v>489.49</v>
+        <v>489.99</v>
       </c>
       <c r="G467" t="n">
         <v>499.99</v>
@@ -14921,13 +14921,13 @@
         </is>
       </c>
       <c r="E468" t="n">
-        <v>498.99</v>
+        <v>499.99</v>
       </c>
       <c r="F468" t="n">
-        <v>489.99</v>
+        <v>491.49</v>
       </c>
       <c r="G468" t="n">
-        <v>499.99</v>
+        <v>498.49</v>
       </c>
     </row>
     <row r="469">
@@ -14952,13 +14952,13 @@
         </is>
       </c>
       <c r="E469" t="n">
-        <v>500.99</v>
+        <v>499.99</v>
       </c>
       <c r="F469" t="n">
-        <v>491.49</v>
+        <v>489.99</v>
       </c>
       <c r="G469" t="n">
-        <v>499.99</v>
+        <v>498.49</v>
       </c>
     </row>
     <row r="470">
@@ -14986,7 +14986,7 @@
         <v>499.99</v>
       </c>
       <c r="F470" t="n">
-        <v>489.99</v>
+        <v>487.49</v>
       </c>
       <c r="G470" t="n">
         <v>498.49</v>
@@ -15017,10 +15017,10 @@
         <v>500.99</v>
       </c>
       <c r="F471" t="n">
-        <v>489.49</v>
+        <v>487.49</v>
       </c>
       <c r="G471" t="n">
-        <v>498.49</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="472">
@@ -15045,13 +15045,13 @@
         </is>
       </c>
       <c r="E472" t="n">
+        <v>500.99</v>
+      </c>
+      <c r="F472" t="n">
+        <v>489.49</v>
+      </c>
+      <c r="G472" t="n">
         <v>499.99</v>
-      </c>
-      <c r="F472" t="n">
-        <v>491.49</v>
-      </c>
-      <c r="G472" t="n">
-        <v>501.99</v>
       </c>
     </row>
     <row r="473">
@@ -15076,13 +15076,13 @@
         </is>
       </c>
       <c r="E473" t="n">
-        <v>500.99</v>
+        <v>499.99</v>
       </c>
       <c r="F473" t="n">
-        <v>489.49</v>
+        <v>489.99</v>
       </c>
       <c r="G473" t="n">
-        <v>498.49</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="474">
@@ -15107,13 +15107,13 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>500.99</v>
+        <v>499.99</v>
       </c>
       <c r="F474" t="n">
         <v>491.49</v>
       </c>
       <c r="G474" t="n">
-        <v>499.99</v>
+        <v>498.49</v>
       </c>
     </row>
     <row r="475">
@@ -15138,13 +15138,13 @@
         </is>
       </c>
       <c r="E475" t="n">
+        <v>498.99</v>
+      </c>
+      <c r="F475" t="n">
+        <v>489.99</v>
+      </c>
+      <c r="G475" t="n">
         <v>499.99</v>
-      </c>
-      <c r="F475" t="n">
-        <v>491.49</v>
-      </c>
-      <c r="G475" t="n">
-        <v>498.49</v>
       </c>
     </row>
     <row r="476">
@@ -15169,13 +15169,13 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>499.99</v>
+        <v>500.99</v>
       </c>
       <c r="F476" t="n">
-        <v>491.49</v>
+        <v>489.99</v>
       </c>
       <c r="G476" t="n">
-        <v>501.99</v>
+        <v>498.49</v>
       </c>
     </row>
     <row r="477">
@@ -15203,7 +15203,7 @@
         <v>499.99</v>
       </c>
       <c r="F477" t="n">
-        <v>487.49</v>
+        <v>489.99</v>
       </c>
       <c r="G477" t="n">
         <v>501.99</v>
@@ -15237,7 +15237,7 @@
         <v>487.49</v>
       </c>
       <c r="G478" t="n">
-        <v>498.49</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="479">
@@ -15262,13 +15262,13 @@
         </is>
       </c>
       <c r="E479" t="n">
-        <v>499.99</v>
+        <v>498.99</v>
       </c>
       <c r="F479" t="n">
-        <v>489.99</v>
+        <v>491.49</v>
       </c>
       <c r="G479" t="n">
-        <v>499.99</v>
+        <v>498.49</v>
       </c>
     </row>
     <row r="480">
@@ -15293,10 +15293,10 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>500.99</v>
+        <v>498.99</v>
       </c>
       <c r="F480" t="n">
-        <v>489.49</v>
+        <v>491.49</v>
       </c>
       <c r="G480" t="n">
         <v>499.99</v>
@@ -15324,13 +15324,13 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>500.99</v>
+        <v>499.99</v>
       </c>
       <c r="F481" t="n">
-        <v>489.49</v>
+        <v>491.49</v>
       </c>
       <c r="G481" t="n">
-        <v>498.49</v>
+        <v>501.99</v>
       </c>
     </row>
   </sheetData>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -478,7 +478,7 @@
         <v>1199</v>
       </c>
       <c r="F2" t="n">
-        <v>1189.99</v>
+        <v>1187.49</v>
       </c>
       <c r="G2" t="n">
         <v>1194</v>
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="F4" t="n">
-        <v>1189.49</v>
+        <v>1189.99</v>
       </c>
       <c r="G4" t="n">
-        <v>1194</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="5">
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="F5" t="n">
         <v>1187.49</v>
       </c>
       <c r="G5" t="n">
-        <v>1194</v>
+        <v>1192.5</v>
       </c>
     </row>
     <row r="6">
@@ -602,7 +602,7 @@
         <v>1199</v>
       </c>
       <c r="F6" t="n">
-        <v>1189.99</v>
+        <v>1191.49</v>
       </c>
       <c r="G6" t="n">
         <v>1196</v>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="F7" t="n">
-        <v>1189.99</v>
+        <v>1189.49</v>
       </c>
       <c r="G7" t="n">
         <v>1194</v>
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="F8" t="n">
-        <v>1187.49</v>
+        <v>1189.99</v>
       </c>
       <c r="G8" t="n">
-        <v>1194</v>
+        <v>1192.5</v>
       </c>
     </row>
     <row r="9">
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="F9" t="n">
-        <v>1189.99</v>
+        <v>1189.49</v>
       </c>
       <c r="G9" t="n">
-        <v>1194</v>
+        <v>1192.5</v>
       </c>
     </row>
     <row r="10">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="F10" t="n">
-        <v>1191.49</v>
+        <v>1187.49</v>
       </c>
       <c r="G10" t="n">
-        <v>1194</v>
+        <v>1192.5</v>
       </c>
     </row>
     <row r="11">
@@ -754,13 +754,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="F11" t="n">
-        <v>1189.99</v>
+        <v>1189.49</v>
       </c>
       <c r="G11" t="n">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="12">
@@ -788,7 +788,7 @@
         <v>1199</v>
       </c>
       <c r="F12" t="n">
-        <v>1187.49</v>
+        <v>1189.99</v>
       </c>
       <c r="G12" t="n">
         <v>1196</v>
@@ -819,10 +819,10 @@
         <v>1199</v>
       </c>
       <c r="F13" t="n">
-        <v>1191.49</v>
+        <v>1189.99</v>
       </c>
       <c r="G13" t="n">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="14">
@@ -850,10 +850,10 @@
         <v>1199</v>
       </c>
       <c r="F14" t="n">
-        <v>1189.99</v>
+        <v>1189.49</v>
       </c>
       <c r="G14" t="n">
-        <v>1192.5</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="15">
@@ -884,7 +884,7 @@
         <v>1189.99</v>
       </c>
       <c r="G15" t="n">
-        <v>1192.5</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="16">
@@ -909,13 +909,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="F16" t="n">
-        <v>1191.49</v>
+        <v>1189.99</v>
       </c>
       <c r="G16" t="n">
-        <v>1192.5</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="17">
@@ -940,13 +940,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="F17" t="n">
         <v>1189.99</v>
       </c>
       <c r="G17" t="n">
-        <v>1194</v>
+        <v>1192.5</v>
       </c>
     </row>
     <row r="18">
@@ -974,10 +974,10 @@
         <v>1199</v>
       </c>
       <c r="F18" t="n">
-        <v>1191.49</v>
+        <v>1187.49</v>
       </c>
       <c r="G18" t="n">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="19">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="F19" t="n">
-        <v>1191.49</v>
+        <v>1189.49</v>
       </c>
       <c r="G19" t="n">
         <v>1194</v>
@@ -1033,13 +1033,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="F20" t="n">
-        <v>1191.49</v>
+        <v>1189.99</v>
       </c>
       <c r="G20" t="n">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="21">
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="F21" t="n">
-        <v>1191.49</v>
+        <v>1189.99</v>
       </c>
       <c r="G21" t="n">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="22">
@@ -1098,10 +1098,10 @@
         <v>1199</v>
       </c>
       <c r="F22" t="n">
-        <v>1189.99</v>
+        <v>1191.49</v>
       </c>
       <c r="G22" t="n">
-        <v>1192.5</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="23">
@@ -1126,13 +1126,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="F23" t="n">
         <v>1189.99</v>
       </c>
       <c r="G23" t="n">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="24">
@@ -1160,10 +1160,10 @@
         <v>1199</v>
       </c>
       <c r="F24" t="n">
-        <v>1189.99</v>
+        <v>1191.49</v>
       </c>
       <c r="G24" t="n">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="25">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="F25" t="n">
-        <v>1191.49</v>
+        <v>1189.49</v>
       </c>
       <c r="G25" t="n">
         <v>1194</v>
@@ -1219,13 +1219,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="F26" t="n">
-        <v>1189.99</v>
+        <v>1191.49</v>
       </c>
       <c r="G26" t="n">
-        <v>1194</v>
+        <v>1192.5</v>
       </c>
     </row>
     <row r="27">
@@ -1256,7 +1256,7 @@
         <v>1189.49</v>
       </c>
       <c r="G27" t="n">
-        <v>1196</v>
+        <v>1192.5</v>
       </c>
     </row>
     <row r="28">
@@ -1281,13 +1281,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="F28" t="n">
-        <v>1187.49</v>
+        <v>1189.99</v>
       </c>
       <c r="G28" t="n">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="29">
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="F29" t="n">
         <v>1189.99</v>
       </c>
       <c r="G29" t="n">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="30">
@@ -1346,7 +1346,7 @@
         <v>1199</v>
       </c>
       <c r="F30" t="n">
-        <v>1187.49</v>
+        <v>1191.49</v>
       </c>
       <c r="G30" t="n">
         <v>1194</v>
@@ -1377,7 +1377,7 @@
         <v>1199</v>
       </c>
       <c r="F31" t="n">
-        <v>1189.99</v>
+        <v>1191.49</v>
       </c>
       <c r="G31" t="n">
         <v>1194</v>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>869.99</v>
+        <v>870.99</v>
       </c>
       <c r="F32" t="n">
-        <v>827.49</v>
+        <v>829.49</v>
       </c>
       <c r="G32" t="n">
         <v>849.99</v>
@@ -1436,13 +1436,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>869.99</v>
+        <v>870.99</v>
       </c>
       <c r="F33" t="n">
-        <v>827.49</v>
+        <v>829.99</v>
       </c>
       <c r="G33" t="n">
-        <v>848.49</v>
+        <v>849.99</v>
       </c>
     </row>
     <row r="34">
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>868.99</v>
+        <v>869.99</v>
       </c>
       <c r="F34" t="n">
         <v>829.99</v>
       </c>
       <c r="G34" t="n">
-        <v>849.99</v>
+        <v>851.99</v>
       </c>
     </row>
     <row r="35">
@@ -1501,10 +1501,10 @@
         <v>869.99</v>
       </c>
       <c r="F35" t="n">
-        <v>831.49</v>
+        <v>827.49</v>
       </c>
       <c r="G35" t="n">
-        <v>851.99</v>
+        <v>849.99</v>
       </c>
     </row>
     <row r="36">
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>870.99</v>
+        <v>868.99</v>
       </c>
       <c r="F36" t="n">
-        <v>831.49</v>
+        <v>827.49</v>
       </c>
       <c r="G36" t="n">
-        <v>849.99</v>
+        <v>851.99</v>
       </c>
     </row>
     <row r="37">
@@ -1560,13 +1560,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>868.99</v>
+        <v>870.99</v>
       </c>
       <c r="F37" t="n">
         <v>829.99</v>
       </c>
       <c r="G37" t="n">
-        <v>848.49</v>
+        <v>849.99</v>
       </c>
     </row>
     <row r="38">
@@ -1591,13 +1591,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>869.99</v>
+        <v>870.99</v>
       </c>
       <c r="F38" t="n">
-        <v>831.49</v>
+        <v>827.49</v>
       </c>
       <c r="G38" t="n">
-        <v>851.99</v>
+        <v>848.49</v>
       </c>
     </row>
     <row r="39">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>869.99</v>
+        <v>870.99</v>
       </c>
       <c r="F39" t="n">
-        <v>829.99</v>
+        <v>827.49</v>
       </c>
       <c r="G39" t="n">
         <v>849.99</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>868.99</v>
+        <v>869.99</v>
       </c>
       <c r="F40" t="n">
         <v>829.99</v>
@@ -1684,13 +1684,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>870.99</v>
+        <v>869.99</v>
       </c>
       <c r="F41" t="n">
-        <v>829.49</v>
+        <v>831.49</v>
       </c>
       <c r="G41" t="n">
-        <v>849.99</v>
+        <v>848.49</v>
       </c>
     </row>
     <row r="42">
@@ -1718,7 +1718,7 @@
         <v>869.99</v>
       </c>
       <c r="F42" t="n">
-        <v>829.99</v>
+        <v>827.49</v>
       </c>
       <c r="G42" t="n">
         <v>849.99</v>
@@ -1749,7 +1749,7 @@
         <v>869.99</v>
       </c>
       <c r="F43" t="n">
-        <v>827.49</v>
+        <v>829.99</v>
       </c>
       <c r="G43" t="n">
         <v>851.99</v>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>869.99</v>
+        <v>868.99</v>
       </c>
       <c r="F44" t="n">
-        <v>827.49</v>
+        <v>829.49</v>
       </c>
       <c r="G44" t="n">
         <v>849.99</v>
@@ -1808,13 +1808,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>870.99</v>
+        <v>869.99</v>
       </c>
       <c r="F45" t="n">
         <v>831.49</v>
       </c>
       <c r="G45" t="n">
-        <v>849.99</v>
+        <v>851.99</v>
       </c>
     </row>
     <row r="46">
@@ -1842,7 +1842,7 @@
         <v>869.99</v>
       </c>
       <c r="F46" t="n">
-        <v>831.49</v>
+        <v>827.49</v>
       </c>
       <c r="G46" t="n">
         <v>848.49</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>868.99</v>
+        <v>869.99</v>
       </c>
       <c r="F48" t="n">
         <v>829.49</v>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>869.99</v>
+        <v>870.99</v>
       </c>
       <c r="F49" t="n">
-        <v>829.99</v>
+        <v>829.49</v>
       </c>
       <c r="G49" t="n">
         <v>849.99</v>
@@ -1969,7 +1969,7 @@
         <v>829.99</v>
       </c>
       <c r="G50" t="n">
-        <v>849.99</v>
+        <v>848.49</v>
       </c>
     </row>
     <row r="51">
@@ -1997,10 +1997,10 @@
         <v>869.99</v>
       </c>
       <c r="F51" t="n">
-        <v>827.49</v>
+        <v>829.99</v>
       </c>
       <c r="G51" t="n">
-        <v>848.49</v>
+        <v>851.99</v>
       </c>
     </row>
     <row r="52">
@@ -2031,7 +2031,7 @@
         <v>829.99</v>
       </c>
       <c r="G52" t="n">
-        <v>849.99</v>
+        <v>851.99</v>
       </c>
     </row>
     <row r="53">
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>870.99</v>
+        <v>868.99</v>
       </c>
       <c r="F53" t="n">
-        <v>829.99</v>
+        <v>829.49</v>
       </c>
       <c r="G53" t="n">
-        <v>849.99</v>
+        <v>848.49</v>
       </c>
     </row>
     <row r="54">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>869.99</v>
+        <v>868.99</v>
       </c>
       <c r="F54" t="n">
         <v>829.99</v>
       </c>
       <c r="G54" t="n">
-        <v>848.49</v>
+        <v>849.99</v>
       </c>
     </row>
     <row r="55">
@@ -2121,10 +2121,10 @@
         <v>869.99</v>
       </c>
       <c r="F55" t="n">
-        <v>831.49</v>
+        <v>829.49</v>
       </c>
       <c r="G55" t="n">
-        <v>848.49</v>
+        <v>849.99</v>
       </c>
     </row>
     <row r="56">
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>870.99</v>
+        <v>868.99</v>
       </c>
       <c r="F56" t="n">
-        <v>831.49</v>
+        <v>829.99</v>
       </c>
       <c r="G56" t="n">
-        <v>851.99</v>
+        <v>849.99</v>
       </c>
     </row>
     <row r="57">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>869.99</v>
+        <v>868.99</v>
       </c>
       <c r="F57" t="n">
-        <v>827.49</v>
+        <v>829.49</v>
       </c>
       <c r="G57" t="n">
-        <v>849.99</v>
+        <v>851.99</v>
       </c>
     </row>
     <row r="58">
@@ -2214,7 +2214,7 @@
         <v>869.99</v>
       </c>
       <c r="F58" t="n">
-        <v>831.49</v>
+        <v>829.99</v>
       </c>
       <c r="G58" t="n">
         <v>849.99</v>
@@ -2245,7 +2245,7 @@
         <v>869.99</v>
       </c>
       <c r="F59" t="n">
-        <v>827.49</v>
+        <v>829.99</v>
       </c>
       <c r="G59" t="n">
         <v>849.99</v>
@@ -2273,13 +2273,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>869.99</v>
+        <v>868.99</v>
       </c>
       <c r="F60" t="n">
-        <v>827.49</v>
+        <v>829.99</v>
       </c>
       <c r="G60" t="n">
-        <v>848.49</v>
+        <v>849.99</v>
       </c>
     </row>
     <row r="61">
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>869.99</v>
+        <v>868.99</v>
       </c>
       <c r="F61" t="n">
-        <v>827.49</v>
+        <v>831.49</v>
       </c>
       <c r="G61" t="n">
         <v>849.99</v>
@@ -2335,13 +2335,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="F62" t="n">
-        <v>1300.5</v>
+        <v>1299</v>
       </c>
       <c r="G62" t="n">
-        <v>1351</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="63">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="F63" t="n">
-        <v>1299</v>
+        <v>1298.5</v>
       </c>
       <c r="G63" t="n">
         <v>1351</v>
@@ -2397,13 +2397,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="F64" t="n">
-        <v>1296.5</v>
+        <v>1300.5</v>
       </c>
       <c r="G64" t="n">
-        <v>1349</v>
+        <v>1347.5</v>
       </c>
     </row>
     <row r="65">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="F65" t="n">
-        <v>1299</v>
+        <v>1300.5</v>
       </c>
       <c r="G65" t="n">
-        <v>1349</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="66">
@@ -2459,13 +2459,13 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="F66" t="n">
         <v>1299</v>
       </c>
       <c r="G66" t="n">
-        <v>1347.5</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="67">
@@ -2490,13 +2490,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="F67" t="n">
-        <v>1300.5</v>
+        <v>1299</v>
       </c>
       <c r="G67" t="n">
-        <v>1351</v>
+        <v>1347.5</v>
       </c>
     </row>
     <row r="68">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="F68" t="n">
-        <v>1299</v>
+        <v>1298.5</v>
       </c>
       <c r="G68" t="n">
-        <v>1349</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="69">
@@ -2552,13 +2552,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="F69" t="n">
-        <v>1299</v>
+        <v>1296.5</v>
       </c>
       <c r="G69" t="n">
-        <v>1351</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="70">
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="F70" t="n">
-        <v>1300.5</v>
+        <v>1299</v>
       </c>
       <c r="G70" t="n">
-        <v>1349</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="71">
@@ -2614,13 +2614,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="F71" t="n">
-        <v>1298.5</v>
+        <v>1296.5</v>
       </c>
       <c r="G71" t="n">
-        <v>1347.5</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="72">
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="F72" t="n">
-        <v>1299</v>
+        <v>1296.5</v>
       </c>
       <c r="G72" t="n">
         <v>1351</v>
@@ -2676,13 +2676,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="F73" t="n">
         <v>1299</v>
       </c>
       <c r="G73" t="n">
-        <v>1349</v>
+        <v>1347.5</v>
       </c>
     </row>
     <row r="74">
@@ -2710,7 +2710,7 @@
         <v>1399</v>
       </c>
       <c r="F74" t="n">
-        <v>1299</v>
+        <v>1298.5</v>
       </c>
       <c r="G74" t="n">
         <v>1351</v>
@@ -2741,10 +2741,10 @@
         <v>1399</v>
       </c>
       <c r="F75" t="n">
-        <v>1299</v>
+        <v>1298.5</v>
       </c>
       <c r="G75" t="n">
-        <v>1351</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="76">
@@ -2772,10 +2772,10 @@
         <v>1399</v>
       </c>
       <c r="F76" t="n">
-        <v>1296.5</v>
+        <v>1300.5</v>
       </c>
       <c r="G76" t="n">
-        <v>1349</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="77">
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="F77" t="n">
         <v>1299</v>
@@ -2831,13 +2831,13 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="F78" t="n">
-        <v>1296.5</v>
+        <v>1299</v>
       </c>
       <c r="G78" t="n">
-        <v>1351</v>
+        <v>1347.5</v>
       </c>
     </row>
     <row r="79">
@@ -2865,10 +2865,10 @@
         <v>1399</v>
       </c>
       <c r="F79" t="n">
-        <v>1296.5</v>
+        <v>1299</v>
       </c>
       <c r="G79" t="n">
-        <v>1349</v>
+        <v>1347.5</v>
       </c>
     </row>
     <row r="80">
@@ -2896,7 +2896,7 @@
         <v>1399</v>
       </c>
       <c r="F80" t="n">
-        <v>1298.5</v>
+        <v>1296.5</v>
       </c>
       <c r="G80" t="n">
         <v>1347.5</v>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="F81" t="n">
-        <v>1296.5</v>
+        <v>1300.5</v>
       </c>
       <c r="G81" t="n">
         <v>1349</v>
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="F82" t="n">
-        <v>1300.5</v>
+        <v>1298.5</v>
       </c>
       <c r="G82" t="n">
-        <v>1347.5</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="83">
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="F84" t="n">
         <v>1299</v>
@@ -3048,13 +3048,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="F85" t="n">
-        <v>1298.5</v>
+        <v>1299</v>
       </c>
       <c r="G85" t="n">
-        <v>1347.5</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="86">
@@ -3085,7 +3085,7 @@
         <v>1299</v>
       </c>
       <c r="G86" t="n">
-        <v>1349</v>
+        <v>1347.5</v>
       </c>
     </row>
     <row r="87">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="F87" t="n">
         <v>1299</v>
       </c>
       <c r="G87" t="n">
-        <v>1349</v>
+        <v>1347.5</v>
       </c>
     </row>
     <row r="88">
@@ -3147,7 +3147,7 @@
         <v>1299</v>
       </c>
       <c r="G88" t="n">
-        <v>1347.5</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="89">
@@ -3172,13 +3172,13 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="F89" t="n">
-        <v>1300.5</v>
+        <v>1299</v>
       </c>
       <c r="G89" t="n">
-        <v>1351</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="90">
@@ -3206,7 +3206,7 @@
         <v>1399</v>
       </c>
       <c r="F90" t="n">
-        <v>1300.5</v>
+        <v>1296.5</v>
       </c>
       <c r="G90" t="n">
         <v>1347.5</v>
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="F91" t="n">
-        <v>1299</v>
+        <v>1298.5</v>
       </c>
       <c r="G91" t="n">
         <v>1347.5</v>
@@ -3268,10 +3268,10 @@
         <v>550</v>
       </c>
       <c r="F92" t="n">
-        <v>499</v>
+        <v>496.5</v>
       </c>
       <c r="G92" t="n">
-        <v>529</v>
+        <v>527.5</v>
       </c>
     </row>
     <row r="93">
@@ -3299,7 +3299,7 @@
         <v>549</v>
       </c>
       <c r="F93" t="n">
-        <v>498.5</v>
+        <v>499</v>
       </c>
       <c r="G93" t="n">
         <v>529</v>
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F94" t="n">
-        <v>496.5</v>
+        <v>498.5</v>
       </c>
       <c r="G94" t="n">
         <v>531</v>
@@ -3358,13 +3358,13 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F95" t="n">
-        <v>500.5</v>
+        <v>499</v>
       </c>
       <c r="G95" t="n">
-        <v>527.5</v>
+        <v>529</v>
       </c>
     </row>
     <row r="96">
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F96" t="n">
-        <v>499</v>
+        <v>500.5</v>
       </c>
       <c r="G96" t="n">
         <v>531</v>
@@ -3426,7 +3426,7 @@
         <v>499</v>
       </c>
       <c r="G97" t="n">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="98">
@@ -3457,7 +3457,7 @@
         <v>499</v>
       </c>
       <c r="G98" t="n">
-        <v>527.5</v>
+        <v>529</v>
       </c>
     </row>
     <row r="99">
@@ -3482,13 +3482,13 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F99" t="n">
         <v>499</v>
       </c>
       <c r="G99" t="n">
-        <v>527.5</v>
+        <v>529</v>
       </c>
     </row>
     <row r="100">
@@ -3516,7 +3516,7 @@
         <v>549</v>
       </c>
       <c r="F100" t="n">
-        <v>498.5</v>
+        <v>496.5</v>
       </c>
       <c r="G100" t="n">
         <v>527.5</v>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F101" t="n">
-        <v>498.5</v>
+        <v>500.5</v>
       </c>
       <c r="G101" t="n">
         <v>529</v>
@@ -3575,13 +3575,13 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="F102" t="n">
-        <v>496.5</v>
+        <v>498.5</v>
       </c>
       <c r="G102" t="n">
-        <v>527.5</v>
+        <v>531</v>
       </c>
     </row>
     <row r="103">
@@ -3609,10 +3609,10 @@
         <v>549</v>
       </c>
       <c r="F103" t="n">
-        <v>500.5</v>
+        <v>499</v>
       </c>
       <c r="G103" t="n">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="104">
@@ -3640,10 +3640,10 @@
         <v>549</v>
       </c>
       <c r="F104" t="n">
-        <v>500.5</v>
+        <v>496.5</v>
       </c>
       <c r="G104" t="n">
-        <v>527.5</v>
+        <v>529</v>
       </c>
     </row>
     <row r="105">
@@ -3668,7 +3668,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F105" t="n">
         <v>500.5</v>
@@ -3705,7 +3705,7 @@
         <v>499</v>
       </c>
       <c r="G106" t="n">
-        <v>527.5</v>
+        <v>531</v>
       </c>
     </row>
     <row r="107">
@@ -3730,13 +3730,13 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F107" t="n">
-        <v>500.5</v>
+        <v>499</v>
       </c>
       <c r="G107" t="n">
-        <v>529</v>
+        <v>527.5</v>
       </c>
     </row>
     <row r="108">
@@ -3764,10 +3764,10 @@
         <v>549</v>
       </c>
       <c r="F108" t="n">
-        <v>499</v>
+        <v>500.5</v>
       </c>
       <c r="G108" t="n">
-        <v>527.5</v>
+        <v>529</v>
       </c>
     </row>
     <row r="109">
@@ -3823,13 +3823,13 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="F110" t="n">
         <v>498.5</v>
       </c>
       <c r="G110" t="n">
-        <v>527.5</v>
+        <v>531</v>
       </c>
     </row>
     <row r="111">
@@ -3854,13 +3854,13 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F111" t="n">
-        <v>498.5</v>
+        <v>499</v>
       </c>
       <c r="G111" t="n">
-        <v>527.5</v>
+        <v>529</v>
       </c>
     </row>
     <row r="112">
@@ -3885,13 +3885,13 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F112" t="n">
-        <v>500.5</v>
+        <v>498.5</v>
       </c>
       <c r="G112" t="n">
-        <v>531</v>
+        <v>527.5</v>
       </c>
     </row>
     <row r="113">
@@ -3919,10 +3919,10 @@
         <v>549</v>
       </c>
       <c r="F113" t="n">
-        <v>496.5</v>
+        <v>500.5</v>
       </c>
       <c r="G113" t="n">
-        <v>527.5</v>
+        <v>529</v>
       </c>
     </row>
     <row r="114">
@@ -3950,10 +3950,10 @@
         <v>549</v>
       </c>
       <c r="F114" t="n">
-        <v>496.5</v>
+        <v>499</v>
       </c>
       <c r="G114" t="n">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="115">
@@ -3978,13 +3978,13 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F115" t="n">
-        <v>500.5</v>
+        <v>499</v>
       </c>
       <c r="G115" t="n">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="116">
@@ -4009,13 +4009,13 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F116" t="n">
-        <v>500.5</v>
+        <v>498.5</v>
       </c>
       <c r="G116" t="n">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="117">
@@ -4046,7 +4046,7 @@
         <v>499</v>
       </c>
       <c r="G117" t="n">
-        <v>529</v>
+        <v>527.5</v>
       </c>
     </row>
     <row r="118">
@@ -4102,13 +4102,13 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F119" t="n">
-        <v>496.5</v>
+        <v>499</v>
       </c>
       <c r="G119" t="n">
-        <v>527.5</v>
+        <v>529</v>
       </c>
     </row>
     <row r="120">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F120" t="n">
-        <v>496.5</v>
+        <v>499</v>
       </c>
       <c r="G120" t="n">
         <v>531</v>
@@ -4164,7 +4164,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F121" t="n">
         <v>499</v>
@@ -4201,7 +4201,7 @@
         <v>1199</v>
       </c>
       <c r="G122" t="n">
-        <v>1247.5</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="123">
@@ -4229,10 +4229,10 @@
         <v>1299</v>
       </c>
       <c r="F123" t="n">
-        <v>1198.5</v>
+        <v>1200.5</v>
       </c>
       <c r="G123" t="n">
-        <v>1247.5</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="124">
@@ -4260,7 +4260,7 @@
         <v>1299</v>
       </c>
       <c r="F124" t="n">
-        <v>1200.5</v>
+        <v>1199</v>
       </c>
       <c r="G124" t="n">
         <v>1247.5</v>
@@ -4291,10 +4291,10 @@
         <v>1299</v>
       </c>
       <c r="F125" t="n">
-        <v>1196.5</v>
+        <v>1199</v>
       </c>
       <c r="G125" t="n">
-        <v>1249</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="126">
@@ -4325,7 +4325,7 @@
         <v>1198.5</v>
       </c>
       <c r="G126" t="n">
-        <v>1247.5</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="127">
@@ -4350,13 +4350,13 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="F127" t="n">
         <v>1199</v>
       </c>
       <c r="G127" t="n">
-        <v>1249</v>
+        <v>1247.5</v>
       </c>
     </row>
     <row r="128">
@@ -4384,7 +4384,7 @@
         <v>1299</v>
       </c>
       <c r="F128" t="n">
-        <v>1200.5</v>
+        <v>1199</v>
       </c>
       <c r="G128" t="n">
         <v>1249</v>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="F129" t="n">
-        <v>1200.5</v>
+        <v>1198.5</v>
       </c>
       <c r="G129" t="n">
         <v>1249</v>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F130" t="n">
-        <v>1198.5</v>
+        <v>1199</v>
       </c>
       <c r="G130" t="n">
-        <v>1247.5</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="131">
@@ -4477,10 +4477,10 @@
         <v>1299</v>
       </c>
       <c r="F131" t="n">
-        <v>1198.5</v>
+        <v>1199</v>
       </c>
       <c r="G131" t="n">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="132">
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F132" t="n">
-        <v>1196.5</v>
+        <v>1199</v>
       </c>
       <c r="G132" t="n">
         <v>1249</v>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="F133" t="n">
-        <v>1199</v>
+        <v>1198.5</v>
       </c>
       <c r="G133" t="n">
         <v>1247.5</v>
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="F134" t="n">
-        <v>1199</v>
+        <v>1196.5</v>
       </c>
       <c r="G134" t="n">
-        <v>1249</v>
+        <v>1247.5</v>
       </c>
     </row>
     <row r="135">
@@ -4598,13 +4598,13 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F135" t="n">
         <v>1198.5</v>
       </c>
       <c r="G135" t="n">
-        <v>1249</v>
+        <v>1247.5</v>
       </c>
     </row>
     <row r="136">
@@ -4635,7 +4635,7 @@
         <v>1199</v>
       </c>
       <c r="G136" t="n">
-        <v>1251</v>
+        <v>1247.5</v>
       </c>
     </row>
     <row r="137">
@@ -4663,10 +4663,10 @@
         <v>1299</v>
       </c>
       <c r="F137" t="n">
-        <v>1199</v>
+        <v>1198.5</v>
       </c>
       <c r="G137" t="n">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="138">
@@ -4691,13 +4691,13 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="F138" t="n">
         <v>1199</v>
       </c>
       <c r="G138" t="n">
-        <v>1249</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="139">
@@ -4722,13 +4722,13 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="F139" t="n">
         <v>1199</v>
       </c>
       <c r="G139" t="n">
-        <v>1247.5</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="140">
@@ -4759,7 +4759,7 @@
         <v>1198.5</v>
       </c>
       <c r="G140" t="n">
-        <v>1249</v>
+        <v>1247.5</v>
       </c>
     </row>
     <row r="141">
@@ -4784,13 +4784,13 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F141" t="n">
-        <v>1196.5</v>
+        <v>1200.5</v>
       </c>
       <c r="G141" t="n">
-        <v>1249</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="142">
@@ -4815,13 +4815,13 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F142" t="n">
-        <v>1198.5</v>
+        <v>1196.5</v>
       </c>
       <c r="G142" t="n">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="143">
@@ -4846,13 +4846,13 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="F143" t="n">
-        <v>1199</v>
+        <v>1196.5</v>
       </c>
       <c r="G143" t="n">
-        <v>1247.5</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="144">
@@ -4883,7 +4883,7 @@
         <v>1199</v>
       </c>
       <c r="G144" t="n">
-        <v>1247.5</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="145">
@@ -4911,10 +4911,10 @@
         <v>1299</v>
       </c>
       <c r="F145" t="n">
-        <v>1199</v>
+        <v>1200.5</v>
       </c>
       <c r="G145" t="n">
-        <v>1247.5</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="146">
@@ -4942,7 +4942,7 @@
         <v>1300</v>
       </c>
       <c r="F146" t="n">
-        <v>1199</v>
+        <v>1198.5</v>
       </c>
       <c r="G146" t="n">
         <v>1249</v>
@@ -4970,13 +4970,13 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="F147" t="n">
-        <v>1200.5</v>
+        <v>1199</v>
       </c>
       <c r="G147" t="n">
-        <v>1249</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="148">
@@ -5001,13 +5001,13 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="F148" t="n">
-        <v>1196.5</v>
+        <v>1199</v>
       </c>
       <c r="G148" t="n">
-        <v>1249</v>
+        <v>1247.5</v>
       </c>
     </row>
     <row r="149">
@@ -5035,7 +5035,7 @@
         <v>1298</v>
       </c>
       <c r="F149" t="n">
-        <v>1198.5</v>
+        <v>1199</v>
       </c>
       <c r="G149" t="n">
         <v>1251</v>
@@ -5069,7 +5069,7 @@
         <v>1199</v>
       </c>
       <c r="G150" t="n">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="151">
@@ -5100,7 +5100,7 @@
         <v>1199</v>
       </c>
       <c r="G151" t="n">
-        <v>1249</v>
+        <v>1247.5</v>
       </c>
     </row>
     <row r="152">
@@ -5131,7 +5131,7 @@
         <v>1149.99</v>
       </c>
       <c r="G152" t="n">
-        <v>1181.99</v>
+        <v>1178.49</v>
       </c>
     </row>
     <row r="153">
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1220.99</v>
+        <v>1219.99</v>
       </c>
       <c r="F153" t="n">
-        <v>1149.99</v>
+        <v>1149.49</v>
       </c>
       <c r="G153" t="n">
         <v>1179.99</v>
@@ -5187,13 +5187,13 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1219.99</v>
+        <v>1218.99</v>
       </c>
       <c r="F154" t="n">
-        <v>1147.49</v>
+        <v>1149.49</v>
       </c>
       <c r="G154" t="n">
-        <v>1178.49</v>
+        <v>1181.99</v>
       </c>
     </row>
     <row r="155">
@@ -5224,7 +5224,7 @@
         <v>1149.99</v>
       </c>
       <c r="G155" t="n">
-        <v>1178.49</v>
+        <v>1181.99</v>
       </c>
     </row>
     <row r="156">
@@ -5252,10 +5252,10 @@
         <v>1219.99</v>
       </c>
       <c r="F156" t="n">
-        <v>1149.49</v>
+        <v>1151.49</v>
       </c>
       <c r="G156" t="n">
-        <v>1179.99</v>
+        <v>1178.49</v>
       </c>
     </row>
     <row r="157">
@@ -5280,13 +5280,13 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1218.99</v>
+        <v>1219.99</v>
       </c>
       <c r="F157" t="n">
         <v>1149.99</v>
       </c>
       <c r="G157" t="n">
-        <v>1181.99</v>
+        <v>1178.49</v>
       </c>
     </row>
     <row r="158">
@@ -5317,7 +5317,7 @@
         <v>1149.99</v>
       </c>
       <c r="G158" t="n">
-        <v>1178.49</v>
+        <v>1181.99</v>
       </c>
     </row>
     <row r="159">
@@ -5345,10 +5345,10 @@
         <v>1219.99</v>
       </c>
       <c r="F159" t="n">
-        <v>1151.49</v>
+        <v>1149.49</v>
       </c>
       <c r="G159" t="n">
-        <v>1178.49</v>
+        <v>1181.99</v>
       </c>
     </row>
     <row r="160">
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1219.99</v>
+        <v>1218.99</v>
       </c>
       <c r="F160" t="n">
-        <v>1149.99</v>
+        <v>1147.49</v>
       </c>
       <c r="G160" t="n">
         <v>1179.99</v>
@@ -5404,7 +5404,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1219.99</v>
+        <v>1218.99</v>
       </c>
       <c r="F161" t="n">
         <v>1149.99</v>
@@ -5435,13 +5435,13 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1220.99</v>
+        <v>1219.99</v>
       </c>
       <c r="F162" t="n">
-        <v>1151.49</v>
+        <v>1149.49</v>
       </c>
       <c r="G162" t="n">
-        <v>1178.49</v>
+        <v>1181.99</v>
       </c>
     </row>
     <row r="163">
@@ -5472,7 +5472,7 @@
         <v>1151.49</v>
       </c>
       <c r="G163" t="n">
-        <v>1179.99</v>
+        <v>1178.49</v>
       </c>
     </row>
     <row r="164">
@@ -5500,10 +5500,10 @@
         <v>1219.99</v>
       </c>
       <c r="F164" t="n">
-        <v>1151.49</v>
+        <v>1149.99</v>
       </c>
       <c r="G164" t="n">
-        <v>1179.99</v>
+        <v>1181.99</v>
       </c>
     </row>
     <row r="165">
@@ -5531,10 +5531,10 @@
         <v>1219.99</v>
       </c>
       <c r="F165" t="n">
-        <v>1149.99</v>
+        <v>1149.49</v>
       </c>
       <c r="G165" t="n">
-        <v>1181.99</v>
+        <v>1179.99</v>
       </c>
     </row>
     <row r="166">
@@ -5559,13 +5559,13 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1218.99</v>
+        <v>1219.99</v>
       </c>
       <c r="F166" t="n">
         <v>1151.49</v>
       </c>
       <c r="G166" t="n">
-        <v>1181.99</v>
+        <v>1179.99</v>
       </c>
     </row>
     <row r="167">
@@ -5596,7 +5596,7 @@
         <v>1151.49</v>
       </c>
       <c r="G167" t="n">
-        <v>1178.49</v>
+        <v>1181.99</v>
       </c>
     </row>
     <row r="168">
@@ -5624,10 +5624,10 @@
         <v>1219.99</v>
       </c>
       <c r="F168" t="n">
-        <v>1149.99</v>
+        <v>1147.49</v>
       </c>
       <c r="G168" t="n">
-        <v>1181.99</v>
+        <v>1179.99</v>
       </c>
     </row>
     <row r="169">
@@ -5686,7 +5686,7 @@
         <v>1219.99</v>
       </c>
       <c r="F170" t="n">
-        <v>1151.49</v>
+        <v>1147.49</v>
       </c>
       <c r="G170" t="n">
         <v>1178.49</v>
@@ -5714,13 +5714,13 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1218.99</v>
+        <v>1220.99</v>
       </c>
       <c r="F171" t="n">
         <v>1149.99</v>
       </c>
       <c r="G171" t="n">
-        <v>1179.99</v>
+        <v>1181.99</v>
       </c>
     </row>
     <row r="172">
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1220.99</v>
+        <v>1218.99</v>
       </c>
       <c r="F172" t="n">
-        <v>1149.99</v>
+        <v>1147.49</v>
       </c>
       <c r="G172" t="n">
         <v>1179.99</v>
@@ -5779,10 +5779,10 @@
         <v>1219.99</v>
       </c>
       <c r="F173" t="n">
-        <v>1149.99</v>
+        <v>1147.49</v>
       </c>
       <c r="G173" t="n">
-        <v>1181.99</v>
+        <v>1179.99</v>
       </c>
     </row>
     <row r="174">
@@ -5810,10 +5810,10 @@
         <v>1219.99</v>
       </c>
       <c r="F174" t="n">
-        <v>1151.49</v>
+        <v>1149.99</v>
       </c>
       <c r="G174" t="n">
-        <v>1179.99</v>
+        <v>1181.99</v>
       </c>
     </row>
     <row r="175">
@@ -5838,13 +5838,13 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1218.99</v>
+        <v>1220.99</v>
       </c>
       <c r="F175" t="n">
-        <v>1149.99</v>
+        <v>1149.49</v>
       </c>
       <c r="G175" t="n">
-        <v>1181.99</v>
+        <v>1178.49</v>
       </c>
     </row>
     <row r="176">
@@ -5869,13 +5869,13 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1220.99</v>
+        <v>1219.99</v>
       </c>
       <c r="F176" t="n">
-        <v>1149.99</v>
+        <v>1151.49</v>
       </c>
       <c r="G176" t="n">
-        <v>1181.99</v>
+        <v>1178.49</v>
       </c>
     </row>
     <row r="177">
@@ -5903,7 +5903,7 @@
         <v>1220.99</v>
       </c>
       <c r="F177" t="n">
-        <v>1151.49</v>
+        <v>1149.49</v>
       </c>
       <c r="G177" t="n">
         <v>1181.99</v>
@@ -5931,13 +5931,13 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1220.99</v>
+        <v>1219.99</v>
       </c>
       <c r="F178" t="n">
-        <v>1151.49</v>
+        <v>1147.49</v>
       </c>
       <c r="G178" t="n">
-        <v>1181.99</v>
+        <v>1178.49</v>
       </c>
     </row>
     <row r="179">
@@ -5962,13 +5962,13 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1220.99</v>
+        <v>1218.99</v>
       </c>
       <c r="F179" t="n">
-        <v>1149.99</v>
+        <v>1151.49</v>
       </c>
       <c r="G179" t="n">
-        <v>1178.49</v>
+        <v>1179.99</v>
       </c>
     </row>
     <row r="180">
@@ -5993,10 +5993,10 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1219.99</v>
+        <v>1218.99</v>
       </c>
       <c r="F180" t="n">
-        <v>1147.49</v>
+        <v>1149.99</v>
       </c>
       <c r="G180" t="n">
         <v>1178.49</v>
@@ -6024,10 +6024,10 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1220.99</v>
+        <v>1219.99</v>
       </c>
       <c r="F181" t="n">
-        <v>1151.49</v>
+        <v>1147.49</v>
       </c>
       <c r="G181" t="n">
         <v>1179.99</v>
@@ -6055,13 +6055,13 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1799.99</v>
+        <v>1200.99</v>
       </c>
       <c r="F182" t="n">
-        <v>1730.5</v>
+        <v>1099.99</v>
       </c>
       <c r="G182" t="n">
-        <v>1751.99</v>
+        <v>1151.99</v>
       </c>
     </row>
     <row r="183">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1799.99</v>
+        <v>1200.99</v>
       </c>
       <c r="F183" t="n">
-        <v>1729</v>
+        <v>1099.49</v>
       </c>
       <c r="G183" t="n">
-        <v>1749.99</v>
+        <v>1148.49</v>
       </c>
     </row>
     <row r="184">
@@ -6117,13 +6117,13 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1799.99</v>
+        <v>1198.99</v>
       </c>
       <c r="F184" t="n">
-        <v>1726.5</v>
+        <v>1101.49</v>
       </c>
       <c r="G184" t="n">
-        <v>1751.99</v>
+        <v>1149.99</v>
       </c>
     </row>
     <row r="185">
@@ -6148,13 +6148,13 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1799.99</v>
+        <v>1200.99</v>
       </c>
       <c r="F185" t="n">
-        <v>1729</v>
+        <v>1101.49</v>
       </c>
       <c r="G185" t="n">
-        <v>1749.99</v>
+        <v>1151.99</v>
       </c>
     </row>
     <row r="186">
@@ -6179,13 +6179,13 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1800.99</v>
+        <v>1198.99</v>
       </c>
       <c r="F186" t="n">
-        <v>1730.5</v>
+        <v>1099.99</v>
       </c>
       <c r="G186" t="n">
-        <v>1751.99</v>
+        <v>1148.49</v>
       </c>
     </row>
     <row r="187">
@@ -6210,13 +6210,13 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1799.99</v>
+        <v>1199.99</v>
       </c>
       <c r="F187" t="n">
-        <v>1728.5</v>
+        <v>1099.49</v>
       </c>
       <c r="G187" t="n">
-        <v>1749.99</v>
+        <v>1149.99</v>
       </c>
     </row>
     <row r="188">
@@ -6241,13 +6241,13 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1799.99</v>
+        <v>1200.99</v>
       </c>
       <c r="F188" t="n">
-        <v>1730.5</v>
+        <v>1099.99</v>
       </c>
       <c r="G188" t="n">
-        <v>1749.99</v>
+        <v>1148.49</v>
       </c>
     </row>
     <row r="189">
@@ -6272,13 +6272,13 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1798.99</v>
+        <v>1198.99</v>
       </c>
       <c r="F189" t="n">
-        <v>1729</v>
+        <v>1101.49</v>
       </c>
       <c r="G189" t="n">
-        <v>1749.99</v>
+        <v>1148.49</v>
       </c>
     </row>
     <row r="190">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1800.99</v>
+        <v>1198.99</v>
       </c>
       <c r="F190" t="n">
-        <v>1729</v>
+        <v>1097.49</v>
       </c>
       <c r="G190" t="n">
-        <v>1751.99</v>
+        <v>1149.99</v>
       </c>
     </row>
     <row r="191">
@@ -6334,13 +6334,13 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1798.99</v>
+        <v>1198.99</v>
       </c>
       <c r="F191" t="n">
-        <v>1730.5</v>
+        <v>1097.49</v>
       </c>
       <c r="G191" t="n">
-        <v>1749.99</v>
+        <v>1151.99</v>
       </c>
     </row>
     <row r="192">
@@ -6365,13 +6365,13 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1799.99</v>
+        <v>1198.99</v>
       </c>
       <c r="F192" t="n">
-        <v>1730.5</v>
+        <v>1099.99</v>
       </c>
       <c r="G192" t="n">
-        <v>1748.49</v>
+        <v>1149.99</v>
       </c>
     </row>
     <row r="193">
@@ -6396,13 +6396,13 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1799.99</v>
+        <v>1199.99</v>
       </c>
       <c r="F193" t="n">
-        <v>1730.5</v>
+        <v>1099.49</v>
       </c>
       <c r="G193" t="n">
-        <v>1749.99</v>
+        <v>1151.99</v>
       </c>
     </row>
     <row r="194">
@@ -6427,13 +6427,13 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1798.99</v>
+        <v>1199.99</v>
       </c>
       <c r="F194" t="n">
-        <v>1728.5</v>
+        <v>1099.99</v>
       </c>
       <c r="G194" t="n">
-        <v>1749.99</v>
+        <v>1148.49</v>
       </c>
     </row>
     <row r="195">
@@ -6458,13 +6458,13 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1799.99</v>
+        <v>1199.99</v>
       </c>
       <c r="F195" t="n">
-        <v>1728.5</v>
+        <v>1101.49</v>
       </c>
       <c r="G195" t="n">
-        <v>1749.99</v>
+        <v>1148.49</v>
       </c>
     </row>
     <row r="196">
@@ -6489,13 +6489,13 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1800.99</v>
+        <v>1198.99</v>
       </c>
       <c r="F196" t="n">
-        <v>1726.5</v>
+        <v>1099.49</v>
       </c>
       <c r="G196" t="n">
-        <v>1748.49</v>
+        <v>1149.99</v>
       </c>
     </row>
     <row r="197">
@@ -6520,13 +6520,13 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1800.99</v>
+        <v>1199.99</v>
       </c>
       <c r="F197" t="n">
-        <v>1726.5</v>
+        <v>1099.99</v>
       </c>
       <c r="G197" t="n">
-        <v>1748.49</v>
+        <v>1149.99</v>
       </c>
     </row>
     <row r="198">
@@ -6551,13 +6551,13 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1799.99</v>
+        <v>1198.99</v>
       </c>
       <c r="F198" t="n">
-        <v>1726.5</v>
+        <v>1097.49</v>
       </c>
       <c r="G198" t="n">
-        <v>1748.49</v>
+        <v>1151.99</v>
       </c>
     </row>
     <row r="199">
@@ -6582,13 +6582,13 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1799.99</v>
+        <v>1199.99</v>
       </c>
       <c r="F199" t="n">
-        <v>1730.5</v>
+        <v>1101.49</v>
       </c>
       <c r="G199" t="n">
-        <v>1749.99</v>
+        <v>1149.99</v>
       </c>
     </row>
     <row r="200">
@@ -6613,13 +6613,13 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1800.99</v>
+        <v>1199.99</v>
       </c>
       <c r="F200" t="n">
-        <v>1728.5</v>
+        <v>1099.49</v>
       </c>
       <c r="G200" t="n">
-        <v>1751.99</v>
+        <v>1151.99</v>
       </c>
     </row>
     <row r="201">
@@ -6644,13 +6644,13 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>1799.99</v>
+        <v>1199.99</v>
       </c>
       <c r="F201" t="n">
-        <v>1730.5</v>
+        <v>1099.99</v>
       </c>
       <c r="G201" t="n">
-        <v>1749.99</v>
+        <v>1149.99</v>
       </c>
     </row>
     <row r="202">
@@ -6675,13 +6675,13 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1800.99</v>
+        <v>1200.99</v>
       </c>
       <c r="F202" t="n">
-        <v>1729</v>
+        <v>1099.99</v>
       </c>
       <c r="G202" t="n">
-        <v>1749.99</v>
+        <v>1148.49</v>
       </c>
     </row>
     <row r="203">
@@ -6706,13 +6706,13 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>1798.99</v>
+        <v>1199.99</v>
       </c>
       <c r="F203" t="n">
-        <v>1729</v>
+        <v>1099.99</v>
       </c>
       <c r="G203" t="n">
-        <v>1748.49</v>
+        <v>1149.99</v>
       </c>
     </row>
     <row r="204">
@@ -6737,13 +6737,13 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1799.99</v>
+        <v>1199.99</v>
       </c>
       <c r="F204" t="n">
-        <v>1730.5</v>
+        <v>1101.49</v>
       </c>
       <c r="G204" t="n">
-        <v>1749.99</v>
+        <v>1151.99</v>
       </c>
     </row>
     <row r="205">
@@ -6768,13 +6768,13 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1798.99</v>
+        <v>1199.99</v>
       </c>
       <c r="F205" t="n">
-        <v>1729</v>
+        <v>1101.49</v>
       </c>
       <c r="G205" t="n">
-        <v>1751.99</v>
+        <v>1151.99</v>
       </c>
     </row>
     <row r="206">
@@ -6799,13 +6799,13 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1798.99</v>
+        <v>1200.99</v>
       </c>
       <c r="F206" t="n">
-        <v>1729</v>
+        <v>1097.49</v>
       </c>
       <c r="G206" t="n">
-        <v>1751.99</v>
+        <v>1148.49</v>
       </c>
     </row>
     <row r="207">
@@ -6830,13 +6830,13 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>1798.99</v>
+        <v>1199.99</v>
       </c>
       <c r="F207" t="n">
-        <v>1728.5</v>
+        <v>1097.49</v>
       </c>
       <c r="G207" t="n">
-        <v>1749.99</v>
+        <v>1149.99</v>
       </c>
     </row>
     <row r="208">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1799.99</v>
+        <v>1199.99</v>
       </c>
       <c r="F208" t="n">
-        <v>1730.5</v>
+        <v>1099.49</v>
       </c>
       <c r="G208" t="n">
-        <v>1749.99</v>
+        <v>1149.99</v>
       </c>
     </row>
     <row r="209">
@@ -6892,13 +6892,13 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>1799.99</v>
+        <v>1198.99</v>
       </c>
       <c r="F209" t="n">
-        <v>1729</v>
+        <v>1099.99</v>
       </c>
       <c r="G209" t="n">
-        <v>1751.99</v>
+        <v>1148.49</v>
       </c>
     </row>
     <row r="210">
@@ -6923,13 +6923,13 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1800.99</v>
+        <v>1199.99</v>
       </c>
       <c r="F210" t="n">
-        <v>1730.5</v>
+        <v>1097.49</v>
       </c>
       <c r="G210" t="n">
-        <v>1751.99</v>
+        <v>1149.99</v>
       </c>
     </row>
     <row r="211">
@@ -6954,13 +6954,13 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>1798.99</v>
+        <v>1199.99</v>
       </c>
       <c r="F211" t="n">
-        <v>1728.5</v>
+        <v>1101.49</v>
       </c>
       <c r="G211" t="n">
-        <v>1749.99</v>
+        <v>1148.49</v>
       </c>
     </row>
     <row r="212">
@@ -6988,10 +6988,10 @@
         <v>649.99</v>
       </c>
       <c r="F212" t="n">
-        <v>547.49</v>
+        <v>549.49</v>
       </c>
       <c r="G212" t="n">
-        <v>601.99</v>
+        <v>598.49</v>
       </c>
     </row>
     <row r="213">
@@ -7016,13 +7016,13 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>650.99</v>
+        <v>649.99</v>
       </c>
       <c r="F213" t="n">
         <v>547.49</v>
       </c>
       <c r="G213" t="n">
-        <v>599.99</v>
+        <v>601.99</v>
       </c>
     </row>
     <row r="214">
@@ -7050,7 +7050,7 @@
         <v>649.99</v>
       </c>
       <c r="F214" t="n">
-        <v>549.99</v>
+        <v>551.49</v>
       </c>
       <c r="G214" t="n">
         <v>599.99</v>
@@ -7078,13 +7078,13 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>648.99</v>
+        <v>650.99</v>
       </c>
       <c r="F215" t="n">
-        <v>547.49</v>
+        <v>549.49</v>
       </c>
       <c r="G215" t="n">
-        <v>599.99</v>
+        <v>601.99</v>
       </c>
     </row>
     <row r="216">
@@ -7112,10 +7112,10 @@
         <v>648.99</v>
       </c>
       <c r="F216" t="n">
-        <v>547.49</v>
+        <v>551.49</v>
       </c>
       <c r="G216" t="n">
-        <v>601.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="217">
@@ -7140,13 +7140,13 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>649.99</v>
+        <v>650.99</v>
       </c>
       <c r="F217" t="n">
-        <v>549.99</v>
+        <v>549.49</v>
       </c>
       <c r="G217" t="n">
-        <v>601.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="218">
@@ -7174,7 +7174,7 @@
         <v>649.99</v>
       </c>
       <c r="F218" t="n">
-        <v>549.99</v>
+        <v>549.49</v>
       </c>
       <c r="G218" t="n">
         <v>599.99</v>
@@ -7205,10 +7205,10 @@
         <v>649.99</v>
       </c>
       <c r="F219" t="n">
-        <v>549.49</v>
+        <v>549.99</v>
       </c>
       <c r="G219" t="n">
-        <v>599.99</v>
+        <v>598.49</v>
       </c>
     </row>
     <row r="220">
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>648.99</v>
+        <v>649.99</v>
       </c>
       <c r="F220" t="n">
-        <v>549.99</v>
+        <v>551.49</v>
       </c>
       <c r="G220" t="n">
         <v>599.99</v>
@@ -7267,7 +7267,7 @@
         <v>649.99</v>
       </c>
       <c r="F221" t="n">
-        <v>547.49</v>
+        <v>549.49</v>
       </c>
       <c r="G221" t="n">
         <v>601.99</v>
@@ -7298,7 +7298,7 @@
         <v>650.99</v>
       </c>
       <c r="F222" t="n">
-        <v>549.49</v>
+        <v>549.99</v>
       </c>
       <c r="G222" t="n">
         <v>599.99</v>
@@ -7326,13 +7326,13 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>650.99</v>
+        <v>649.99</v>
       </c>
       <c r="F223" t="n">
-        <v>549.99</v>
+        <v>551.49</v>
       </c>
       <c r="G223" t="n">
-        <v>599.99</v>
+        <v>601.99</v>
       </c>
     </row>
     <row r="224">
@@ -7357,10 +7357,10 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>649.99</v>
+        <v>648.99</v>
       </c>
       <c r="F224" t="n">
-        <v>549.99</v>
+        <v>549.49</v>
       </c>
       <c r="G224" t="n">
         <v>599.99</v>
@@ -7388,13 +7388,13 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>648.99</v>
+        <v>649.99</v>
       </c>
       <c r="F225" t="n">
-        <v>549.99</v>
+        <v>551.49</v>
       </c>
       <c r="G225" t="n">
-        <v>599.99</v>
+        <v>598.49</v>
       </c>
     </row>
     <row r="226">
@@ -7422,7 +7422,7 @@
         <v>649.99</v>
       </c>
       <c r="F226" t="n">
-        <v>551.49</v>
+        <v>549.99</v>
       </c>
       <c r="G226" t="n">
         <v>599.99</v>
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>649.99</v>
+        <v>650.99</v>
       </c>
       <c r="F227" t="n">
-        <v>549.99</v>
+        <v>547.49</v>
       </c>
       <c r="G227" t="n">
         <v>599.99</v>
@@ -7487,7 +7487,7 @@
         <v>549.99</v>
       </c>
       <c r="G228" t="n">
-        <v>599.99</v>
+        <v>601.99</v>
       </c>
     </row>
     <row r="229">
@@ -7512,13 +7512,13 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>649.99</v>
+        <v>648.99</v>
       </c>
       <c r="F229" t="n">
-        <v>551.49</v>
+        <v>547.49</v>
       </c>
       <c r="G229" t="n">
-        <v>599.99</v>
+        <v>601.99</v>
       </c>
     </row>
     <row r="230">
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>650.99</v>
+        <v>649.99</v>
       </c>
       <c r="F230" t="n">
-        <v>549.99</v>
+        <v>547.49</v>
       </c>
       <c r="G230" t="n">
-        <v>598.49</v>
+        <v>601.99</v>
       </c>
     </row>
     <row r="231">
@@ -7574,10 +7574,10 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>650.99</v>
+        <v>648.99</v>
       </c>
       <c r="F231" t="n">
-        <v>551.49</v>
+        <v>549.99</v>
       </c>
       <c r="G231" t="n">
         <v>599.99</v>
@@ -7605,10 +7605,10 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>649.99</v>
+        <v>648.99</v>
       </c>
       <c r="F232" t="n">
-        <v>549.99</v>
+        <v>551.49</v>
       </c>
       <c r="G232" t="n">
         <v>601.99</v>
@@ -7636,13 +7636,13 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>650.99</v>
+        <v>648.99</v>
       </c>
       <c r="F233" t="n">
         <v>549.99</v>
       </c>
       <c r="G233" t="n">
-        <v>598.49</v>
+        <v>601.99</v>
       </c>
     </row>
     <row r="234">
@@ -7670,7 +7670,7 @@
         <v>649.99</v>
       </c>
       <c r="F234" t="n">
-        <v>549.49</v>
+        <v>547.49</v>
       </c>
       <c r="G234" t="n">
         <v>599.99</v>
@@ -7698,13 +7698,13 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>648.99</v>
+        <v>650.99</v>
       </c>
       <c r="F235" t="n">
-        <v>549.49</v>
+        <v>547.49</v>
       </c>
       <c r="G235" t="n">
-        <v>599.99</v>
+        <v>601.99</v>
       </c>
     </row>
     <row r="236">
@@ -7735,7 +7735,7 @@
         <v>551.49</v>
       </c>
       <c r="G236" t="n">
-        <v>599.99</v>
+        <v>598.49</v>
       </c>
     </row>
     <row r="237">
@@ -7760,10 +7760,10 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>648.99</v>
+        <v>649.99</v>
       </c>
       <c r="F237" t="n">
-        <v>549.99</v>
+        <v>547.49</v>
       </c>
       <c r="G237" t="n">
         <v>599.99</v>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>650.99</v>
+        <v>649.99</v>
       </c>
       <c r="F238" t="n">
-        <v>549.99</v>
+        <v>551.49</v>
       </c>
       <c r="G238" t="n">
         <v>598.49</v>
@@ -7825,10 +7825,10 @@
         <v>648.99</v>
       </c>
       <c r="F239" t="n">
-        <v>549.99</v>
+        <v>551.49</v>
       </c>
       <c r="G239" t="n">
-        <v>601.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="240">
@@ -7853,13 +7853,13 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>650.99</v>
+        <v>649.99</v>
       </c>
       <c r="F240" t="n">
         <v>549.49</v>
       </c>
       <c r="G240" t="n">
-        <v>598.49</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="241">
@@ -7887,10 +7887,10 @@
         <v>649.99</v>
       </c>
       <c r="F241" t="n">
-        <v>547.49</v>
+        <v>549.99</v>
       </c>
       <c r="G241" t="n">
-        <v>601.99</v>
+        <v>599.99</v>
       </c>
     </row>
     <row r="242">
@@ -7918,10 +7918,10 @@
         <v>379.99</v>
       </c>
       <c r="F242" t="n">
-        <v>329.5</v>
+        <v>327.5</v>
       </c>
       <c r="G242" t="n">
-        <v>350</v>
+        <v>346.5</v>
       </c>
     </row>
     <row r="243">
@@ -7952,7 +7952,7 @@
         <v>325.5</v>
       </c>
       <c r="G243" t="n">
-        <v>346.5</v>
+        <v>348</v>
       </c>
     </row>
     <row r="244">
@@ -7977,10 +7977,10 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>380.99</v>
+        <v>379.99</v>
       </c>
       <c r="F244" t="n">
-        <v>328</v>
+        <v>327.5</v>
       </c>
       <c r="G244" t="n">
         <v>348</v>
@@ -8008,13 +8008,13 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>378.99</v>
+        <v>380.99</v>
       </c>
       <c r="F245" t="n">
-        <v>328</v>
+        <v>329.5</v>
       </c>
       <c r="G245" t="n">
-        <v>346.5</v>
+        <v>350</v>
       </c>
     </row>
     <row r="246">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>379.99</v>
+        <v>378.99</v>
       </c>
       <c r="F246" t="n">
-        <v>329.5</v>
+        <v>328</v>
       </c>
       <c r="G246" t="n">
-        <v>348</v>
+        <v>346.5</v>
       </c>
     </row>
     <row r="247">
@@ -8070,10 +8070,10 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>378.99</v>
+        <v>379.99</v>
       </c>
       <c r="F247" t="n">
-        <v>327.5</v>
+        <v>328</v>
       </c>
       <c r="G247" t="n">
         <v>348</v>
@@ -8104,10 +8104,10 @@
         <v>379.99</v>
       </c>
       <c r="F248" t="n">
-        <v>328</v>
+        <v>325.5</v>
       </c>
       <c r="G248" t="n">
-        <v>348</v>
+        <v>346.5</v>
       </c>
     </row>
     <row r="249">
@@ -8135,7 +8135,7 @@
         <v>379.99</v>
       </c>
       <c r="F249" t="n">
-        <v>325.5</v>
+        <v>329.5</v>
       </c>
       <c r="G249" t="n">
         <v>348</v>
@@ -8166,7 +8166,7 @@
         <v>379.99</v>
       </c>
       <c r="F250" t="n">
-        <v>328</v>
+        <v>327.5</v>
       </c>
       <c r="G250" t="n">
         <v>346.5</v>
@@ -8194,10 +8194,10 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>378.99</v>
+        <v>380.99</v>
       </c>
       <c r="F251" t="n">
-        <v>327.5</v>
+        <v>328</v>
       </c>
       <c r="G251" t="n">
         <v>348</v>
@@ -8225,7 +8225,7 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>378.99</v>
+        <v>379.99</v>
       </c>
       <c r="F252" t="n">
         <v>327.5</v>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>379.99</v>
+        <v>378.99</v>
       </c>
       <c r="F253" t="n">
         <v>327.5</v>
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>379.99</v>
+        <v>380.99</v>
       </c>
       <c r="F254" t="n">
-        <v>325.5</v>
+        <v>328</v>
       </c>
       <c r="G254" t="n">
-        <v>348</v>
+        <v>346.5</v>
       </c>
     </row>
     <row r="255">
@@ -8318,10 +8318,10 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>379.99</v>
+        <v>380.99</v>
       </c>
       <c r="F255" t="n">
-        <v>327.5</v>
+        <v>329.5</v>
       </c>
       <c r="G255" t="n">
         <v>350</v>
@@ -8352,10 +8352,10 @@
         <v>380.99</v>
       </c>
       <c r="F256" t="n">
-        <v>329.5</v>
+        <v>325.5</v>
       </c>
       <c r="G256" t="n">
-        <v>348</v>
+        <v>346.5</v>
       </c>
     </row>
     <row r="257">
@@ -8380,13 +8380,13 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>380.99</v>
+        <v>379.99</v>
       </c>
       <c r="F257" t="n">
-        <v>329.5</v>
+        <v>328</v>
       </c>
       <c r="G257" t="n">
-        <v>348</v>
+        <v>346.5</v>
       </c>
     </row>
     <row r="258">
@@ -8414,7 +8414,7 @@
         <v>379.99</v>
       </c>
       <c r="F258" t="n">
-        <v>327.5</v>
+        <v>328</v>
       </c>
       <c r="G258" t="n">
         <v>348</v>
@@ -8442,13 +8442,13 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>378.99</v>
+        <v>380.99</v>
       </c>
       <c r="F259" t="n">
         <v>327.5</v>
       </c>
       <c r="G259" t="n">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="260">
@@ -8476,10 +8476,10 @@
         <v>379.99</v>
       </c>
       <c r="F260" t="n">
-        <v>329.5</v>
+        <v>328</v>
       </c>
       <c r="G260" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="261">
@@ -8507,10 +8507,10 @@
         <v>379.99</v>
       </c>
       <c r="F261" t="n">
-        <v>328</v>
+        <v>329.5</v>
       </c>
       <c r="G261" t="n">
-        <v>350</v>
+        <v>346.5</v>
       </c>
     </row>
     <row r="262">
@@ -8535,10 +8535,10 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>379.99</v>
+        <v>378.99</v>
       </c>
       <c r="F262" t="n">
-        <v>328</v>
+        <v>329.5</v>
       </c>
       <c r="G262" t="n">
         <v>348</v>
@@ -8569,10 +8569,10 @@
         <v>379.99</v>
       </c>
       <c r="F263" t="n">
-        <v>327.5</v>
+        <v>328</v>
       </c>
       <c r="G263" t="n">
-        <v>350</v>
+        <v>346.5</v>
       </c>
     </row>
     <row r="264">
@@ -8603,7 +8603,7 @@
         <v>328</v>
       </c>
       <c r="G264" t="n">
-        <v>346.5</v>
+        <v>348</v>
       </c>
     </row>
     <row r="265">
@@ -8628,13 +8628,13 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>380.99</v>
+        <v>379.99</v>
       </c>
       <c r="F265" t="n">
-        <v>328</v>
+        <v>327.5</v>
       </c>
       <c r="G265" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="266">
@@ -8662,7 +8662,7 @@
         <v>379.99</v>
       </c>
       <c r="F266" t="n">
-        <v>325.5</v>
+        <v>327.5</v>
       </c>
       <c r="G266" t="n">
         <v>350</v>
@@ -8690,13 +8690,13 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>380.99</v>
+        <v>379.99</v>
       </c>
       <c r="F267" t="n">
         <v>328</v>
       </c>
       <c r="G267" t="n">
-        <v>346.5</v>
+        <v>348</v>
       </c>
     </row>
     <row r="268">
@@ -8724,10 +8724,10 @@
         <v>379.99</v>
       </c>
       <c r="F268" t="n">
-        <v>325.5</v>
+        <v>329.5</v>
       </c>
       <c r="G268" t="n">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="269">
@@ -8752,13 +8752,13 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>379.99</v>
+        <v>378.99</v>
       </c>
       <c r="F269" t="n">
-        <v>328</v>
+        <v>327.5</v>
       </c>
       <c r="G269" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="270">
@@ -8786,10 +8786,10 @@
         <v>378.99</v>
       </c>
       <c r="F270" t="n">
-        <v>328</v>
+        <v>327.5</v>
       </c>
       <c r="G270" t="n">
-        <v>348</v>
+        <v>346.5</v>
       </c>
     </row>
     <row r="271">
@@ -8814,7 +8814,7 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>378.99</v>
+        <v>379.99</v>
       </c>
       <c r="F271" t="n">
         <v>328</v>
@@ -8848,10 +8848,10 @@
         <v>699.99</v>
       </c>
       <c r="F272" t="n">
-        <v>701.49</v>
+        <v>699.49</v>
       </c>
       <c r="G272" t="n">
-        <v>699.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="273">
@@ -8876,13 +8876,13 @@
         </is>
       </c>
       <c r="E273" t="n">
+        <v>700.99</v>
+      </c>
+      <c r="F273" t="n">
         <v>699.99</v>
       </c>
-      <c r="F273" t="n">
-        <v>697.49</v>
-      </c>
       <c r="G273" t="n">
-        <v>698.49</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="274">
@@ -8910,7 +8910,7 @@
         <v>700.99</v>
       </c>
       <c r="F274" t="n">
-        <v>699.99</v>
+        <v>699.49</v>
       </c>
       <c r="G274" t="n">
         <v>698.49</v>
@@ -8938,13 +8938,13 @@
         </is>
       </c>
       <c r="E275" t="n">
+        <v>698.99</v>
+      </c>
+      <c r="F275" t="n">
+        <v>697.49</v>
+      </c>
+      <c r="G275" t="n">
         <v>699.99</v>
-      </c>
-      <c r="F275" t="n">
-        <v>699.49</v>
-      </c>
-      <c r="G275" t="n">
-        <v>701.99</v>
       </c>
     </row>
     <row r="276">
@@ -8969,13 +8969,13 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>698.99</v>
+        <v>700.99</v>
       </c>
       <c r="F276" t="n">
-        <v>699.99</v>
+        <v>699.49</v>
       </c>
       <c r="G276" t="n">
-        <v>699.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="277">
@@ -9000,13 +9000,13 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>700.99</v>
+        <v>699.99</v>
       </c>
       <c r="F277" t="n">
-        <v>697.49</v>
+        <v>699.99</v>
       </c>
       <c r="G277" t="n">
-        <v>699.99</v>
+        <v>701.99</v>
       </c>
     </row>
     <row r="278">
@@ -9034,7 +9034,7 @@
         <v>699.99</v>
       </c>
       <c r="F278" t="n">
-        <v>697.49</v>
+        <v>701.49</v>
       </c>
       <c r="G278" t="n">
         <v>699.99</v>
@@ -9065,7 +9065,7 @@
         <v>700.99</v>
       </c>
       <c r="F279" t="n">
-        <v>699.49</v>
+        <v>699.99</v>
       </c>
       <c r="G279" t="n">
         <v>699.99</v>
@@ -9093,10 +9093,10 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>699.99</v>
+        <v>698.99</v>
       </c>
       <c r="F280" t="n">
-        <v>699.49</v>
+        <v>697.49</v>
       </c>
       <c r="G280" t="n">
         <v>699.99</v>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>700.99</v>
+        <v>699.99</v>
       </c>
       <c r="F281" t="n">
-        <v>699.49</v>
+        <v>699.99</v>
       </c>
       <c r="G281" t="n">
         <v>699.99</v>
@@ -9155,13 +9155,13 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>698.99</v>
+        <v>699.99</v>
       </c>
       <c r="F282" t="n">
         <v>699.99</v>
       </c>
       <c r="G282" t="n">
-        <v>701.99</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="283">
@@ -9189,10 +9189,10 @@
         <v>699.99</v>
       </c>
       <c r="F283" t="n">
+        <v>701.49</v>
+      </c>
+      <c r="G283" t="n">
         <v>699.99</v>
-      </c>
-      <c r="G283" t="n">
-        <v>698.49</v>
       </c>
     </row>
     <row r="284">
@@ -9248,13 +9248,13 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>698.99</v>
+        <v>699.99</v>
       </c>
       <c r="F285" t="n">
         <v>699.99</v>
       </c>
       <c r="G285" t="n">
-        <v>701.99</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="286">
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>700.99</v>
+        <v>698.99</v>
       </c>
       <c r="F286" t="n">
-        <v>697.49</v>
+        <v>701.49</v>
       </c>
       <c r="G286" t="n">
         <v>698.49</v>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>698.99</v>
+        <v>699.99</v>
       </c>
       <c r="F287" t="n">
         <v>699.99</v>
@@ -9341,13 +9341,13 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>699.99</v>
+        <v>700.99</v>
       </c>
       <c r="F288" t="n">
-        <v>697.49</v>
+        <v>701.49</v>
       </c>
       <c r="G288" t="n">
-        <v>699.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="289">
@@ -9375,10 +9375,10 @@
         <v>698.99</v>
       </c>
       <c r="F289" t="n">
-        <v>697.49</v>
+        <v>699.99</v>
       </c>
       <c r="G289" t="n">
-        <v>701.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="290">
@@ -9406,10 +9406,10 @@
         <v>699.99</v>
       </c>
       <c r="F290" t="n">
-        <v>699.99</v>
+        <v>699.49</v>
       </c>
       <c r="G290" t="n">
-        <v>698.49</v>
+        <v>701.99</v>
       </c>
     </row>
     <row r="291">
@@ -9434,13 +9434,13 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>699.99</v>
+        <v>698.99</v>
       </c>
       <c r="F291" t="n">
-        <v>697.49</v>
+        <v>699.49</v>
       </c>
       <c r="G291" t="n">
-        <v>701.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="292">
@@ -9499,7 +9499,7 @@
         <v>699.99</v>
       </c>
       <c r="F293" t="n">
-        <v>697.49</v>
+        <v>699.99</v>
       </c>
       <c r="G293" t="n">
         <v>699.99</v>
@@ -9530,7 +9530,7 @@
         <v>700.99</v>
       </c>
       <c r="F294" t="n">
-        <v>701.49</v>
+        <v>699.99</v>
       </c>
       <c r="G294" t="n">
         <v>698.49</v>
@@ -9558,10 +9558,10 @@
         </is>
       </c>
       <c r="E295" t="n">
+        <v>698.99</v>
+      </c>
+      <c r="F295" t="n">
         <v>699.99</v>
-      </c>
-      <c r="F295" t="n">
-        <v>701.49</v>
       </c>
       <c r="G295" t="n">
         <v>699.99</v>
@@ -9626,7 +9626,7 @@
         <v>699.99</v>
       </c>
       <c r="G297" t="n">
-        <v>698.49</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="298">
@@ -9651,7 +9651,7 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>698.99</v>
+        <v>699.99</v>
       </c>
       <c r="F298" t="n">
         <v>697.49</v>
@@ -9685,7 +9685,7 @@
         <v>699.99</v>
       </c>
       <c r="F299" t="n">
-        <v>699.49</v>
+        <v>697.49</v>
       </c>
       <c r="G299" t="n">
         <v>699.99</v>
@@ -9716,7 +9716,7 @@
         <v>699.99</v>
       </c>
       <c r="F300" t="n">
-        <v>699.49</v>
+        <v>699.99</v>
       </c>
       <c r="G300" t="n">
         <v>699.99</v>
@@ -9747,10 +9747,10 @@
         <v>699.99</v>
       </c>
       <c r="F301" t="n">
-        <v>697.49</v>
+        <v>699.99</v>
       </c>
       <c r="G301" t="n">
-        <v>699.99</v>
+        <v>701.99</v>
       </c>
     </row>
     <row r="302">
@@ -9775,13 +9775,13 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>600.99</v>
+        <v>599.99</v>
       </c>
       <c r="F302" t="n">
-        <v>579.99</v>
+        <v>581.49</v>
       </c>
       <c r="G302" t="n">
-        <v>589.99</v>
+        <v>591.99</v>
       </c>
     </row>
     <row r="303">
@@ -9806,13 +9806,13 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>599.99</v>
+        <v>600.99</v>
       </c>
       <c r="F303" t="n">
         <v>579.99</v>
       </c>
       <c r="G303" t="n">
-        <v>589.99</v>
+        <v>591.99</v>
       </c>
     </row>
     <row r="304">
@@ -9837,10 +9837,10 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>600.99</v>
+        <v>599.99</v>
       </c>
       <c r="F304" t="n">
-        <v>579.99</v>
+        <v>577.49</v>
       </c>
       <c r="G304" t="n">
         <v>589.99</v>
@@ -9868,10 +9868,10 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>600.99</v>
+        <v>598.99</v>
       </c>
       <c r="F305" t="n">
-        <v>579.49</v>
+        <v>577.49</v>
       </c>
       <c r="G305" t="n">
         <v>591.99</v>
@@ -9899,7 +9899,7 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>600.99</v>
+        <v>598.99</v>
       </c>
       <c r="F306" t="n">
         <v>581.49</v>
@@ -9933,10 +9933,10 @@
         <v>599.99</v>
       </c>
       <c r="F307" t="n">
-        <v>577.49</v>
+        <v>579.99</v>
       </c>
       <c r="G307" t="n">
-        <v>588.49</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="308">
@@ -9961,13 +9961,13 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>599.99</v>
+        <v>598.99</v>
       </c>
       <c r="F308" t="n">
-        <v>579.99</v>
+        <v>577.49</v>
       </c>
       <c r="G308" t="n">
-        <v>588.49</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="309">
@@ -9992,13 +9992,13 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>599.99</v>
+        <v>600.99</v>
       </c>
       <c r="F309" t="n">
-        <v>579.49</v>
+        <v>579.99</v>
       </c>
       <c r="G309" t="n">
-        <v>588.49</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="310">
@@ -10023,10 +10023,10 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>599.99</v>
+        <v>598.99</v>
       </c>
       <c r="F310" t="n">
-        <v>579.99</v>
+        <v>581.49</v>
       </c>
       <c r="G310" t="n">
         <v>591.99</v>
@@ -10057,10 +10057,10 @@
         <v>599.99</v>
       </c>
       <c r="F311" t="n">
-        <v>581.49</v>
+        <v>579.99</v>
       </c>
       <c r="G311" t="n">
-        <v>591.99</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="312">
@@ -10119,10 +10119,10 @@
         <v>600.99</v>
       </c>
       <c r="F313" t="n">
-        <v>577.49</v>
+        <v>579.49</v>
       </c>
       <c r="G313" t="n">
-        <v>591.99</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="314">
@@ -10181,10 +10181,10 @@
         <v>599.99</v>
       </c>
       <c r="F315" t="n">
-        <v>581.49</v>
+        <v>579.49</v>
       </c>
       <c r="G315" t="n">
-        <v>589.99</v>
+        <v>588.49</v>
       </c>
     </row>
     <row r="316">
@@ -10209,13 +10209,13 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>599.99</v>
+        <v>598.99</v>
       </c>
       <c r="F316" t="n">
-        <v>579.99</v>
+        <v>581.49</v>
       </c>
       <c r="G316" t="n">
-        <v>589.99</v>
+        <v>588.49</v>
       </c>
     </row>
     <row r="317">
@@ -10240,13 +10240,13 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>600.99</v>
+        <v>598.99</v>
       </c>
       <c r="F317" t="n">
         <v>579.49</v>
       </c>
       <c r="G317" t="n">
-        <v>588.49</v>
+        <v>591.99</v>
       </c>
     </row>
     <row r="318">
@@ -10271,7 +10271,7 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>600.99</v>
+        <v>598.99</v>
       </c>
       <c r="F318" t="n">
         <v>579.99</v>
@@ -10302,13 +10302,13 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>599.99</v>
+        <v>600.99</v>
       </c>
       <c r="F319" t="n">
-        <v>581.49</v>
+        <v>579.99</v>
       </c>
       <c r="G319" t="n">
-        <v>588.49</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="320">
@@ -10333,13 +10333,13 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>598.99</v>
+        <v>599.99</v>
       </c>
       <c r="F320" t="n">
-        <v>581.49</v>
+        <v>579.99</v>
       </c>
       <c r="G320" t="n">
-        <v>588.49</v>
+        <v>591.99</v>
       </c>
     </row>
     <row r="321">
@@ -10364,13 +10364,13 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>600.99</v>
+        <v>599.99</v>
       </c>
       <c r="F321" t="n">
         <v>579.49</v>
       </c>
       <c r="G321" t="n">
-        <v>589.99</v>
+        <v>588.49</v>
       </c>
     </row>
     <row r="322">
@@ -10395,13 +10395,13 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>598.99</v>
+        <v>599.99</v>
       </c>
       <c r="F322" t="n">
-        <v>579.99</v>
+        <v>577.49</v>
       </c>
       <c r="G322" t="n">
-        <v>591.99</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="323">
@@ -10426,10 +10426,10 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>598.99</v>
+        <v>599.99</v>
       </c>
       <c r="F323" t="n">
-        <v>579.49</v>
+        <v>577.49</v>
       </c>
       <c r="G323" t="n">
         <v>588.49</v>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>599.99</v>
+        <v>600.99</v>
       </c>
       <c r="F324" t="n">
-        <v>577.49</v>
+        <v>581.49</v>
       </c>
       <c r="G324" t="n">
         <v>589.99</v>
@@ -10491,10 +10491,10 @@
         <v>599.99</v>
       </c>
       <c r="F325" t="n">
-        <v>579.49</v>
+        <v>577.49</v>
       </c>
       <c r="G325" t="n">
-        <v>589.99</v>
+        <v>591.99</v>
       </c>
     </row>
     <row r="326">
@@ -10522,10 +10522,10 @@
         <v>599.99</v>
       </c>
       <c r="F326" t="n">
-        <v>579.99</v>
+        <v>579.49</v>
       </c>
       <c r="G326" t="n">
-        <v>591.99</v>
+        <v>588.49</v>
       </c>
     </row>
     <row r="327">
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>598.99</v>
+        <v>599.99</v>
       </c>
       <c r="F327" t="n">
         <v>579.99</v>
       </c>
       <c r="G327" t="n">
-        <v>589.99</v>
+        <v>588.49</v>
       </c>
     </row>
     <row r="328">
@@ -10584,7 +10584,7 @@
         <v>599.99</v>
       </c>
       <c r="F328" t="n">
-        <v>579.99</v>
+        <v>579.49</v>
       </c>
       <c r="G328" t="n">
         <v>588.49</v>
@@ -10615,7 +10615,7 @@
         <v>599.99</v>
       </c>
       <c r="F329" t="n">
-        <v>577.49</v>
+        <v>579.99</v>
       </c>
       <c r="G329" t="n">
         <v>589.99</v>
@@ -10649,7 +10649,7 @@
         <v>579.49</v>
       </c>
       <c r="G330" t="n">
-        <v>589.99</v>
+        <v>588.49</v>
       </c>
     </row>
     <row r="331">
@@ -10677,10 +10677,10 @@
         <v>599.99</v>
       </c>
       <c r="F331" t="n">
-        <v>581.49</v>
+        <v>579.99</v>
       </c>
       <c r="G331" t="n">
-        <v>588.49</v>
+        <v>589.99</v>
       </c>
     </row>
     <row r="332">
@@ -10705,10 +10705,10 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>750.99</v>
+        <v>749.99</v>
       </c>
       <c r="F332" t="n">
-        <v>649.49</v>
+        <v>647.49</v>
       </c>
       <c r="G332" t="n">
         <v>699.99</v>
@@ -10736,10 +10736,10 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>749.99</v>
+        <v>750.99</v>
       </c>
       <c r="F333" t="n">
-        <v>649.99</v>
+        <v>651.49</v>
       </c>
       <c r="G333" t="n">
         <v>699.99</v>
@@ -10767,13 +10767,13 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>748.99</v>
+        <v>749.99</v>
       </c>
       <c r="F334" t="n">
-        <v>649.49</v>
+        <v>649.99</v>
       </c>
       <c r="G334" t="n">
-        <v>699.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="335">
@@ -10798,13 +10798,13 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>749.99</v>
+        <v>748.99</v>
       </c>
       <c r="F335" t="n">
-        <v>649.49</v>
+        <v>651.49</v>
       </c>
       <c r="G335" t="n">
-        <v>699.99</v>
+        <v>701.99</v>
       </c>
     </row>
     <row r="336">
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>748.99</v>
+        <v>749.99</v>
       </c>
       <c r="F336" t="n">
         <v>649.99</v>
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>748.99</v>
+        <v>749.99</v>
       </c>
       <c r="F337" t="n">
-        <v>649.49</v>
+        <v>649.99</v>
       </c>
       <c r="G337" t="n">
-        <v>698.49</v>
+        <v>701.99</v>
       </c>
     </row>
     <row r="338">
@@ -10891,13 +10891,13 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>749.99</v>
+        <v>748.99</v>
       </c>
       <c r="F338" t="n">
-        <v>647.49</v>
+        <v>649.99</v>
       </c>
       <c r="G338" t="n">
-        <v>701.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="339">
@@ -10925,10 +10925,10 @@
         <v>749.99</v>
       </c>
       <c r="F339" t="n">
-        <v>647.49</v>
+        <v>649.49</v>
       </c>
       <c r="G339" t="n">
-        <v>701.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="340">
@@ -10953,13 +10953,13 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>749.99</v>
+        <v>750.99</v>
       </c>
       <c r="F340" t="n">
-        <v>647.49</v>
+        <v>649.49</v>
       </c>
       <c r="G340" t="n">
-        <v>701.99</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="341">
@@ -10984,13 +10984,13 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>749.99</v>
+        <v>748.99</v>
       </c>
       <c r="F341" t="n">
-        <v>647.49</v>
+        <v>649.49</v>
       </c>
       <c r="G341" t="n">
-        <v>699.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="342">
@@ -11018,10 +11018,10 @@
         <v>749.99</v>
       </c>
       <c r="F342" t="n">
-        <v>649.49</v>
+        <v>651.49</v>
       </c>
       <c r="G342" t="n">
-        <v>701.99</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="343">
@@ -11049,10 +11049,10 @@
         <v>749.99</v>
       </c>
       <c r="F343" t="n">
-        <v>647.49</v>
+        <v>649.49</v>
       </c>
       <c r="G343" t="n">
-        <v>699.99</v>
+        <v>701.99</v>
       </c>
     </row>
     <row r="344">
@@ -11077,13 +11077,13 @@
         </is>
       </c>
       <c r="E344" t="n">
-        <v>750.99</v>
+        <v>749.99</v>
       </c>
       <c r="F344" t="n">
-        <v>649.49</v>
+        <v>647.49</v>
       </c>
       <c r="G344" t="n">
-        <v>698.49</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="345">
@@ -11108,13 +11108,13 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>750.99</v>
+        <v>749.99</v>
       </c>
       <c r="F345" t="n">
         <v>651.49</v>
       </c>
       <c r="G345" t="n">
-        <v>699.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="346">
@@ -11139,13 +11139,13 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>750.99</v>
+        <v>749.99</v>
       </c>
       <c r="F346" t="n">
-        <v>647.49</v>
+        <v>651.49</v>
       </c>
       <c r="G346" t="n">
-        <v>701.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="347">
@@ -11170,10 +11170,10 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>748.99</v>
+        <v>749.99</v>
       </c>
       <c r="F347" t="n">
-        <v>647.49</v>
+        <v>651.49</v>
       </c>
       <c r="G347" t="n">
         <v>699.99</v>
@@ -11201,7 +11201,7 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>748.99</v>
+        <v>749.99</v>
       </c>
       <c r="F348" t="n">
         <v>651.49</v>
@@ -11238,7 +11238,7 @@
         <v>651.49</v>
       </c>
       <c r="G349" t="n">
-        <v>698.49</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="350">
@@ -11266,10 +11266,10 @@
         <v>749.99</v>
       </c>
       <c r="F350" t="n">
-        <v>651.49</v>
+        <v>649.49</v>
       </c>
       <c r="G350" t="n">
-        <v>698.49</v>
+        <v>699.99</v>
       </c>
     </row>
     <row r="351">
@@ -11294,13 +11294,13 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>749.99</v>
+        <v>748.99</v>
       </c>
       <c r="F351" t="n">
-        <v>649.99</v>
+        <v>651.49</v>
       </c>
       <c r="G351" t="n">
-        <v>699.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="352">
@@ -11325,10 +11325,10 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>748.99</v>
+        <v>749.99</v>
       </c>
       <c r="F352" t="n">
-        <v>649.49</v>
+        <v>649.99</v>
       </c>
       <c r="G352" t="n">
         <v>701.99</v>
@@ -11356,13 +11356,13 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>749.99</v>
+        <v>750.99</v>
       </c>
       <c r="F353" t="n">
-        <v>649.99</v>
+        <v>649.49</v>
       </c>
       <c r="G353" t="n">
-        <v>699.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="354">
@@ -11387,10 +11387,10 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>748.99</v>
+        <v>749.99</v>
       </c>
       <c r="F354" t="n">
-        <v>649.49</v>
+        <v>647.49</v>
       </c>
       <c r="G354" t="n">
         <v>698.49</v>
@@ -11418,7 +11418,7 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>748.99</v>
+        <v>749.99</v>
       </c>
       <c r="F355" t="n">
         <v>651.49</v>
@@ -11452,7 +11452,7 @@
         <v>749.99</v>
       </c>
       <c r="F356" t="n">
-        <v>649.99</v>
+        <v>649.49</v>
       </c>
       <c r="G356" t="n">
         <v>698.49</v>
@@ -11480,7 +11480,7 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>748.99</v>
+        <v>749.99</v>
       </c>
       <c r="F357" t="n">
         <v>649.99</v>
@@ -11511,13 +11511,13 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>748.99</v>
+        <v>750.99</v>
       </c>
       <c r="F358" t="n">
         <v>651.49</v>
       </c>
       <c r="G358" t="n">
-        <v>701.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="359">
@@ -11542,10 +11542,10 @@
         </is>
       </c>
       <c r="E359" t="n">
-        <v>750.99</v>
+        <v>749.99</v>
       </c>
       <c r="F359" t="n">
-        <v>651.49</v>
+        <v>647.49</v>
       </c>
       <c r="G359" t="n">
         <v>698.49</v>
@@ -11604,13 +11604,13 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>748.99</v>
+        <v>750.99</v>
       </c>
       <c r="F361" t="n">
-        <v>649.99</v>
+        <v>651.49</v>
       </c>
       <c r="G361" t="n">
-        <v>699.99</v>
+        <v>698.49</v>
       </c>
     </row>
     <row r="362">
@@ -11638,10 +11638,10 @@
         <v>428</v>
       </c>
       <c r="F362" t="n">
-        <v>376.5</v>
+        <v>379</v>
       </c>
       <c r="G362" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="363">
@@ -11728,10 +11728,10 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F365" t="n">
-        <v>378.5</v>
+        <v>380.5</v>
       </c>
       <c r="G365" t="n">
         <v>399</v>
@@ -11759,10 +11759,10 @@
         </is>
       </c>
       <c r="E366" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F366" t="n">
-        <v>378.5</v>
+        <v>380.5</v>
       </c>
       <c r="G366" t="n">
         <v>397.5</v>
@@ -11796,7 +11796,7 @@
         <v>379</v>
       </c>
       <c r="G367" t="n">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="368">
@@ -11827,7 +11827,7 @@
         <v>379</v>
       </c>
       <c r="G368" t="n">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="369">
@@ -11852,13 +11852,13 @@
         </is>
       </c>
       <c r="E369" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F369" t="n">
-        <v>379</v>
+        <v>376.5</v>
       </c>
       <c r="G369" t="n">
-        <v>397.5</v>
+        <v>399</v>
       </c>
     </row>
     <row r="370">
@@ -11886,7 +11886,7 @@
         <v>429</v>
       </c>
       <c r="F370" t="n">
-        <v>378.5</v>
+        <v>379</v>
       </c>
       <c r="G370" t="n">
         <v>397.5</v>
@@ -11914,10 +11914,10 @@
         </is>
       </c>
       <c r="E371" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F371" t="n">
-        <v>379</v>
+        <v>380.5</v>
       </c>
       <c r="G371" t="n">
         <v>399</v>
@@ -11948,10 +11948,10 @@
         <v>429</v>
       </c>
       <c r="F372" t="n">
-        <v>379</v>
+        <v>380.5</v>
       </c>
       <c r="G372" t="n">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="373">
@@ -11979,10 +11979,10 @@
         <v>429</v>
       </c>
       <c r="F373" t="n">
-        <v>376.5</v>
+        <v>379</v>
       </c>
       <c r="G373" t="n">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="374">
@@ -12010,7 +12010,7 @@
         <v>428</v>
       </c>
       <c r="F374" t="n">
-        <v>378.5</v>
+        <v>379</v>
       </c>
       <c r="G374" t="n">
         <v>399</v>
@@ -12041,7 +12041,7 @@
         <v>428</v>
       </c>
       <c r="F375" t="n">
-        <v>378.5</v>
+        <v>379</v>
       </c>
       <c r="G375" t="n">
         <v>397.5</v>
@@ -12075,7 +12075,7 @@
         <v>380.5</v>
       </c>
       <c r="G376" t="n">
-        <v>397.5</v>
+        <v>399</v>
       </c>
     </row>
     <row r="377">
@@ -12103,10 +12103,10 @@
         <v>429</v>
       </c>
       <c r="F377" t="n">
-        <v>379</v>
+        <v>378.5</v>
       </c>
       <c r="G377" t="n">
-        <v>399</v>
+        <v>397.5</v>
       </c>
     </row>
     <row r="378">
@@ -12134,7 +12134,7 @@
         <v>429</v>
       </c>
       <c r="F378" t="n">
-        <v>378.5</v>
+        <v>376.5</v>
       </c>
       <c r="G378" t="n">
         <v>399</v>
@@ -12162,13 +12162,13 @@
         </is>
       </c>
       <c r="E379" t="n">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F379" t="n">
-        <v>379</v>
+        <v>380.5</v>
       </c>
       <c r="G379" t="n">
-        <v>397.5</v>
+        <v>399</v>
       </c>
     </row>
     <row r="380">
@@ -12193,10 +12193,10 @@
         </is>
       </c>
       <c r="E380" t="n">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F380" t="n">
-        <v>379</v>
+        <v>380.5</v>
       </c>
       <c r="G380" t="n">
         <v>399</v>
@@ -12227,10 +12227,10 @@
         <v>429</v>
       </c>
       <c r="F381" t="n">
-        <v>376.5</v>
+        <v>378.5</v>
       </c>
       <c r="G381" t="n">
-        <v>397.5</v>
+        <v>401</v>
       </c>
     </row>
     <row r="382">
@@ -12258,10 +12258,10 @@
         <v>429</v>
       </c>
       <c r="F382" t="n">
-        <v>378.5</v>
+        <v>379</v>
       </c>
       <c r="G382" t="n">
-        <v>397.5</v>
+        <v>399</v>
       </c>
     </row>
     <row r="383">
@@ -12289,10 +12289,10 @@
         <v>429</v>
       </c>
       <c r="F383" t="n">
-        <v>379</v>
+        <v>378.5</v>
       </c>
       <c r="G383" t="n">
-        <v>397.5</v>
+        <v>399</v>
       </c>
     </row>
     <row r="384">
@@ -12317,13 +12317,13 @@
         </is>
       </c>
       <c r="E384" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F384" t="n">
-        <v>378.5</v>
+        <v>379</v>
       </c>
       <c r="G384" t="n">
-        <v>399</v>
+        <v>397.5</v>
       </c>
     </row>
     <row r="385">
@@ -12348,10 +12348,10 @@
         </is>
       </c>
       <c r="E385" t="n">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F385" t="n">
-        <v>379</v>
+        <v>376.5</v>
       </c>
       <c r="G385" t="n">
         <v>401</v>
@@ -12379,10 +12379,10 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F386" t="n">
-        <v>379</v>
+        <v>378.5</v>
       </c>
       <c r="G386" t="n">
         <v>399</v>
@@ -12410,13 +12410,13 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F387" t="n">
-        <v>379</v>
+        <v>378.5</v>
       </c>
       <c r="G387" t="n">
-        <v>399</v>
+        <v>397.5</v>
       </c>
     </row>
     <row r="388">
@@ -12447,7 +12447,7 @@
         <v>378.5</v>
       </c>
       <c r="G388" t="n">
-        <v>397.5</v>
+        <v>399</v>
       </c>
     </row>
     <row r="389">
@@ -12472,10 +12472,10 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F389" t="n">
-        <v>378.5</v>
+        <v>380.5</v>
       </c>
       <c r="G389" t="n">
         <v>397.5</v>
@@ -12503,13 +12503,13 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F390" t="n">
-        <v>376.5</v>
+        <v>379</v>
       </c>
       <c r="G390" t="n">
-        <v>397.5</v>
+        <v>401</v>
       </c>
     </row>
     <row r="391">
@@ -12537,10 +12537,10 @@
         <v>429</v>
       </c>
       <c r="F391" t="n">
-        <v>376.5</v>
+        <v>379</v>
       </c>
       <c r="G391" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="392">
@@ -12568,7 +12568,7 @@
         <v>1149</v>
       </c>
       <c r="F392" t="n">
-        <v>1049</v>
+        <v>1048.5</v>
       </c>
       <c r="G392" t="n">
         <v>1069</v>
@@ -12596,10 +12596,10 @@
         </is>
       </c>
       <c r="E393" t="n">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="F393" t="n">
-        <v>1050.5</v>
+        <v>1049</v>
       </c>
       <c r="G393" t="n">
         <v>1069</v>
@@ -12633,7 +12633,7 @@
         <v>1049</v>
       </c>
       <c r="G394" t="n">
-        <v>1069</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="395">
@@ -12658,13 +12658,13 @@
         </is>
       </c>
       <c r="E395" t="n">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="F395" t="n">
-        <v>1049</v>
+        <v>1046.5</v>
       </c>
       <c r="G395" t="n">
-        <v>1069</v>
+        <v>1067.5</v>
       </c>
     </row>
     <row r="396">
@@ -12689,10 +12689,10 @@
         </is>
       </c>
       <c r="E396" t="n">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="F396" t="n">
-        <v>1046.5</v>
+        <v>1050.5</v>
       </c>
       <c r="G396" t="n">
         <v>1069</v>
@@ -12751,13 +12751,13 @@
         </is>
       </c>
       <c r="E398" t="n">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="F398" t="n">
-        <v>1049</v>
+        <v>1048.5</v>
       </c>
       <c r="G398" t="n">
-        <v>1071</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="399">
@@ -12785,10 +12785,10 @@
         <v>1149</v>
       </c>
       <c r="F399" t="n">
-        <v>1046.5</v>
+        <v>1049</v>
       </c>
       <c r="G399" t="n">
-        <v>1071</v>
+        <v>1067.5</v>
       </c>
     </row>
     <row r="400">
@@ -12847,10 +12847,10 @@
         <v>1149</v>
       </c>
       <c r="F401" t="n">
-        <v>1050.5</v>
+        <v>1048.5</v>
       </c>
       <c r="G401" t="n">
-        <v>1071</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="402">
@@ -12875,7 +12875,7 @@
         </is>
       </c>
       <c r="E402" t="n">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="F402" t="n">
         <v>1046.5</v>
@@ -12906,10 +12906,10 @@
         </is>
       </c>
       <c r="E403" t="n">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F403" t="n">
-        <v>1048.5</v>
+        <v>1046.5</v>
       </c>
       <c r="G403" t="n">
         <v>1067.5</v>
@@ -12937,13 +12937,13 @@
         </is>
       </c>
       <c r="E404" t="n">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="F404" t="n">
-        <v>1050.5</v>
+        <v>1046.5</v>
       </c>
       <c r="G404" t="n">
-        <v>1069</v>
+        <v>1067.5</v>
       </c>
     </row>
     <row r="405">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="E405" t="n">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F405" t="n">
-        <v>1046.5</v>
+        <v>1049</v>
       </c>
       <c r="G405" t="n">
-        <v>1067.5</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="406">
@@ -13002,7 +13002,7 @@
         <v>1149</v>
       </c>
       <c r="F406" t="n">
-        <v>1048.5</v>
+        <v>1050.5</v>
       </c>
       <c r="G406" t="n">
         <v>1067.5</v>
@@ -13033,10 +13033,10 @@
         <v>1149</v>
       </c>
       <c r="F407" t="n">
-        <v>1046.5</v>
+        <v>1048.5</v>
       </c>
       <c r="G407" t="n">
-        <v>1069</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="408">
@@ -13061,10 +13061,10 @@
         </is>
       </c>
       <c r="E408" t="n">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F408" t="n">
-        <v>1046.5</v>
+        <v>1048.5</v>
       </c>
       <c r="G408" t="n">
         <v>1067.5</v>
@@ -13098,7 +13098,7 @@
         <v>1046.5</v>
       </c>
       <c r="G409" t="n">
-        <v>1071</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="410">
@@ -13123,13 +13123,13 @@
         </is>
       </c>
       <c r="E410" t="n">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="F410" t="n">
-        <v>1049</v>
+        <v>1048.5</v>
       </c>
       <c r="G410" t="n">
-        <v>1067.5</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="411">
@@ -13160,7 +13160,7 @@
         <v>1049</v>
       </c>
       <c r="G411" t="n">
-        <v>1071</v>
+        <v>1067.5</v>
       </c>
     </row>
     <row r="412">
@@ -13185,13 +13185,13 @@
         </is>
       </c>
       <c r="E412" t="n">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F412" t="n">
         <v>1046.5</v>
       </c>
       <c r="G412" t="n">
-        <v>1067.5</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="413">
@@ -13216,13 +13216,13 @@
         </is>
       </c>
       <c r="E413" t="n">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="F413" t="n">
         <v>1049</v>
       </c>
       <c r="G413" t="n">
-        <v>1067.5</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="414">
@@ -13250,10 +13250,10 @@
         <v>1149</v>
       </c>
       <c r="F414" t="n">
-        <v>1049</v>
+        <v>1048.5</v>
       </c>
       <c r="G414" t="n">
-        <v>1069</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="415">
@@ -13278,13 +13278,13 @@
         </is>
       </c>
       <c r="E415" t="n">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F415" t="n">
         <v>1050.5</v>
       </c>
       <c r="G415" t="n">
-        <v>1069</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="416">
@@ -13309,13 +13309,13 @@
         </is>
       </c>
       <c r="E416" t="n">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="F416" t="n">
-        <v>1049</v>
+        <v>1050.5</v>
       </c>
       <c r="G416" t="n">
-        <v>1071</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="417">
@@ -13340,10 +13340,10 @@
         </is>
       </c>
       <c r="E417" t="n">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="F417" t="n">
-        <v>1048.5</v>
+        <v>1049</v>
       </c>
       <c r="G417" t="n">
         <v>1069</v>
@@ -13374,10 +13374,10 @@
         <v>1149</v>
       </c>
       <c r="F418" t="n">
-        <v>1050.5</v>
+        <v>1046.5</v>
       </c>
       <c r="G418" t="n">
-        <v>1069</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="419">
@@ -13402,10 +13402,10 @@
         </is>
       </c>
       <c r="E419" t="n">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="F419" t="n">
-        <v>1049</v>
+        <v>1050.5</v>
       </c>
       <c r="G419" t="n">
         <v>1069</v>
@@ -13433,10 +13433,10 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F420" t="n">
-        <v>1049</v>
+        <v>1046.5</v>
       </c>
       <c r="G420" t="n">
         <v>1069</v>
@@ -13464,13 +13464,13 @@
         </is>
       </c>
       <c r="E421" t="n">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="F421" t="n">
         <v>1048.5</v>
       </c>
       <c r="G421" t="n">
-        <v>1067.5</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="422">
@@ -13495,13 +13495,13 @@
         </is>
       </c>
       <c r="E422" t="n">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="F422" t="n">
         <v>1048.5</v>
       </c>
       <c r="G422" t="n">
-        <v>1081</v>
+        <v>1077.5</v>
       </c>
     </row>
     <row r="423">
@@ -13526,7 +13526,7 @@
         </is>
       </c>
       <c r="E423" t="n">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="F423" t="n">
         <v>1050.5</v>
@@ -13560,7 +13560,7 @@
         <v>1099</v>
       </c>
       <c r="F424" t="n">
-        <v>1050.5</v>
+        <v>1046.5</v>
       </c>
       <c r="G424" t="n">
         <v>1081</v>
@@ -13591,7 +13591,7 @@
         <v>1099</v>
       </c>
       <c r="F425" t="n">
-        <v>1046.5</v>
+        <v>1049</v>
       </c>
       <c r="G425" t="n">
         <v>1079</v>
@@ -13622,7 +13622,7 @@
         <v>1100</v>
       </c>
       <c r="F426" t="n">
-        <v>1049</v>
+        <v>1048.5</v>
       </c>
       <c r="G426" t="n">
         <v>1079</v>
@@ -13650,10 +13650,10 @@
         </is>
       </c>
       <c r="E427" t="n">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="F427" t="n">
-        <v>1049</v>
+        <v>1050.5</v>
       </c>
       <c r="G427" t="n">
         <v>1079</v>
@@ -13684,10 +13684,10 @@
         <v>1099</v>
       </c>
       <c r="F428" t="n">
-        <v>1049</v>
+        <v>1048.5</v>
       </c>
       <c r="G428" t="n">
-        <v>1079</v>
+        <v>1077.5</v>
       </c>
     </row>
     <row r="429">
@@ -13712,10 +13712,10 @@
         </is>
       </c>
       <c r="E429" t="n">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="F429" t="n">
-        <v>1049</v>
+        <v>1048.5</v>
       </c>
       <c r="G429" t="n">
         <v>1081</v>
@@ -13746,7 +13746,7 @@
         <v>1099</v>
       </c>
       <c r="F430" t="n">
-        <v>1046.5</v>
+        <v>1049</v>
       </c>
       <c r="G430" t="n">
         <v>1081</v>
@@ -13777,10 +13777,10 @@
         <v>1099</v>
       </c>
       <c r="F431" t="n">
-        <v>1050.5</v>
+        <v>1049</v>
       </c>
       <c r="G431" t="n">
-        <v>1077.5</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="432">
@@ -13805,13 +13805,13 @@
         </is>
       </c>
       <c r="E432" t="n">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="F432" t="n">
-        <v>1050.5</v>
+        <v>1049</v>
       </c>
       <c r="G432" t="n">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="433">
@@ -13867,13 +13867,13 @@
         </is>
       </c>
       <c r="E434" t="n">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="F434" t="n">
-        <v>1050.5</v>
+        <v>1046.5</v>
       </c>
       <c r="G434" t="n">
-        <v>1077.5</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="435">
@@ -13898,13 +13898,13 @@
         </is>
       </c>
       <c r="E435" t="n">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="F435" t="n">
-        <v>1046.5</v>
+        <v>1049</v>
       </c>
       <c r="G435" t="n">
-        <v>1077.5</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="436">
@@ -13932,7 +13932,7 @@
         <v>1099</v>
       </c>
       <c r="F436" t="n">
-        <v>1048.5</v>
+        <v>1046.5</v>
       </c>
       <c r="G436" t="n">
         <v>1079</v>
@@ -13960,13 +13960,13 @@
         </is>
       </c>
       <c r="E437" t="n">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="F437" t="n">
         <v>1049</v>
       </c>
       <c r="G437" t="n">
-        <v>1077.5</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="438">
@@ -13991,13 +13991,13 @@
         </is>
       </c>
       <c r="E438" t="n">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="F438" t="n">
-        <v>1048.5</v>
+        <v>1049</v>
       </c>
       <c r="G438" t="n">
-        <v>1077.5</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="439">
@@ -14025,7 +14025,7 @@
         <v>1099</v>
       </c>
       <c r="F439" t="n">
-        <v>1050.5</v>
+        <v>1049</v>
       </c>
       <c r="G439" t="n">
         <v>1081</v>
@@ -14121,7 +14121,7 @@
         <v>1046.5</v>
       </c>
       <c r="G442" t="n">
-        <v>1077.5</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="443">
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="E443" t="n">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="F443" t="n">
         <v>1048.5</v>
@@ -14177,10 +14177,10 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="F444" t="n">
-        <v>1046.5</v>
+        <v>1050.5</v>
       </c>
       <c r="G444" t="n">
         <v>1079</v>
@@ -14208,7 +14208,7 @@
         </is>
       </c>
       <c r="E445" t="n">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="F445" t="n">
         <v>1049</v>
@@ -14245,7 +14245,7 @@
         <v>1049</v>
       </c>
       <c r="G446" t="n">
-        <v>1079</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="447">
@@ -14270,13 +14270,13 @@
         </is>
       </c>
       <c r="E447" t="n">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="F447" t="n">
-        <v>1050.5</v>
+        <v>1049</v>
       </c>
       <c r="G447" t="n">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="448">
@@ -14304,7 +14304,7 @@
         <v>1099</v>
       </c>
       <c r="F448" t="n">
-        <v>1046.5</v>
+        <v>1050.5</v>
       </c>
       <c r="G448" t="n">
         <v>1077.5</v>
@@ -14332,10 +14332,10 @@
         </is>
       </c>
       <c r="E449" t="n">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="F449" t="n">
-        <v>1048.5</v>
+        <v>1049</v>
       </c>
       <c r="G449" t="n">
         <v>1079</v>
@@ -14369,7 +14369,7 @@
         <v>1049</v>
       </c>
       <c r="G450" t="n">
-        <v>1077.5</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="451">
@@ -14394,10 +14394,10 @@
         </is>
       </c>
       <c r="E451" t="n">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="F451" t="n">
-        <v>1049</v>
+        <v>1046.5</v>
       </c>
       <c r="G451" t="n">
         <v>1079</v>
@@ -14428,7 +14428,7 @@
         <v>499.99</v>
       </c>
       <c r="F452" t="n">
-        <v>487.49</v>
+        <v>489.49</v>
       </c>
       <c r="G452" t="n">
         <v>499.99</v>
@@ -14459,10 +14459,10 @@
         <v>499.99</v>
       </c>
       <c r="F453" t="n">
-        <v>489.99</v>
+        <v>489.49</v>
       </c>
       <c r="G453" t="n">
-        <v>499.99</v>
+        <v>498.49</v>
       </c>
     </row>
     <row r="454">
@@ -14487,10 +14487,10 @@
         </is>
       </c>
       <c r="E454" t="n">
-        <v>500.99</v>
+        <v>498.99</v>
       </c>
       <c r="F454" t="n">
-        <v>491.49</v>
+        <v>489.99</v>
       </c>
       <c r="G454" t="n">
         <v>501.99</v>
@@ -14518,13 +14518,13 @@
         </is>
       </c>
       <c r="E455" t="n">
-        <v>498.99</v>
+        <v>500.99</v>
       </c>
       <c r="F455" t="n">
-        <v>489.49</v>
+        <v>489.99</v>
       </c>
       <c r="G455" t="n">
-        <v>499.99</v>
+        <v>501.99</v>
       </c>
     </row>
     <row r="456">
@@ -14549,10 +14549,10 @@
         </is>
       </c>
       <c r="E456" t="n">
-        <v>498.99</v>
+        <v>499.99</v>
       </c>
       <c r="F456" t="n">
-        <v>491.49</v>
+        <v>489.99</v>
       </c>
       <c r="G456" t="n">
         <v>499.99</v>
@@ -14586,7 +14586,7 @@
         <v>489.99</v>
       </c>
       <c r="G457" t="n">
-        <v>499.99</v>
+        <v>498.49</v>
       </c>
     </row>
     <row r="458">
@@ -14611,10 +14611,10 @@
         </is>
       </c>
       <c r="E458" t="n">
-        <v>500.99</v>
+        <v>499.99</v>
       </c>
       <c r="F458" t="n">
-        <v>489.99</v>
+        <v>489.49</v>
       </c>
       <c r="G458" t="n">
         <v>499.99</v>
@@ -14642,13 +14642,13 @@
         </is>
       </c>
       <c r="E459" t="n">
-        <v>499.99</v>
+        <v>500.99</v>
       </c>
       <c r="F459" t="n">
-        <v>491.49</v>
+        <v>489.49</v>
       </c>
       <c r="G459" t="n">
-        <v>499.99</v>
+        <v>501.99</v>
       </c>
     </row>
     <row r="460">
@@ -14673,13 +14673,13 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>500.99</v>
+        <v>499.99</v>
       </c>
       <c r="F460" t="n">
-        <v>489.99</v>
+        <v>487.49</v>
       </c>
       <c r="G460" t="n">
-        <v>501.99</v>
+        <v>498.49</v>
       </c>
     </row>
     <row r="461">
@@ -14707,7 +14707,7 @@
         <v>499.99</v>
       </c>
       <c r="F461" t="n">
-        <v>489.99</v>
+        <v>487.49</v>
       </c>
       <c r="G461" t="n">
         <v>499.99</v>
@@ -14735,13 +14735,13 @@
         </is>
       </c>
       <c r="E462" t="n">
-        <v>500.99</v>
+        <v>498.99</v>
       </c>
       <c r="F462" t="n">
-        <v>491.49</v>
+        <v>487.49</v>
       </c>
       <c r="G462" t="n">
-        <v>501.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="463">
@@ -14769,7 +14769,7 @@
         <v>499.99</v>
       </c>
       <c r="F463" t="n">
-        <v>487.49</v>
+        <v>491.49</v>
       </c>
       <c r="G463" t="n">
         <v>499.99</v>
@@ -14800,10 +14800,10 @@
         <v>500.99</v>
       </c>
       <c r="F464" t="n">
-        <v>487.49</v>
+        <v>489.49</v>
       </c>
       <c r="G464" t="n">
-        <v>501.99</v>
+        <v>498.49</v>
       </c>
     </row>
     <row r="465">
@@ -14831,10 +14831,10 @@
         <v>499.99</v>
       </c>
       <c r="F465" t="n">
-        <v>487.49</v>
+        <v>491.49</v>
       </c>
       <c r="G465" t="n">
-        <v>499.99</v>
+        <v>501.99</v>
       </c>
     </row>
     <row r="466">
@@ -14862,10 +14862,10 @@
         <v>500.99</v>
       </c>
       <c r="F466" t="n">
-        <v>491.49</v>
+        <v>487.49</v>
       </c>
       <c r="G466" t="n">
-        <v>499.99</v>
+        <v>498.49</v>
       </c>
     </row>
     <row r="467">
@@ -14890,10 +14890,10 @@
         </is>
       </c>
       <c r="E467" t="n">
-        <v>499.99</v>
+        <v>500.99</v>
       </c>
       <c r="F467" t="n">
-        <v>489.99</v>
+        <v>491.49</v>
       </c>
       <c r="G467" t="n">
         <v>499.99</v>
@@ -14924,10 +14924,10 @@
         <v>499.99</v>
       </c>
       <c r="F468" t="n">
-        <v>491.49</v>
+        <v>489.99</v>
       </c>
       <c r="G468" t="n">
-        <v>498.49</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="469">
@@ -14955,10 +14955,10 @@
         <v>499.99</v>
       </c>
       <c r="F469" t="n">
-        <v>489.99</v>
+        <v>487.49</v>
       </c>
       <c r="G469" t="n">
-        <v>498.49</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="470">
@@ -14989,7 +14989,7 @@
         <v>487.49</v>
       </c>
       <c r="G470" t="n">
-        <v>498.49</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="471">
@@ -15014,10 +15014,10 @@
         </is>
       </c>
       <c r="E471" t="n">
-        <v>500.99</v>
+        <v>498.99</v>
       </c>
       <c r="F471" t="n">
-        <v>487.49</v>
+        <v>489.99</v>
       </c>
       <c r="G471" t="n">
         <v>499.99</v>
@@ -15045,13 +15045,13 @@
         </is>
       </c>
       <c r="E472" t="n">
-        <v>500.99</v>
+        <v>498.99</v>
       </c>
       <c r="F472" t="n">
-        <v>489.49</v>
+        <v>489.99</v>
       </c>
       <c r="G472" t="n">
-        <v>499.99</v>
+        <v>501.99</v>
       </c>
     </row>
     <row r="473">
@@ -15079,7 +15079,7 @@
         <v>499.99</v>
       </c>
       <c r="F473" t="n">
-        <v>489.99</v>
+        <v>487.49</v>
       </c>
       <c r="G473" t="n">
         <v>499.99</v>
@@ -15107,13 +15107,13 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>499.99</v>
+        <v>498.99</v>
       </c>
       <c r="F474" t="n">
         <v>491.49</v>
       </c>
       <c r="G474" t="n">
-        <v>498.49</v>
+        <v>501.99</v>
       </c>
     </row>
     <row r="475">
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="E475" t="n">
-        <v>498.99</v>
+        <v>499.99</v>
       </c>
       <c r="F475" t="n">
-        <v>489.99</v>
+        <v>489.49</v>
       </c>
       <c r="G475" t="n">
         <v>499.99</v>
@@ -15169,13 +15169,13 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>500.99</v>
+        <v>499.99</v>
       </c>
       <c r="F476" t="n">
         <v>489.99</v>
       </c>
       <c r="G476" t="n">
-        <v>498.49</v>
+        <v>501.99</v>
       </c>
     </row>
     <row r="477">
@@ -15200,13 +15200,13 @@
         </is>
       </c>
       <c r="E477" t="n">
-        <v>499.99</v>
+        <v>500.99</v>
       </c>
       <c r="F477" t="n">
         <v>489.99</v>
       </c>
       <c r="G477" t="n">
-        <v>501.99</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="478">
@@ -15231,7 +15231,7 @@
         </is>
       </c>
       <c r="E478" t="n">
-        <v>499.99</v>
+        <v>498.99</v>
       </c>
       <c r="F478" t="n">
         <v>487.49</v>
@@ -15265,10 +15265,10 @@
         <v>498.99</v>
       </c>
       <c r="F479" t="n">
-        <v>491.49</v>
+        <v>489.49</v>
       </c>
       <c r="G479" t="n">
-        <v>498.49</v>
+        <v>499.99</v>
       </c>
     </row>
     <row r="480">
@@ -15293,13 +15293,13 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>498.99</v>
+        <v>499.99</v>
       </c>
       <c r="F480" t="n">
         <v>491.49</v>
       </c>
       <c r="G480" t="n">
-        <v>499.99</v>
+        <v>498.49</v>
       </c>
     </row>
     <row r="481">
@@ -15327,7 +15327,7 @@
         <v>499.99</v>
       </c>
       <c r="F481" t="n">
-        <v>491.49</v>
+        <v>487.49</v>
       </c>
       <c r="G481" t="n">
         <v>501.99</v>
